--- a/curriculum/master-map/Mathematics_Understood_Master_Curriculum_Map_v0.2.xlsx
+++ b/curriculum/master-map/Mathematics_Understood_Master_Curriculum_Map_v0.2.xlsx
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>Representation notes belong in the representation column, not the prerequisite-ID column.</t>
+          <t>Cell-level check confirms representation notes are in the representation column and the prerequisite-ID field is empty.</t>
         </is>
       </c>
     </row>
@@ -1564,22 +1564,22 @@
       </c>
       <c r="D21" s="76" t="inlineStr">
         <is>
-          <t>FND-001 representation notes were placed in Core prerequisite IDs.</t>
+          <t>FND-001 field placement was inspected against the source; representation notes are already in the correct column.</t>
         </is>
       </c>
       <c r="E21" s="76" t="inlineStr">
         <is>
-          <t>Move those notes to Representations / visual requirements and keep prerequisites empty unless actual concept IDs are required.</t>
+          <t>Preserve the correct source data and keep a regression check that the prerequisite column contains concept IDs only.</t>
         </is>
       </c>
       <c r="F21" s="78" t="inlineStr">
         <is>
-          <t>Resolved in v0.2</t>
+          <t>Resolved — verified</t>
         </is>
       </c>
       <c r="G21" s="76" t="inlineStr">
         <is>
-          <t>FND-001 prerequisite cell is empty; representation cell has the notes; prerequisite pairs reconcile.</t>
+          <t>Cell-level check confirms the prerequisite cell is empty and the representation column contains the notes.</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Audited successor to v0.1. One FND-001 field-alignment issue was corrected. Concepts and dependency interpretations remain provisional pending pedagogical review.</t>
+          <t>Audited successor to v0.1. FND-001 field placement was checked against the source and is already correct. Concepts and dependency interpretations remain provisional pending pedagogical review.</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>

--- a/curriculum/master-map/Mathematics_Understood_Master_Curriculum_Map_v0.2.xlsx
+++ b/curriculum/master-map/Mathematics_Understood_Master_Curriculum_Map_v0.2.xlsx
@@ -755,7 +755,7 @@
     <tableColumn id="6" name="v0.1 status"/>
     <tableColumn id="7" name="v0.2 review classification"/>
     <tableColumn id="8" name="Specific dependency mechanism / evidence"/>
-    <tableColumn id="9" name="Validation check / test"/>
+    <tableColumn id="9" name="Proposed validation check / test"/>
     <tableColumn id="10" name="Reviewer"/>
     <tableColumn id="11" name="Review date"/>
   </tableColumns>
@@ -764,8 +764,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="CurriculumStructuralAuditV02" displayName="CurriculumStructuralAuditV02" ref="A4:C16" headerRowCount="1">
-  <autoFilter ref="A4:C16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="CurriculumStructuralAuditV02" displayName="CurriculumStructuralAuditV02" ref="A4:C18" headerRowCount="1">
+  <autoFilter ref="A4:C18"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Structural check"/>
     <tableColumn id="2" name="Result"/>
@@ -1182,6 +1182,14 @@
       <c r="H13" s="1" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="53" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary edge reviews</t>
+        </is>
+      </c>
+      <c r="B14" s="53" t="n">
+        <v>27</v>
+      </c>
       <c r="D14" s="60" t="inlineStr">
         <is>
           <t>4 — University core</t>
@@ -1195,6 +1203,14 @@
       <c r="H14" s="1" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="53" t="inlineStr">
+        <is>
+          <t>Edges still unreviewed</t>
+        </is>
+      </c>
+      <c r="B15" s="53" t="n">
+        <v>241</v>
+      </c>
       <c r="D15" s="60" t="inlineStr">
         <is>
           <t>5 — Advanced applied mathematics</t>
@@ -1392,7 +1408,7 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t>Inventory/edge-list mismatch pairs after repair</t>
+          <t>Inventory/edge-list mismatch pairs after field validation</t>
         </is>
       </c>
       <c r="B10" s="30" t="n">
@@ -1452,45 +1468,75 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>FND-001 field alignment</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>Corrected</t>
-        </is>
+          <t>Edges with AI-assisted preliminary desk review</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>27</v>
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>Cell-level check confirms representation notes are in the representation column and the prerequisite-ID field is empty.</t>
+          <t>Draft classifications only; educator confirmation and learner evidence remain pending.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>Science application rows</t>
+          <t>Edges remaining unreviewed</t>
         </is>
       </c>
       <c r="B15" s="30" t="n">
-        <v>13</v>
+        <v>241</v>
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>Each needs science/source review and explicit model assumptions.</t>
+          <t>Do not infer a classification from the edge's position or old v0.1 label.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
+          <t>FND-001 field alignment</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>Already aligned</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>Cell-level check confirms representation notes are in the representation column and the prerequisite-ID field is empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>Science application rows</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>Each needs science/source review and explicit model assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
           <t>Open design decisions</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B18" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>Stages remain provisional and do not define final book volumes.</t>
         </is>
@@ -1601,22 +1647,22 @@
       </c>
       <c r="D22" s="76" t="inlineStr">
         <is>
-          <t>All 268 edges use the Core / presumed prerequisite label and remain provisional.</t>
+          <t>27 of 268 edges have AI-assisted preliminary desk classifications; 241 remain unreviewed.</t>
         </is>
       </c>
       <c r="E22" s="76" t="inlineStr">
         <is>
-          <t>Review every edge; classify it as Core required, Helpful, Repair path, Contextual link, or Remove; record a specific reason and a validation check.</t>
+          <t>Continue reviewing in focused tranches. Treat prefilled classifications as draft hypotheses until a mathematics educator checks them and learner diagnostics/transfer tasks support the intended pathway.</t>
         </is>
       </c>
       <c r="F22" s="80" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Working</t>
         </is>
       </c>
       <c r="G22" s="76" t="inlineStr">
         <is>
-          <t>All edge rows have a reviewed classification, specific mechanism, validation check, reviewer, and date.</t>
+          <t>Each edge has an explicit classification, specific mechanism, proposed validation check, reviewer, and date; educator sign-off is distinguished from AI-assisted desk review.</t>
         </is>
       </c>
     </row>
@@ -19997,7 +20043,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="71" t="inlineStr">
         <is>
-          <t>All v0.1 edge types and rationale text are preserved as historical proposals. Every row begins UNREVIEWED; classify a relationship only after deciding whether it is required, helpful, a repair path, contextual, or unnecessary.</t>
+          <t>All v0.1 edge types and rationale text are preserved as historical proposals. The first 27 high-leverage foundation/algebra edges have AI-assisted preliminary desk reviews; educator confirmation is pending. All other rows remain UNREVIEWED. A preliminary classification is not a final pedagogical sign-off.</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -20071,7 +20117,7 @@
       </c>
       <c r="I4" s="73" t="inlineStr">
         <is>
-          <t>Validation check / test</t>
+          <t>Proposed validation check / test</t>
         </is>
       </c>
       <c r="J4" s="73" t="inlineStr">
@@ -21266,13 +21312,29 @@
       </c>
       <c r="G33" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H33" s="74" t="n"/>
-      <c r="I33" s="74" t="n"/>
-      <c r="J33" s="74" t="n"/>
-      <c r="K33" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H33" s="74" t="inlineStr">
+        <is>
+          <t>Signed-rational arithmetic helps with later examples but is not needed to introduce the roles of variable, unknown, and parameter. Use whole-number contexts first; provide FND-015 as a repair path where calculations—not letter roles—block learning.</t>
+        </is>
+      </c>
+      <c r="I33" s="74" t="inlineStr">
+        <is>
+          <t>Teach the letter-role objective with whole-number contexts, then test a separate signed-rational transfer item. If only the second fails, do not treat FND-015 as a gate for ALG-001.</t>
+        </is>
+      </c>
+      <c r="J33" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K33" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="32" t="inlineStr">
@@ -21307,13 +21369,29 @@
       </c>
       <c r="G34" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H34" s="74" t="n"/>
-      <c r="I34" s="74" t="n"/>
-      <c r="J34" s="74" t="n"/>
-      <c r="K34" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H34" s="74" t="inlineStr">
+        <is>
+          <t>Minimum symbol/statement literacy supports reading letters and translating between verbal and symbolic forms. For accessible self-study, teach this minimum within an ALG-001 bridge instead of denying entry.</t>
+        </is>
+      </c>
+      <c r="I34" s="74" t="inlineStr">
+        <is>
+          <t>Diagnostic: interpret x + 2 and translate 'a number plus 2'; provide a short notation bridge and retest variable/unknown/parameter distinctions.</t>
+        </is>
+      </c>
+      <c r="J34" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K34" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="32" t="inlineStr">
@@ -21348,13 +21426,29 @@
       </c>
       <c r="G35" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H35" s="74" t="n"/>
-      <c r="I35" s="74" t="n"/>
-      <c r="J35" s="74" t="n"/>
-      <c r="K35" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H35" s="74" t="inlineStr">
+        <is>
+          <t>The meanings of variables and parameters are needed to interpret symbolic expressions and reason about equivalence; the two concepts may be scaffolded in adjacent lessons.</t>
+        </is>
+      </c>
+      <c r="I35" s="74" t="inlineStr">
+        <is>
+          <t>Ask learners to identify the role of a letter and explain why 2x + 3 and 3 + 2x are equivalent; record whether an ALG-001 refresh is enough.</t>
+        </is>
+      </c>
+      <c r="J35" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K35" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="32" t="inlineStr">
@@ -21389,13 +21483,29 @@
       </c>
       <c r="G36" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H36" s="74" t="n"/>
-      <c r="I36" s="74" t="n"/>
-      <c r="J36" s="74" t="n"/>
-      <c r="K36" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H36" s="74" t="inlineStr">
+        <is>
+          <t>Numerical operation meanings and basic properties underpin interpretation and simplification of symbolic expressions. This requires operational meaning, not mastery of every arithmetic strand.</t>
+        </is>
+      </c>
+      <c r="I36" s="74" t="inlineStr">
+        <is>
+          <t>Move from 3 + 2 and 3 × 2 to 3x + 2x and equivalent forms; distinguish operation-meaning errors from notation errors.</t>
+        </is>
+      </c>
+      <c r="J36" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K36" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="32" t="inlineStr">
@@ -21430,13 +21540,29 @@
       </c>
       <c r="G37" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H37" s="74" t="n"/>
-      <c r="I37" s="74" t="n"/>
-      <c r="J37" s="74" t="n"/>
-      <c r="K37" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H37" s="74" t="inlineStr">
+        <is>
+          <t>Exponent notation appears in some expressions, but initial expression meaning/equivalence can be learned without exponent laws. Introduce FND-014 just in time when powers enter.</t>
+        </is>
+      </c>
+      <c r="I37" s="74" t="inlineStr">
+        <is>
+          <t>Check the ALG-002 outcomes using expressions without exponents; verify that power laws are not secretly assumed before introducing them explicitly.</t>
+        </is>
+      </c>
+      <c r="J37" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K37" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="32" t="inlineStr">
@@ -21471,13 +21597,29 @@
       </c>
       <c r="G38" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H38" s="74" t="n"/>
-      <c r="I38" s="74" t="n"/>
-      <c r="J38" s="74" t="n"/>
-      <c r="K38" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H38" s="74" t="inlineStr">
+        <is>
+          <t>Equations and inequalities relate expressions and constrain possible values, so expression interpretation and equivalence are foundational to the current mapped outcome.</t>
+        </is>
+      </c>
+      <c r="I38" s="74" t="inlineStr">
+        <is>
+          <t>Ask learners to interpret x + 2 = 5 and x + 2 &lt; 5, distinguish expression from statement, and test candidate values.</t>
+        </is>
+      </c>
+      <c r="J38" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K38" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="32" t="inlineStr">
@@ -21512,13 +21654,29 @@
       </c>
       <c r="G39" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H39" s="74" t="n"/>
-      <c r="I39" s="74" t="n"/>
-      <c r="J39" s="74" t="n"/>
-      <c r="K39" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H39" s="74" t="inlineStr">
+        <is>
+          <t>A signed number line is important for representing solution sets with negative values, but the meaning of an equation or inequality as a statement can be taught earlier. This cluster combines both tasks.</t>
+        </is>
+      </c>
+      <c r="I39" s="74" t="inlineStr">
+        <is>
+          <t>Assess separately: identify an equation/inequality as a constraint, then graph a solution set spanning negative and positive values. FND-006 is more essential for the latter.</t>
+        </is>
+      </c>
+      <c r="J39" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K39" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="32" t="inlineStr">
@@ -21553,13 +21711,29 @@
       </c>
       <c r="G40" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H40" s="74" t="n"/>
-      <c r="I40" s="74" t="n"/>
-      <c r="J40" s="74" t="n"/>
-      <c r="K40" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H40" s="74" t="inlineStr">
+        <is>
+          <t>Solving equations depends on understanding them as constraints and preserving the solution set under valid transformations.</t>
+        </is>
+      </c>
+      <c r="I40" s="74" t="inlineStr">
+        <is>
+          <t>Have learners solve and verify a linear equation, then explain why a valid operation performed on both sides preserves equality.</t>
+        </is>
+      </c>
+      <c r="J40" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K40" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="32" t="inlineStr">
@@ -21594,13 +21768,29 @@
       </c>
       <c r="G41" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H41" s="74" t="n"/>
-      <c r="I41" s="74" t="n"/>
-      <c r="J41" s="74" t="n"/>
-      <c r="K41" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H41" s="74" t="inlineStr">
+        <is>
+          <t>Full linear equation/inequality fluency with standard rational coefficients uses signed and rational arithmetic. Integer-only starter examples may precede it, but the complete ALG-004 outcome needs this capability or targeted repair.</t>
+        </is>
+      </c>
+      <c r="I41" s="74" t="inlineStr">
+        <is>
+          <t>Use equations with negative/fractional coefficients and sign-sensitive inequalities. Diagnose arithmetic errors separately and provide an FND-015 repair where needed.</t>
+        </is>
+      </c>
+      <c r="J41" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K41" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="32" t="inlineStr">
@@ -21635,13 +21825,29 @@
       </c>
       <c r="G42" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H42" s="74" t="n"/>
-      <c r="I42" s="74" t="n"/>
-      <c r="J42" s="74" t="n"/>
-      <c r="K42" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H42" s="74" t="inlineStr">
+        <is>
+          <t>Rearranging literal formulas extends isolating an unknown through reversible equation transformations, the central capability developed in linear equation solving.</t>
+        </is>
+      </c>
+      <c r="I42" s="74" t="inlineStr">
+        <is>
+          <t>Rearrange a familiar formula for a different variable, substitute back, and check nonzero-denominator restrictions.</t>
+        </is>
+      </c>
+      <c r="J42" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K42" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="32" t="inlineStr">
@@ -21676,13 +21882,29 @@
       </c>
       <c r="G43" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H43" s="74" t="n"/>
-      <c r="I43" s="74" t="n"/>
-      <c r="J43" s="74" t="n"/>
-      <c r="K43" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H43" s="74" t="inlineStr">
+        <is>
+          <t>Formula rearrangement requires learners to interpret and maintain equivalent symbolic expressions even when the target variable changes.</t>
+        </is>
+      </c>
+      <c r="I43" s="74" t="inlineStr">
+        <is>
+          <t>Give an equivalent-expression task before rearranging a literal formula; check whether the transformation reasoning transfers.</t>
+        </is>
+      </c>
+      <c r="J43" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K43" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="32" t="inlineStr">
@@ -21717,13 +21939,29 @@
       </c>
       <c r="G44" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H44" s="74" t="n"/>
-      <c r="I44" s="74" t="n"/>
-      <c r="J44" s="74" t="n"/>
-      <c r="K44" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H44" s="74" t="inlineStr">
+        <is>
+          <t>Unit conversion and dimensional sense are not prerequisites for symbolic rearrangement itself; they are important for interpreting unit-bearing formulas and scientific applications.</t>
+        </is>
+      </c>
+      <c r="I44" s="74" t="inlineStr">
+        <is>
+          <t>Compare a pure-symbol rearrangement with a unit-bearing application; assess algebraic success separately from interpreting and checking units.</t>
+        </is>
+      </c>
+      <c r="J44" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K44" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="32" t="inlineStr">
@@ -21758,13 +21996,29 @@
       </c>
       <c r="G45" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H45" s="74" t="n"/>
-      <c r="I45" s="74" t="n"/>
-      <c r="J45" s="74" t="n"/>
-      <c r="K45" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H45" s="74" t="inlineStr">
+        <is>
+          <t>The coordinate-plane outcome includes signed coordinates and points in all quadrants. Understanding signed values relative to zero is a direct conceptual support and can be bridged locally.</t>
+        </is>
+      </c>
+      <c r="I45" s="74" t="inlineStr">
+        <is>
+          <t>Ask learners to order signed values on a number line, then plot ordered pairs in all four quadrants; identify sign and axis errors.</t>
+        </is>
+      </c>
+      <c r="J45" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K45" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="32" t="inlineStr">
@@ -21799,13 +22053,29 @@
       </c>
       <c r="G46" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H46" s="74" t="n"/>
-      <c r="I46" s="74" t="n"/>
-      <c r="J46" s="74" t="n"/>
-      <c r="K46" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H46" s="74" t="inlineStr">
+        <is>
+          <t>Basic notation helps with ordered pairs and coordinate labels, but these conventions are teachable inside the coordinate lesson. Do not make the entire FND-001 cluster a rigid gate.</t>
+        </is>
+      </c>
+      <c r="I46" s="74" t="inlineStr">
+        <is>
+          <t>Give a brief ordered-pair/axis primer and test plotting; compare error types before and after the local explanation.</t>
+        </is>
+      </c>
+      <c r="J46" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K46" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="32" t="inlineStr">
@@ -21840,13 +22110,29 @@
       </c>
       <c r="G47" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H47" s="74" t="n"/>
-      <c r="I47" s="74" t="n"/>
-      <c r="J47" s="74" t="n"/>
-      <c r="K47" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H47" s="74" t="inlineStr">
+        <is>
+          <t>Graph literacy explicitly requires plotting/interpreting coordinates and relating graphs to tables, equations, and contexts; coordinate-plane fluency is a direct dependency.</t>
+        </is>
+      </c>
+      <c r="I47" s="74" t="inlineStr">
+        <is>
+          <t>Before graph-construction tasks, plot table values with labelled axes and scales; assess coordinate plotting separately from trend interpretation.</t>
+        </is>
+      </c>
+      <c r="J47" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K47" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="32" t="inlineStr">
@@ -21881,13 +22167,29 @@
       </c>
       <c r="G48" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H48" s="74" t="n"/>
-      <c r="I48" s="74" t="n"/>
-      <c r="J48" s="74" t="n"/>
-      <c r="K48" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H48" s="74" t="inlineStr">
+        <is>
+          <t>Proportional relationships offer useful graphs through the origin, but graph literacy must cover non-proportional, nonlinear, and empirical graphs too.</t>
+        </is>
+      </c>
+      <c r="I48" s="74" t="inlineStr">
+        <is>
+          <t>Test graph interpretation on non-proportional lines, nonlinear curves, and empirical/categorical data as well as percentage examples.</t>
+        </is>
+      </c>
+      <c r="J48" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K48" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="32" t="inlineStr">
@@ -21922,13 +22224,29 @@
       </c>
       <c r="G49" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H49" s="74" t="n"/>
-      <c r="I49" s="74" t="n"/>
-      <c r="J49" s="74" t="n"/>
-      <c r="K49" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H49" s="74" t="inlineStr">
+        <is>
+          <t>The current slope/rate outcome includes graph interpretation and proportional-versus-affine comparison; graph literacy supports axis/scale reading and representation changes.</t>
+        </is>
+      </c>
+      <c r="I49" s="74" t="inlineStr">
+        <is>
+          <t>Infer rate from a graph with nontrivial axis scales, confirm from a table, and separate graph-reading errors from rate-reasoning errors.</t>
+        </is>
+      </c>
+      <c r="J49" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K49" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="32" t="inlineStr">
@@ -21963,13 +22281,29 @@
       </c>
       <c r="G50" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H50" s="74" t="n"/>
-      <c r="I50" s="74" t="n"/>
-      <c r="J50" s="74" t="n"/>
-      <c r="K50" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H50" s="74" t="inlineStr">
+        <is>
+          <t>Slope/rate of change is change-per-change; ratios and unit rates supply the conceptual basis for interpreting slope rather than memorizing rise-over-run.</t>
+        </is>
+      </c>
+      <c r="I50" s="74" t="inlineStr">
+        <is>
+          <t>Transfer from a unit-rate context and double number line to a table and graph; explain the ratio and its units.</t>
+        </is>
+      </c>
+      <c r="J50" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K50" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="32" t="inlineStr">
@@ -22004,13 +22338,29 @@
       </c>
       <c r="G51" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H51" s="74" t="n"/>
-      <c r="I51" s="74" t="n"/>
-      <c r="J51" s="74" t="n"/>
-      <c r="K51" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H51" s="74" t="inlineStr">
+        <is>
+          <t>Unit/dimensional sense improves interpretation of slope and intercept units, but an initial slope concept can be taught on a unitless graph. The full measurement cluster is broader than the minimum prerequisite.</t>
+        </is>
+      </c>
+      <c r="I51" s="74" t="inlineStr">
+        <is>
+          <t>Assess calculation first and unit interpretation second; teach only the missing unit subskill locally when needed.</t>
+        </is>
+      </c>
+      <c r="J51" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K51" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="32" t="inlineStr">
@@ -22045,13 +22395,29 @@
       </c>
       <c r="G52" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H52" s="74" t="n"/>
-      <c r="I52" s="74" t="n"/>
-      <c r="J52" s="74" t="n"/>
-      <c r="K52" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H52" s="74" t="inlineStr">
+        <is>
+          <t>A function can first be introduced through mappings, input-output tables, and uniqueness, without symbolic expressions. Expression skill is needed for formula representations.</t>
+        </is>
+      </c>
+      <c r="I52" s="74" t="inlineStr">
+        <is>
+          <t>Teach a mapping/table example before a formula; assess function recognition separately from interpretation of symbolic rules.</t>
+        </is>
+      </c>
+      <c r="J52" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K52" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="32" t="inlineStr">
@@ -22086,13 +22452,29 @@
       </c>
       <c r="G53" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H53" s="74" t="n"/>
-      <c r="I53" s="74" t="n"/>
-      <c r="J53" s="74" t="n"/>
-      <c r="K53" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H53" s="74" t="inlineStr">
+        <is>
+          <t>Coordinates are needed for graphical representations of functions, not for the input-output/mapping definition itself. Multiple representations should provide more than one entry route.</t>
+        </is>
+      </c>
+      <c r="I53" s="74" t="inlineStr">
+        <is>
+          <t>Assess function recognition from mappings and tables before graph tasks; keep graph interpretation as a dependent sub-outcome.</t>
+        </is>
+      </c>
+      <c r="J53" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K53" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="32" t="inlineStr">
@@ -22127,13 +22509,29 @@
       </c>
       <c r="G54" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H54" s="74" t="n"/>
-      <c r="I54" s="74" t="n"/>
-      <c r="J54" s="74" t="n"/>
-      <c r="K54" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H54" s="74" t="inlineStr">
+        <is>
+          <t>The mapped linear-function outcome uses slope/rate and the proportional-versus-affine distinction established in ALG-008.</t>
+        </is>
+      </c>
+      <c r="I54" s="74" t="inlineStr">
+        <is>
+          <t>From a table with constant first differences, build a linear rule, identify slope/intercept, and distinguish a line through the origin from one with nonzero intercept.</t>
+        </is>
+      </c>
+      <c r="J54" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K54" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="32" t="inlineStr">
@@ -22168,13 +22566,29 @@
       </c>
       <c r="G55" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H55" s="74" t="n"/>
-      <c r="I55" s="74" t="n"/>
-      <c r="J55" s="74" t="n"/>
-      <c r="K55" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H55" s="74" t="inlineStr">
+        <is>
+          <t>In this curriculum, a general function concept supplies input-output, domain, and range language needed to position linear functions as one function family. Motivation with a linear example can still come first.</t>
+        </is>
+      </c>
+      <c r="I55" s="74" t="inlineStr">
+        <is>
+          <t>Compare linear and non-linear functions and a relation that fails uniqueness; check whether learners can explain the special case and its domain.</t>
+        </is>
+      </c>
+      <c r="J55" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K55" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="32" t="inlineStr">
@@ -22209,13 +22623,29 @@
       </c>
       <c r="G56" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H56" s="74" t="n"/>
-      <c r="I56" s="74" t="n"/>
-      <c r="J56" s="74" t="n"/>
-      <c r="K56" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H56" s="74" t="inlineStr">
+        <is>
+          <t>Interpreting a linear function as an equation requires minimum fluency with equality as a relation and symbolic statements. Teach that minimum within the linear-function lesson if necessary.</t>
+        </is>
+      </c>
+      <c r="I56" s="74" t="inlineStr">
+        <is>
+          <t>Ask learners to read y = 2x + 3 as a relationship, explain what equality asserts, and interpret slope/intercept; note if a short bridge suffices.</t>
+        </is>
+      </c>
+      <c r="J56" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K56" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="32" t="inlineStr">
@@ -22250,13 +22680,29 @@
       </c>
       <c r="G57" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H57" s="74" t="n"/>
-      <c r="I57" s="74" t="n"/>
-      <c r="J57" s="74" t="n"/>
-      <c r="K57" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H57" s="74" t="inlineStr">
+        <is>
+          <t>Substitution and elimination extend equation-solving transformations and depend on preserving equality while isolating or eliminating variables.</t>
+        </is>
+      </c>
+      <c r="I57" s="74" t="inlineStr">
+        <is>
+          <t>Have learners solve/check a one-variable linear equation before a system; code errors as equation-solving, sign, or system-model issues.</t>
+        </is>
+      </c>
+      <c r="J57" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K57" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="32" t="inlineStr">
@@ -22291,13 +22737,29 @@
       </c>
       <c r="G58" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H58" s="74" t="n"/>
-      <c r="I58" s="74" t="n"/>
-      <c r="J58" s="74" t="n"/>
-      <c r="K58" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H58" s="74" t="inlineStr">
+        <is>
+          <t>The mapped systems outcome explicitly includes graphical solutions, which require coordinate plotting and reading intersection points. Algebraic methods may be introduced separately.</t>
+        </is>
+      </c>
+      <c r="I58" s="74" t="inlineStr">
+        <is>
+          <t>Solve a two-line system graphically and algebraically, then compare the intersection with the ordered-pair solution.</t>
+        </is>
+      </c>
+      <c r="J58" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K58" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="32" t="inlineStr">
@@ -22332,13 +22794,29 @@
       </c>
       <c r="G59" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H59" s="74" t="n"/>
-      <c r="I59" s="74" t="n"/>
-      <c r="J59" s="74" t="n"/>
-      <c r="K59" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H59" s="74" t="inlineStr">
+        <is>
+          <t>Linear-function representations supply the line equations and intersection meaning used in graphical systems. This is core to the full multi-representation outcome, though substitution/elimination can be taught separately.</t>
+        </is>
+      </c>
+      <c r="I59" s="74" t="inlineStr">
+        <is>
+          <t>Plot two linear functions, identify their intersection, and substitute the ordered pair into both equations; assess algebra and graph-reading separately.</t>
+        </is>
+      </c>
+      <c r="J59" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted preliminary desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K59" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="32" t="inlineStr">

--- a/curriculum/master-map/Mathematics_Understood_Master_Curriculum_Map_v0.2.xlsx
+++ b/curriculum/master-map/Mathematics_Understood_Master_Curriculum_Map_v0.2.xlsx
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="B14" s="53" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D14" s="60" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="B15" s="53" t="n">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D15" s="60" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="B14" s="30" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B15" s="30" t="n">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D22" s="76" t="inlineStr">
         <is>
-          <t>27 of 268 edges have AI-assisted preliminary desk classifications; 241 remain unreviewed.</t>
+          <t>35 of 268 edges have AI-assisted preliminary desk classifications; 233 remain unreviewed.</t>
         </is>
       </c>
       <c r="E22" s="76" t="inlineStr">
@@ -20043,7 +20043,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="71" t="inlineStr">
         <is>
-          <t>All v0.1 edge types and rationale text are preserved as historical proposals. The first 27 high-leverage foundation/algebra edges have AI-assisted preliminary desk reviews; educator confirmation is pending. All other rows remain UNREVIEWED. A preliminary classification is not a final pedagogical sign-off.</t>
+          <t>All v0.1 edge types and rationale text are preserved as historical proposals. 35 edges have AI-assisted preliminary desk reviews across the current batches; educator confirmation is pending. 233 rows remain UNREVIEWED. A preliminary classification is not a final pedagogical sign-off.</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -22892,13 +22892,29 @@
       </c>
       <c r="G61" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H61" s="74" t="n"/>
-      <c r="I61" s="74" t="n"/>
-      <c r="J61" s="74" t="n"/>
-      <c r="K61" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H61" s="74" t="inlineStr">
+        <is>
+          <t>The polynomial cluster uses powers of the variable and interprets degree/coefficient structure; exponent meaning is part of reading polynomial terms, though a brief exponent refresher can be embedded in the first polynomial lesson.</t>
+        </is>
+      </c>
+      <c r="I61" s="74" t="inlineStr">
+        <is>
+          <t>Ask learners to read and compare x, x², and 3x² + 2x; check whether they can explain the exponent/degree meaning and carry out products without an exponent-law prerequisite gap.</t>
+        </is>
+      </c>
+      <c r="J61" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K61" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="32" t="inlineStr">
@@ -22974,13 +22990,29 @@
       </c>
       <c r="G63" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H63" s="74" t="n"/>
-      <c r="I63" s="74" t="n"/>
-      <c r="J63" s="74" t="n"/>
-      <c r="K63" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H63" s="74" t="inlineStr">
+        <is>
+          <t>Integer factors and common multiples can support factor intuition, but polynomial factorization is not simply prime factorization. Treat FND-007 as a source of examples, not a gate to learning algebraic identities.</t>
+        </is>
+      </c>
+      <c r="I63" s="74" t="inlineStr">
+        <is>
+          <t>Test factoring simple polynomials such as x² + 5x + 6 and x² - 9 after teaching polynomial structure; compare performance with a separate numerical-factor diagnostic to see what actually blocks progress.</t>
+        </is>
+      </c>
+      <c r="J63" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K63" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="32" t="inlineStr">
@@ -23220,13 +23252,29 @@
       </c>
       <c r="G69" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H69" s="74" t="n"/>
-      <c r="I69" s="74" t="n"/>
-      <c r="J69" s="74" t="n"/>
-      <c r="K69" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H69" s="74" t="inlineStr">
+        <is>
+          <t>Rational expressions are quotients of expressions/polynomials and can be introduced without prior fluency with powers and integer exponents. Powers are useful for later rational-expression examples but not for the basic fraction/domain idea.</t>
+        </is>
+      </c>
+      <c r="I69" s="74" t="inlineStr">
+        <is>
+          <t>Assess simplification and excluded-value reasoning on (x² - 1)/(x - 1) and simple linear quotients before using exponent-heavy examples; insert an exponent refresher only when required.</t>
+        </is>
+      </c>
+      <c r="J69" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K69" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="32" t="inlineStr">
@@ -23261,13 +23309,29 @@
       </c>
       <c r="G70" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H70" s="74" t="n"/>
-      <c r="I70" s="74" t="n"/>
-      <c r="J70" s="74" t="n"/>
-      <c r="K70" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H70" s="74" t="inlineStr">
+        <is>
+          <t>The radicals/rational-exponents cluster directly relies on the meaning of powers and exponent notation. Real-domain rules and equivalence manipulations build on that base.</t>
+        </is>
+      </c>
+      <c r="I70" s="74" t="inlineStr">
+        <is>
+          <t>Use conversion tasks between square roots and fractional exponents, simplify simple powers, then solve a radical equation and check the result. Distinguish exponent meaning errors from domain errors.</t>
+        </is>
+      </c>
+      <c r="J70" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K70" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="32" t="inlineStr">
@@ -23343,13 +23407,29 @@
       </c>
       <c r="G72" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H72" s="74" t="n"/>
-      <c r="I72" s="74" t="n"/>
-      <c r="J72" s="74" t="n"/>
-      <c r="K72" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H72" s="74" t="inlineStr">
+        <is>
+          <t>For the full radicals/rational-exponents outcome, learners need to reason about real-number domains, intervals, and valid values—especially even roots and constraints introduced by transformations. Teach any missing subskill locally as a bridge.</t>
+        </is>
+      </c>
+      <c r="I72" s="74" t="inlineStr">
+        <is>
+          <t>Give real-domain tasks such as √(x - 2), distinguish domain from output range, and ask which values make a proposed equation meaningful; identify whether interval/number-order reasoning is a genuine blocker.</t>
+        </is>
+      </c>
+      <c r="J72" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K72" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="32" t="inlineStr">
@@ -23425,13 +23505,29 @@
       </c>
       <c r="G74" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H74" s="74" t="n"/>
-      <c r="I74" s="74" t="n"/>
-      <c r="J74" s="74" t="n"/>
-      <c r="K74" s="74" t="n"/>
+          <t>Core required</t>
+        </is>
+      </c>
+      <c r="H74" s="74" t="inlineStr">
+        <is>
+          <t>Integer-exponent meaning underpins exponential functions as repeated multiplicative change and supports the inverse relationship between exponentials and logarithms.</t>
+        </is>
+      </c>
+      <c r="I74" s="74" t="inlineStr">
+        <is>
+          <t>Translate repeated percentage growth into an exponential rule, compare it with a linear sequence, and explain the role of the exponent; check this before teaching logarithms as the inverse operation.</t>
+        </is>
+      </c>
+      <c r="J74" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K74" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="32" t="inlineStr">
@@ -23507,13 +23603,29 @@
       </c>
       <c r="G76" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H76" s="74" t="n"/>
-      <c r="I76" s="74" t="n"/>
-      <c r="J76" s="74" t="n"/>
-      <c r="K76" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H76" s="74" t="inlineStr">
+        <is>
+          <t>Real-number order and interval notation help state domains/ranges and logarithm constraints, but the essential positive-input restriction for logarithms can be taught explicitly in ALG-017. The whole FND-016 cluster is broader than the minimum needed.</t>
+        </is>
+      </c>
+      <c r="I76" s="74" t="inlineStr">
+        <is>
+          <t>Teach log input restrictions locally, then test domain/range statements and interval notation separately. If learners understand positive inputs but struggle only with notation, treat FND-016 as a repair path rather than a hard gate.</t>
+        </is>
+      </c>
+      <c r="J76" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K76" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="32" t="inlineStr">
@@ -23589,13 +23701,29 @@
       </c>
       <c r="G78" s="74" t="inlineStr">
         <is>
-          <t>UNREVIEWED</t>
-        </is>
-      </c>
-      <c r="H78" s="74" t="n"/>
-      <c r="I78" s="74" t="n"/>
-      <c r="J78" s="74" t="n"/>
-      <c r="K78" s="74" t="n"/>
+          <t>Helpful</t>
+        </is>
+      </c>
+      <c r="H78" s="74" t="inlineStr">
+        <is>
+          <t>Sequences and patterns can be introduced through finite lists, tables, and recursive rules before exponent fluency. Powers are useful for geometric sequences and exponential patterns but not for every sequence.</t>
+        </is>
+      </c>
+      <c r="I78" s="74" t="inlineStr">
+        <is>
+          <t>Assess arithmetic and recursive sequence rules without exponents first, then geometric sequences with powers. Separate the objectives and only require FND-014 for the latter.</t>
+        </is>
+      </c>
+      <c r="J78" s="74" t="inlineStr">
+        <is>
+          <t>AI-assisted desk review; educator confirmation pending</t>
+        </is>
+      </c>
+      <c r="K78" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="32" t="inlineStr">

--- a/curriculum/master-map/Mathematics_Understood_Master_Curriculum_Map_v0.2.xlsx
+++ b/curriculum/master-map/Mathematics_Understood_Master_Curriculum_Map_v0.2.xlsx
@@ -173,20 +173,20 @@
     <border/>
     <border/>
     <border>
-      <bottom style="medium">
-        <color rgb="000F6B78"/>
+      <bottom style="thin">
+        <color rgb="00D9E1F2"/>
       </bottom>
     </border>
     <border>
-      <bottom style="thin">
-        <color rgb="00D9E1F2"/>
+      <bottom style="medium">
+        <color rgb="000F6B78"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -337,6 +337,9 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -346,28 +349,28 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1167,7 +1170,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="60" t="inlineStr">
         <is>
@@ -1286,7 +1289,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="70" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>MASTER CURRICULUM MAP v0.2 — AUDIT &amp; REVIEW QUEUE</t>
         </is>
@@ -1299,7 +1302,7 @@
       <c r="G1" s="1" t="n"/>
     </row>
     <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>Automated structural audit completed 2026-10-19. Structural checks do not prove that every prerequisite is pedagogically necessary. Expert review and learner testing remain required.</t>
         </is>
@@ -1312,17 +1315,17 @@
       <c r="G2" s="1" t="n"/>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="73" t="inlineStr">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>Structural check</t>
         </is>
       </c>
-      <c r="B4" s="73" t="inlineStr">
+      <c r="B4" s="74" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C4" s="73" t="inlineStr">
+      <c r="C4" s="74" t="inlineStr">
         <is>
           <t>Interpretation / limit</t>
         </is>
@@ -1534,7 +1537,7 @@
         </is>
       </c>
       <c r="B18" s="30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
@@ -1543,7 +1546,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="75" t="inlineStr">
+      <c r="A19" s="76" t="inlineStr">
         <is>
           <t>PRIORITIZED HUMAN-REVIEW QUEUE</t>
         </is>
@@ -1556,407 +1559,407 @@
       <c r="G19" s="1" t="n"/>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="73" t="inlineStr">
+      <c r="A20" s="74" t="inlineStr">
         <is>
           <t>Queue ID</t>
         </is>
       </c>
-      <c r="B20" s="73" t="inlineStr">
+      <c r="B20" s="74" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C20" s="73" t="inlineStr">
+      <c r="C20" s="74" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="D20" s="73" t="inlineStr">
+      <c r="D20" s="74" t="inlineStr">
         <is>
           <t>Finding / question</t>
         </is>
       </c>
-      <c r="E20" s="73" t="inlineStr">
+      <c r="E20" s="74" t="inlineStr">
         <is>
           <t>Action required</t>
         </is>
       </c>
-      <c r="F20" s="73" t="inlineStr">
+      <c r="F20" s="74" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G20" s="73" t="inlineStr">
+      <c r="G20" s="74" t="inlineStr">
         <is>
           <t>Evidence required to close</t>
         </is>
       </c>
     </row>
     <row r="21" ht="64" customHeight="1">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="77" t="inlineStr">
         <is>
           <t>RQ-001</t>
         </is>
       </c>
-      <c r="B21" s="77" t="inlineStr">
+      <c r="B21" s="78" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C21" s="76" t="inlineStr">
+      <c r="C21" s="77" t="inlineStr">
         <is>
           <t>Data integrity</t>
         </is>
       </c>
-      <c r="D21" s="76" t="inlineStr">
+      <c r="D21" s="77" t="inlineStr">
         <is>
           <t>FND-001 field placement was inspected against the source; representation notes are already in the correct column.</t>
         </is>
       </c>
-      <c r="E21" s="76" t="inlineStr">
+      <c r="E21" s="77" t="inlineStr">
         <is>
           <t>Preserve the correct source data and keep a regression check that the prerequisite column contains concept IDs only.</t>
         </is>
       </c>
-      <c r="F21" s="78" t="inlineStr">
+      <c r="F21" s="79" t="inlineStr">
         <is>
           <t>Resolved — verified</t>
         </is>
       </c>
-      <c r="G21" s="76" t="inlineStr">
+      <c r="G21" s="77" t="inlineStr">
         <is>
           <t>Cell-level check confirms the prerequisite cell is empty and the representation column contains the notes.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="64" customHeight="1">
-      <c r="A22" s="76" t="inlineStr">
+      <c r="A22" s="77" t="inlineStr">
         <is>
           <t>RQ-002</t>
         </is>
       </c>
-      <c r="B22" s="79" t="inlineStr">
+      <c r="B22" s="80" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C22" s="76" t="inlineStr">
+      <c r="C22" s="77" t="inlineStr">
         <is>
           <t>Dependency semantics</t>
         </is>
       </c>
-      <c r="D22" s="76" t="inlineStr">
+      <c r="D22" s="77" t="inlineStr">
         <is>
           <t>35 of 268 edges have AI-assisted preliminary desk classifications; 233 remain unreviewed.</t>
         </is>
       </c>
-      <c r="E22" s="76" t="inlineStr">
+      <c r="E22" s="77" t="inlineStr">
         <is>
           <t>Continue reviewing in focused tranches. Treat prefilled classifications as draft hypotheses until a mathematics educator checks them and learner diagnostics/transfer tasks support the intended pathway.</t>
         </is>
       </c>
-      <c r="F22" s="80" t="inlineStr">
+      <c r="F22" s="81" t="inlineStr">
         <is>
           <t>Working</t>
         </is>
       </c>
-      <c r="G22" s="76" t="inlineStr">
+      <c r="G22" s="77" t="inlineStr">
         <is>
           <t>Each edge has an explicit classification, specific mechanism, proposed validation check, reviewer, and date; educator sign-off is distinguished from AI-assisted desk review.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="64" customHeight="1">
-      <c r="A23" s="76" t="inlineStr">
+      <c r="A23" s="77" t="inlineStr">
         <is>
           <t>RQ-003</t>
         </is>
       </c>
-      <c r="B23" s="79" t="inlineStr">
+      <c r="B23" s="80" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C23" s="76" t="inlineStr">
+      <c r="C23" s="77" t="inlineStr">
         <is>
           <t>Stage placement</t>
         </is>
       </c>
-      <c r="D23" s="76" t="inlineStr">
+      <c r="D23" s="77" t="inlineStr">
         <is>
           <t>CA-001, Complex numbers and geometric representation, is assigned to 6 — Advanced theory; listed prerequisites: FND-016;FND-014;ALG-004;GEO-006.</t>
         </is>
       </c>
-      <c r="E23" s="76" t="inlineStr">
+      <c r="E23" s="77" t="inlineStr">
         <is>
           <t>Decide whether introductory complex numbers belong earlier or should be split from advanced complex analysis. Update prerequisites, visuals, and cross-references together.</t>
         </is>
       </c>
-      <c r="F23" s="80" t="inlineStr">
+      <c r="F23" s="81" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G23" s="76" t="inlineStr">
+      <c r="G23" s="77" t="inlineStr">
         <is>
           <t>A dated decision documents alternatives, prerequisite effects, and reviewer rationale.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="64" customHeight="1">
-      <c r="A24" s="76" t="inlineStr">
+      <c r="A24" s="77" t="inlineStr">
         <is>
           <t>RQ-004</t>
         </is>
       </c>
-      <c r="B24" s="79" t="inlineStr">
+      <c r="B24" s="80" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C24" s="76" t="inlineStr">
+      <c r="C24" s="77" t="inlineStr">
         <is>
           <t>Prerequisite graph</t>
         </is>
       </c>
-      <c r="D24" s="76" t="inlineStr">
+      <c r="D24" s="77" t="inlineStr">
         <is>
           <t>No cycles, duplicate edges, or invalid endpoints were found, but consistency does not prove that each edge is necessary.</t>
         </is>
       </c>
-      <c r="E24" s="76" t="inlineStr">
+      <c r="E24" s="77" t="inlineStr">
         <is>
           <t>Prioritize foundational-to-algebra links and edges that cross learning stages; distinguish necessary prerequisites from helpful material and repair routes.</t>
         </is>
       </c>
-      <c r="F24" s="80" t="inlineStr">
+      <c r="F24" s="81" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G24" s="76" t="inlineStr">
+      <c r="G24" s="77" t="inlineStr">
         <is>
           <t>Documented review protocol and edge-level judgments with specific reasons.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="64" customHeight="1">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="77" t="inlineStr">
         <is>
           <t>RQ-005</t>
         </is>
       </c>
-      <c r="B25" s="79" t="inlineStr">
+      <c r="B25" s="80" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C25" s="76" t="inlineStr">
+      <c r="C25" s="77" t="inlineStr">
         <is>
           <t>Pilot learning design</t>
         </is>
       </c>
-      <c r="D25" s="76" t="inlineStr">
+      <c r="D25" s="77" t="inlineStr">
         <is>
           <t>Problem-first learning, CEM, MDP, and visual independence are design commitments, not yet validated for this series.</t>
         </is>
       </c>
-      <c r="E25" s="76" t="inlineStr">
+      <c r="E25" s="77" t="inlineStr">
         <is>
           <t>Build and test the fractions/ratios pilot and the electrostatic interaction/dipole pilot; include independent transfer tasks and delayed follow-up where feasible.</t>
         </is>
       </c>
-      <c r="F25" s="80" t="inlineStr">
+      <c r="F25" s="81" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G25" s="76" t="inlineStr">
+      <c r="G25" s="77" t="inlineStr">
         <is>
           <t>Recorded learner observations, transfer checks, limitations, and resulting revisions.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="64" customHeight="1">
-      <c r="A26" s="76" t="inlineStr">
+      <c r="A26" s="77" t="inlineStr">
         <is>
           <t>RQ-006</t>
         </is>
       </c>
-      <c r="B26" s="80" t="inlineStr">
+      <c r="B26" s="81" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C26" s="76" t="inlineStr">
+      <c r="C26" s="77" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="D26" s="76" t="inlineStr">
+      <c r="D26" s="77" t="inlineStr">
         <is>
           <t>The 103 concept clusters are an architectural map, not proof that all topics are covered at the right depth.</t>
         </is>
       </c>
-      <c r="E26" s="76" t="inlineStr">
+      <c r="E26" s="77" t="inlineStr">
         <is>
           <t>Review core, optional, and specialist coverage with mathematics educators; identify missing clusters and alternative entry routes.</t>
         </is>
       </c>
-      <c r="F26" s="80" t="inlineStr">
+      <c r="F26" s="81" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G26" s="76" t="inlineStr">
+      <c r="G26" s="77" t="inlineStr">
         <is>
           <t>Coverage matrix with explicit inclusion decisions and rationale.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="64" customHeight="1">
-      <c r="A27" s="76" t="inlineStr">
+      <c r="A27" s="77" t="inlineStr">
         <is>
           <t>RQ-007</t>
         </is>
       </c>
-      <c r="B27" s="80" t="inlineStr">
+      <c r="B27" s="81" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C27" s="76" t="inlineStr">
+      <c r="C27" s="77" t="inlineStr">
         <is>
           <t>Science links</t>
         </is>
       </c>
-      <c r="D27" s="76" t="inlineStr">
+      <c r="D27" s="77" t="inlineStr">
         <is>
           <t>13 science application rows resolve to current concepts, but science validity has not been fully audited.</t>
         </is>
       </c>
-      <c r="E27" s="76" t="inlineStr">
+      <c r="E27" s="77" t="inlineStr">
         <is>
           <t>Check units, dimensions, domains, model assumptions, empirical-vs-mathematical claims, and approximation limits.</t>
         </is>
       </c>
-      <c r="F27" s="80" t="inlineStr">
+      <c r="F27" s="81" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G27" s="76" t="inlineStr">
+      <c r="G27" s="77" t="inlineStr">
         <is>
           <t>Each application has a qualified review or traceable source plus model boundaries.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="64" customHeight="1">
-      <c r="A28" s="76" t="inlineStr">
+      <c r="A28" s="77" t="inlineStr">
         <is>
           <t>RQ-008</t>
         </is>
       </c>
-      <c r="B28" s="80" t="inlineStr">
+      <c r="B28" s="81" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C28" s="76" t="inlineStr">
+      <c r="C28" s="77" t="inlineStr">
         <is>
           <t>Notation/accessibility</t>
         </is>
       </c>
-      <c r="D28" s="76" t="inlineStr">
+      <c r="D28" s="77" t="inlineStr">
         <is>
           <t>Notation choices remain open, and visual assets need accessible descriptions and non-imagery-dependent routes.</t>
         </is>
       </c>
-      <c r="E28" s="76" t="inlineStr">
+      <c r="E28" s="77" t="inlineStr">
         <is>
           <t>Create a notation guide and figure QA checklist for labels, scales, alt text, print legibility, and alternatives.</t>
         </is>
       </c>
-      <c r="F28" s="80" t="inlineStr">
+      <c r="F28" s="81" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G28" s="76" t="inlineStr">
+      <c r="G28" s="77" t="inlineStr">
         <is>
           <t>Notation and accessibility checks applied to both pilot chapters.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="64" customHeight="1">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="77" t="inlineStr">
         <is>
           <t>RQ-009</t>
         </is>
       </c>
-      <c r="B29" s="80" t="inlineStr">
+      <c r="B29" s="81" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C29" s="76" t="inlineStr">
+      <c r="C29" s="77" t="inlineStr">
         <is>
           <t>Stages vs volumes</t>
         </is>
       </c>
-      <c r="D29" s="76" t="inlineStr">
+      <c r="D29" s="77" t="inlineStr">
         <is>
           <t>The workbook correctly says stages are dependency bands, not final book boundaries.</t>
         </is>
       </c>
-      <c r="E29" s="76" t="inlineStr">
+      <c r="E29" s="77" t="inlineStr">
         <is>
           <t>Keep volume count and boundaries provisional until dependency review and pilot-reader navigation are complete.</t>
         </is>
       </c>
-      <c r="F29" s="80" t="inlineStr">
+      <c r="F29" s="81" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G29" s="76" t="inlineStr">
+      <c r="G29" s="77" t="inlineStr">
         <is>
           <t>Boundaries follow reviewed prerequisite clusters and tested learner navigation.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="64" customHeight="1">
-      <c r="A30" s="76" t="inlineStr">
+      <c r="A30" s="77" t="inlineStr">
         <is>
           <t>RQ-010</t>
         </is>
       </c>
-      <c r="B30" s="80" t="inlineStr">
+      <c r="B30" s="81" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C30" s="76" t="inlineStr">
+      <c r="C30" s="77" t="inlineStr">
         <is>
           <t>Claim/source verification</t>
         </is>
       </c>
-      <c r="D30" s="76" t="inlineStr">
+      <c r="D30" s="77" t="inlineStr">
         <is>
           <t>QA reminders exist, but chapter work needs a practical claim/source ledger.</t>
         </is>
       </c>
-      <c r="E30" s="76" t="inlineStr">
+      <c r="E30" s="77" t="inlineStr">
         <is>
           <t>Track significant claims, assumptions, derivations/sources, independent checks, status, limitations, and reviewer.</t>
         </is>
       </c>
-      <c r="F30" s="80" t="inlineStr">
+      <c r="F30" s="81" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G30" s="76" t="inlineStr">
+      <c r="G30" s="77" t="inlineStr">
         <is>
           <t>High-severity claims are traceable and independently checked before release.</t>
         </is>
@@ -19539,7 +19542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19981,6 +19984,43 @@
       <c r="G14" s="32" t="inlineStr">
         <is>
           <t>During advanced route design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="72" customHeight="1">
+      <c r="A15" s="70" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="B15" s="70" t="inlineStr">
+        <is>
+          <t>Complex-number scope and stage split</t>
+        </is>
+      </c>
+      <c r="C15" s="70" t="inlineStr">
+        <is>
+          <t>Elementary algebraic complex numbers, polar/geometric representation, and complex analysis use different prerequisite sets; one combined cluster may delay introductory content or force trigonometry too early.</t>
+        </is>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>Open proposal: re-scope CA-001 as algebraic complex numbers in Stage 1; create CA-003 for complex plane/polar/geometric representation in Stage 2; keep CA-002 complex analysis in Stage 6.</t>
+        </is>
+      </c>
+      <c r="E15" s="70" t="inlineStr">
+        <is>
+          <t>Review OpenStax's elementary/polar-form sequencing, check the full dependency graph, and obtain mathematics-educator feedback before implementing the split.</t>
+        </is>
+      </c>
+      <c r="F15" s="70" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G15" s="70" t="inlineStr">
+        <is>
+          <t>Before producing a new workbook version or drafting the complex-number chapters.</t>
         </is>
       </c>
     </row>
@@ -20024,7 +20064,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="70" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>DEPENDENCY REVIEW — Evidence and Classification Ledger</t>
         </is>
@@ -20041,7 +20081,7 @@
       <c r="K1" s="1" t="n"/>
     </row>
     <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>All v0.1 edge types and rationale text are preserved as historical proposals. 35 edges have AI-assisted preliminary desk reviews across the current batches; educator confirmation is pending. 233 rows remain UNREVIEWED. A preliminary classification is not a final pedagogical sign-off.</t>
         </is>
@@ -20058,7 +20098,7 @@
       <c r="K2" s="1" t="n"/>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="72" t="inlineStr">
+      <c r="A3" s="73" t="inlineStr">
         <is>
           <t>Review rule: a valid graph is not necessarily a valid curriculum. State the specific learning mechanism and a check/test; do not treat topic order or an LLM suggestion alone as evidence.</t>
         </is>
@@ -20075,57 +20115,57 @@
       <c r="K3" s="1" t="n"/>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="73" t="inlineStr">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>Edge ID</t>
         </is>
       </c>
-      <c r="B4" s="73" t="inlineStr">
+      <c r="B4" s="74" t="inlineStr">
         <is>
           <t>Prerequisite concept ID</t>
         </is>
       </c>
-      <c r="C4" s="73" t="inlineStr">
+      <c r="C4" s="74" t="inlineStr">
         <is>
           <t>Dependent concept ID</t>
         </is>
       </c>
-      <c r="D4" s="73" t="inlineStr">
+      <c r="D4" s="74" t="inlineStr">
         <is>
           <t>v0.1 proposed edge type (unverified)</t>
         </is>
       </c>
-      <c r="E4" s="73" t="inlineStr">
+      <c r="E4" s="74" t="inlineStr">
         <is>
           <t>v0.1 rationale text (template; not evidence)</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>v0.1 status</t>
         </is>
       </c>
-      <c r="G4" s="73" t="inlineStr">
+      <c r="G4" s="74" t="inlineStr">
         <is>
           <t>v0.2 review classification</t>
         </is>
       </c>
-      <c r="H4" s="73" t="inlineStr">
+      <c r="H4" s="74" t="inlineStr">
         <is>
           <t>Specific dependency mechanism / evidence</t>
         </is>
       </c>
-      <c r="I4" s="73" t="inlineStr">
+      <c r="I4" s="74" t="inlineStr">
         <is>
           <t>Proposed validation check / test</t>
         </is>
       </c>
-      <c r="J4" s="73" t="inlineStr">
+      <c r="J4" s="74" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="K4" s="73" t="inlineStr">
+      <c r="K4" s="74" t="inlineStr">
         <is>
           <t>Review date</t>
         </is>
@@ -20162,15 +20202,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G5" s="74" t="inlineStr">
+      <c r="G5" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H5" s="74" t="n"/>
-      <c r="I5" s="74" t="n"/>
-      <c r="J5" s="74" t="n"/>
-      <c r="K5" s="74" t="n"/>
+      <c r="H5" s="75" t="n"/>
+      <c r="I5" s="75" t="n"/>
+      <c r="J5" s="75" t="n"/>
+      <c r="K5" s="75" t="n"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="32" t="inlineStr">
@@ -20203,15 +20243,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G6" s="74" t="inlineStr">
+      <c r="G6" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H6" s="74" t="n"/>
-      <c r="I6" s="74" t="n"/>
-      <c r="J6" s="74" t="n"/>
-      <c r="K6" s="74" t="n"/>
+      <c r="H6" s="75" t="n"/>
+      <c r="I6" s="75" t="n"/>
+      <c r="J6" s="75" t="n"/>
+      <c r="K6" s="75" t="n"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="32" t="inlineStr">
@@ -20244,15 +20284,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G7" s="74" t="inlineStr">
+      <c r="G7" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H7" s="74" t="n"/>
-      <c r="I7" s="74" t="n"/>
-      <c r="J7" s="74" t="n"/>
-      <c r="K7" s="74" t="n"/>
+      <c r="H7" s="75" t="n"/>
+      <c r="I7" s="75" t="n"/>
+      <c r="J7" s="75" t="n"/>
+      <c r="K7" s="75" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="32" t="inlineStr">
@@ -20285,15 +20325,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G8" s="74" t="inlineStr">
+      <c r="G8" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H8" s="74" t="n"/>
-      <c r="I8" s="74" t="n"/>
-      <c r="J8" s="74" t="n"/>
-      <c r="K8" s="74" t="n"/>
+      <c r="H8" s="75" t="n"/>
+      <c r="I8" s="75" t="n"/>
+      <c r="J8" s="75" t="n"/>
+      <c r="K8" s="75" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="32" t="inlineStr">
@@ -20326,15 +20366,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G9" s="74" t="inlineStr">
+      <c r="G9" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H9" s="74" t="n"/>
-      <c r="I9" s="74" t="n"/>
-      <c r="J9" s="74" t="n"/>
-      <c r="K9" s="74" t="n"/>
+      <c r="H9" s="75" t="n"/>
+      <c r="I9" s="75" t="n"/>
+      <c r="J9" s="75" t="n"/>
+      <c r="K9" s="75" t="n"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="32" t="inlineStr">
@@ -20367,15 +20407,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G10" s="74" t="inlineStr">
+      <c r="G10" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H10" s="74" t="n"/>
-      <c r="I10" s="74" t="n"/>
-      <c r="J10" s="74" t="n"/>
-      <c r="K10" s="74" t="n"/>
+      <c r="H10" s="75" t="n"/>
+      <c r="I10" s="75" t="n"/>
+      <c r="J10" s="75" t="n"/>
+      <c r="K10" s="75" t="n"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="32" t="inlineStr">
@@ -20408,15 +20448,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G11" s="74" t="inlineStr">
+      <c r="G11" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H11" s="74" t="n"/>
-      <c r="I11" s="74" t="n"/>
-      <c r="J11" s="74" t="n"/>
-      <c r="K11" s="74" t="n"/>
+      <c r="H11" s="75" t="n"/>
+      <c r="I11" s="75" t="n"/>
+      <c r="J11" s="75" t="n"/>
+      <c r="K11" s="75" t="n"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="32" t="inlineStr">
@@ -20449,15 +20489,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G12" s="74" t="inlineStr">
+      <c r="G12" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H12" s="74" t="n"/>
-      <c r="I12" s="74" t="n"/>
-      <c r="J12" s="74" t="n"/>
-      <c r="K12" s="74" t="n"/>
+      <c r="H12" s="75" t="n"/>
+      <c r="I12" s="75" t="n"/>
+      <c r="J12" s="75" t="n"/>
+      <c r="K12" s="75" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="32" t="inlineStr">
@@ -20490,15 +20530,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G13" s="74" t="inlineStr">
+      <c r="G13" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H13" s="74" t="n"/>
-      <c r="I13" s="74" t="n"/>
-      <c r="J13" s="74" t="n"/>
-      <c r="K13" s="74" t="n"/>
+      <c r="H13" s="75" t="n"/>
+      <c r="I13" s="75" t="n"/>
+      <c r="J13" s="75" t="n"/>
+      <c r="K13" s="75" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="32" t="inlineStr">
@@ -20531,15 +20571,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G14" s="74" t="inlineStr">
+      <c r="G14" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H14" s="74" t="n"/>
-      <c r="I14" s="74" t="n"/>
-      <c r="J14" s="74" t="n"/>
-      <c r="K14" s="74" t="n"/>
+      <c r="H14" s="75" t="n"/>
+      <c r="I14" s="75" t="n"/>
+      <c r="J14" s="75" t="n"/>
+      <c r="K14" s="75" t="n"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="32" t="inlineStr">
@@ -20572,15 +20612,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G15" s="74" t="inlineStr">
+      <c r="G15" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H15" s="74" t="n"/>
-      <c r="I15" s="74" t="n"/>
-      <c r="J15" s="74" t="n"/>
-      <c r="K15" s="74" t="n"/>
+      <c r="H15" s="75" t="n"/>
+      <c r="I15" s="75" t="n"/>
+      <c r="J15" s="75" t="n"/>
+      <c r="K15" s="75" t="n"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="32" t="inlineStr">
@@ -20613,15 +20653,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G16" s="74" t="inlineStr">
+      <c r="G16" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H16" s="74" t="n"/>
-      <c r="I16" s="74" t="n"/>
-      <c r="J16" s="74" t="n"/>
-      <c r="K16" s="74" t="n"/>
+      <c r="H16" s="75" t="n"/>
+      <c r="I16" s="75" t="n"/>
+      <c r="J16" s="75" t="n"/>
+      <c r="K16" s="75" t="n"/>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="32" t="inlineStr">
@@ -20654,15 +20694,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G17" s="74" t="inlineStr">
+      <c r="G17" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H17" s="74" t="n"/>
-      <c r="I17" s="74" t="n"/>
-      <c r="J17" s="74" t="n"/>
-      <c r="K17" s="74" t="n"/>
+      <c r="H17" s="75" t="n"/>
+      <c r="I17" s="75" t="n"/>
+      <c r="J17" s="75" t="n"/>
+      <c r="K17" s="75" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="32" t="inlineStr">
@@ -20695,15 +20735,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G18" s="74" t="inlineStr">
+      <c r="G18" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H18" s="74" t="n"/>
-      <c r="I18" s="74" t="n"/>
-      <c r="J18" s="74" t="n"/>
-      <c r="K18" s="74" t="n"/>
+      <c r="H18" s="75" t="n"/>
+      <c r="I18" s="75" t="n"/>
+      <c r="J18" s="75" t="n"/>
+      <c r="K18" s="75" t="n"/>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="32" t="inlineStr">
@@ -20736,15 +20776,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G19" s="74" t="inlineStr">
+      <c r="G19" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H19" s="74" t="n"/>
-      <c r="I19" s="74" t="n"/>
-      <c r="J19" s="74" t="n"/>
-      <c r="K19" s="74" t="n"/>
+      <c r="H19" s="75" t="n"/>
+      <c r="I19" s="75" t="n"/>
+      <c r="J19" s="75" t="n"/>
+      <c r="K19" s="75" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="32" t="inlineStr">
@@ -20777,15 +20817,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G20" s="74" t="inlineStr">
+      <c r="G20" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H20" s="74" t="n"/>
-      <c r="I20" s="74" t="n"/>
-      <c r="J20" s="74" t="n"/>
-      <c r="K20" s="74" t="n"/>
+      <c r="H20" s="75" t="n"/>
+      <c r="I20" s="75" t="n"/>
+      <c r="J20" s="75" t="n"/>
+      <c r="K20" s="75" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="32" t="inlineStr">
@@ -20818,15 +20858,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G21" s="74" t="inlineStr">
+      <c r="G21" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H21" s="74" t="n"/>
-      <c r="I21" s="74" t="n"/>
-      <c r="J21" s="74" t="n"/>
-      <c r="K21" s="74" t="n"/>
+      <c r="H21" s="75" t="n"/>
+      <c r="I21" s="75" t="n"/>
+      <c r="J21" s="75" t="n"/>
+      <c r="K21" s="75" t="n"/>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="32" t="inlineStr">
@@ -20859,15 +20899,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G22" s="74" t="inlineStr">
+      <c r="G22" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H22" s="74" t="n"/>
-      <c r="I22" s="74" t="n"/>
-      <c r="J22" s="74" t="n"/>
-      <c r="K22" s="74" t="n"/>
+      <c r="H22" s="75" t="n"/>
+      <c r="I22" s="75" t="n"/>
+      <c r="J22" s="75" t="n"/>
+      <c r="K22" s="75" t="n"/>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="32" t="inlineStr">
@@ -20900,15 +20940,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G23" s="74" t="inlineStr">
+      <c r="G23" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H23" s="74" t="n"/>
-      <c r="I23" s="74" t="n"/>
-      <c r="J23" s="74" t="n"/>
-      <c r="K23" s="74" t="n"/>
+      <c r="H23" s="75" t="n"/>
+      <c r="I23" s="75" t="n"/>
+      <c r="J23" s="75" t="n"/>
+      <c r="K23" s="75" t="n"/>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="32" t="inlineStr">
@@ -20941,15 +20981,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G24" s="74" t="inlineStr">
+      <c r="G24" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H24" s="74" t="n"/>
-      <c r="I24" s="74" t="n"/>
-      <c r="J24" s="74" t="n"/>
-      <c r="K24" s="74" t="n"/>
+      <c r="H24" s="75" t="n"/>
+      <c r="I24" s="75" t="n"/>
+      <c r="J24" s="75" t="n"/>
+      <c r="K24" s="75" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="32" t="inlineStr">
@@ -20982,15 +21022,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G25" s="74" t="inlineStr">
+      <c r="G25" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H25" s="74" t="n"/>
-      <c r="I25" s="74" t="n"/>
-      <c r="J25" s="74" t="n"/>
-      <c r="K25" s="74" t="n"/>
+      <c r="H25" s="75" t="n"/>
+      <c r="I25" s="75" t="n"/>
+      <c r="J25" s="75" t="n"/>
+      <c r="K25" s="75" t="n"/>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="32" t="inlineStr">
@@ -21023,15 +21063,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G26" s="74" t="inlineStr">
+      <c r="G26" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H26" s="74" t="n"/>
-      <c r="I26" s="74" t="n"/>
-      <c r="J26" s="74" t="n"/>
-      <c r="K26" s="74" t="n"/>
+      <c r="H26" s="75" t="n"/>
+      <c r="I26" s="75" t="n"/>
+      <c r="J26" s="75" t="n"/>
+      <c r="K26" s="75" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="32" t="inlineStr">
@@ -21064,15 +21104,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G27" s="74" t="inlineStr">
+      <c r="G27" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H27" s="74" t="n"/>
-      <c r="I27" s="74" t="n"/>
-      <c r="J27" s="74" t="n"/>
-      <c r="K27" s="74" t="n"/>
+      <c r="H27" s="75" t="n"/>
+      <c r="I27" s="75" t="n"/>
+      <c r="J27" s="75" t="n"/>
+      <c r="K27" s="75" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="32" t="inlineStr">
@@ -21105,15 +21145,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G28" s="74" t="inlineStr">
+      <c r="G28" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H28" s="74" t="n"/>
-      <c r="I28" s="74" t="n"/>
-      <c r="J28" s="74" t="n"/>
-      <c r="K28" s="74" t="n"/>
+      <c r="H28" s="75" t="n"/>
+      <c r="I28" s="75" t="n"/>
+      <c r="J28" s="75" t="n"/>
+      <c r="K28" s="75" t="n"/>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="32" t="inlineStr">
@@ -21146,15 +21186,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G29" s="74" t="inlineStr">
+      <c r="G29" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H29" s="74" t="n"/>
-      <c r="I29" s="74" t="n"/>
-      <c r="J29" s="74" t="n"/>
-      <c r="K29" s="74" t="n"/>
+      <c r="H29" s="75" t="n"/>
+      <c r="I29" s="75" t="n"/>
+      <c r="J29" s="75" t="n"/>
+      <c r="K29" s="75" t="n"/>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="32" t="inlineStr">
@@ -21187,15 +21227,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G30" s="74" t="inlineStr">
+      <c r="G30" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H30" s="74" t="n"/>
-      <c r="I30" s="74" t="n"/>
-      <c r="J30" s="74" t="n"/>
-      <c r="K30" s="74" t="n"/>
+      <c r="H30" s="75" t="n"/>
+      <c r="I30" s="75" t="n"/>
+      <c r="J30" s="75" t="n"/>
+      <c r="K30" s="75" t="n"/>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="32" t="inlineStr">
@@ -21228,15 +21268,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G31" s="74" t="inlineStr">
+      <c r="G31" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H31" s="74" t="n"/>
-      <c r="I31" s="74" t="n"/>
-      <c r="J31" s="74" t="n"/>
-      <c r="K31" s="74" t="n"/>
+      <c r="H31" s="75" t="n"/>
+      <c r="I31" s="75" t="n"/>
+      <c r="J31" s="75" t="n"/>
+      <c r="K31" s="75" t="n"/>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="32" t="inlineStr">
@@ -21269,15 +21309,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G32" s="74" t="inlineStr">
+      <c r="G32" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H32" s="74" t="n"/>
-      <c r="I32" s="74" t="n"/>
-      <c r="J32" s="74" t="n"/>
-      <c r="K32" s="74" t="n"/>
+      <c r="H32" s="75" t="n"/>
+      <c r="I32" s="75" t="n"/>
+      <c r="J32" s="75" t="n"/>
+      <c r="K32" s="75" t="n"/>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="32" t="inlineStr">
@@ -21310,27 +21350,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G33" s="74" t="inlineStr">
+      <c r="G33" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H33" s="74" t="inlineStr">
+      <c r="H33" s="75" t="inlineStr">
         <is>
           <t>Signed-rational arithmetic helps with later examples but is not needed to introduce the roles of variable, unknown, and parameter. Use whole-number contexts first; provide FND-015 as a repair path where calculations—not letter roles—block learning.</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>Teach the letter-role objective with whole-number contexts, then test a separate signed-rational transfer item. If only the second fails, do not treat FND-015 as a gate for ALG-001.</t>
         </is>
       </c>
-      <c r="J33" s="74" t="inlineStr">
+      <c r="J33" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K33" s="74" t="inlineStr">
+      <c r="K33" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21367,27 +21407,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G34" s="74" t="inlineStr">
+      <c r="G34" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H34" s="74" t="inlineStr">
+      <c r="H34" s="75" t="inlineStr">
         <is>
           <t>Minimum symbol/statement literacy supports reading letters and translating between verbal and symbolic forms. For accessible self-study, teach this minimum within an ALG-001 bridge instead of denying entry.</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>Diagnostic: interpret x + 2 and translate 'a number plus 2'; provide a short notation bridge and retest variable/unknown/parameter distinctions.</t>
         </is>
       </c>
-      <c r="J34" s="74" t="inlineStr">
+      <c r="J34" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K34" s="74" t="inlineStr">
+      <c r="K34" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21424,27 +21464,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G35" s="74" t="inlineStr">
+      <c r="G35" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H35" s="74" t="inlineStr">
+      <c r="H35" s="75" t="inlineStr">
         <is>
           <t>The meanings of variables and parameters are needed to interpret symbolic expressions and reason about equivalence; the two concepts may be scaffolded in adjacent lessons.</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>Ask learners to identify the role of a letter and explain why 2x + 3 and 3 + 2x are equivalent; record whether an ALG-001 refresh is enough.</t>
         </is>
       </c>
-      <c r="J35" s="74" t="inlineStr">
+      <c r="J35" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K35" s="74" t="inlineStr">
+      <c r="K35" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21481,27 +21521,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G36" s="74" t="inlineStr">
+      <c r="G36" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H36" s="74" t="inlineStr">
+      <c r="H36" s="75" t="inlineStr">
         <is>
           <t>Numerical operation meanings and basic properties underpin interpretation and simplification of symbolic expressions. This requires operational meaning, not mastery of every arithmetic strand.</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>Move from 3 + 2 and 3 × 2 to 3x + 2x and equivalent forms; distinguish operation-meaning errors from notation errors.</t>
         </is>
       </c>
-      <c r="J36" s="74" t="inlineStr">
+      <c r="J36" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K36" s="74" t="inlineStr">
+      <c r="K36" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21538,27 +21578,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G37" s="74" t="inlineStr">
+      <c r="G37" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H37" s="74" t="inlineStr">
+      <c r="H37" s="75" t="inlineStr">
         <is>
           <t>Exponent notation appears in some expressions, but initial expression meaning/equivalence can be learned without exponent laws. Introduce FND-014 just in time when powers enter.</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>Check the ALG-002 outcomes using expressions without exponents; verify that power laws are not secretly assumed before introducing them explicitly.</t>
         </is>
       </c>
-      <c r="J37" s="74" t="inlineStr">
+      <c r="J37" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K37" s="74" t="inlineStr">
+      <c r="K37" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21595,27 +21635,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G38" s="74" t="inlineStr">
+      <c r="G38" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H38" s="74" t="inlineStr">
+      <c r="H38" s="75" t="inlineStr">
         <is>
           <t>Equations and inequalities relate expressions and constrain possible values, so expression interpretation and equivalence are foundational to the current mapped outcome.</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>Ask learners to interpret x + 2 = 5 and x + 2 &lt; 5, distinguish expression from statement, and test candidate values.</t>
         </is>
       </c>
-      <c r="J38" s="74" t="inlineStr">
+      <c r="J38" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K38" s="74" t="inlineStr">
+      <c r="K38" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21652,27 +21692,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G39" s="74" t="inlineStr">
+      <c r="G39" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H39" s="74" t="inlineStr">
+      <c r="H39" s="75" t="inlineStr">
         <is>
           <t>A signed number line is important for representing solution sets with negative values, but the meaning of an equation or inequality as a statement can be taught earlier. This cluster combines both tasks.</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>Assess separately: identify an equation/inequality as a constraint, then graph a solution set spanning negative and positive values. FND-006 is more essential for the latter.</t>
         </is>
       </c>
-      <c r="J39" s="74" t="inlineStr">
+      <c r="J39" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K39" s="74" t="inlineStr">
+      <c r="K39" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21709,27 +21749,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G40" s="74" t="inlineStr">
+      <c r="G40" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H40" s="74" t="inlineStr">
+      <c r="H40" s="75" t="inlineStr">
         <is>
           <t>Solving equations depends on understanding them as constraints and preserving the solution set under valid transformations.</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>Have learners solve and verify a linear equation, then explain why a valid operation performed on both sides preserves equality.</t>
         </is>
       </c>
-      <c r="J40" s="74" t="inlineStr">
+      <c r="J40" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K40" s="74" t="inlineStr">
+      <c r="K40" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21766,27 +21806,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G41" s="74" t="inlineStr">
+      <c r="G41" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H41" s="74" t="inlineStr">
+      <c r="H41" s="75" t="inlineStr">
         <is>
           <t>Full linear equation/inequality fluency with standard rational coefficients uses signed and rational arithmetic. Integer-only starter examples may precede it, but the complete ALG-004 outcome needs this capability or targeted repair.</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>Use equations with negative/fractional coefficients and sign-sensitive inequalities. Diagnose arithmetic errors separately and provide an FND-015 repair where needed.</t>
         </is>
       </c>
-      <c r="J41" s="74" t="inlineStr">
+      <c r="J41" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K41" s="74" t="inlineStr">
+      <c r="K41" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21823,27 +21863,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G42" s="74" t="inlineStr">
+      <c r="G42" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H42" s="74" t="inlineStr">
+      <c r="H42" s="75" t="inlineStr">
         <is>
           <t>Rearranging literal formulas extends isolating an unknown through reversible equation transformations, the central capability developed in linear equation solving.</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>Rearrange a familiar formula for a different variable, substitute back, and check nonzero-denominator restrictions.</t>
         </is>
       </c>
-      <c r="J42" s="74" t="inlineStr">
+      <c r="J42" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K42" s="74" t="inlineStr">
+      <c r="K42" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21880,27 +21920,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G43" s="74" t="inlineStr">
+      <c r="G43" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H43" s="74" t="inlineStr">
+      <c r="H43" s="75" t="inlineStr">
         <is>
           <t>Formula rearrangement requires learners to interpret and maintain equivalent symbolic expressions even when the target variable changes.</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>Give an equivalent-expression task before rearranging a literal formula; check whether the transformation reasoning transfers.</t>
         </is>
       </c>
-      <c r="J43" s="74" t="inlineStr">
+      <c r="J43" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K43" s="74" t="inlineStr">
+      <c r="K43" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21937,27 +21977,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G44" s="74" t="inlineStr">
+      <c r="G44" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H44" s="74" t="inlineStr">
+      <c r="H44" s="75" t="inlineStr">
         <is>
           <t>Unit conversion and dimensional sense are not prerequisites for symbolic rearrangement itself; they are important for interpreting unit-bearing formulas and scientific applications.</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>Compare a pure-symbol rearrangement with a unit-bearing application; assess algebraic success separately from interpreting and checking units.</t>
         </is>
       </c>
-      <c r="J44" s="74" t="inlineStr">
+      <c r="J44" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K44" s="74" t="inlineStr">
+      <c r="K44" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -21994,27 +22034,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G45" s="74" t="inlineStr">
+      <c r="G45" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H45" s="74" t="inlineStr">
+      <c r="H45" s="75" t="inlineStr">
         <is>
           <t>The coordinate-plane outcome includes signed coordinates and points in all quadrants. Understanding signed values relative to zero is a direct conceptual support and can be bridged locally.</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>Ask learners to order signed values on a number line, then plot ordered pairs in all four quadrants; identify sign and axis errors.</t>
         </is>
       </c>
-      <c r="J45" s="74" t="inlineStr">
+      <c r="J45" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K45" s="74" t="inlineStr">
+      <c r="K45" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22051,27 +22091,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G46" s="74" t="inlineStr">
+      <c r="G46" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H46" s="74" t="inlineStr">
+      <c r="H46" s="75" t="inlineStr">
         <is>
           <t>Basic notation helps with ordered pairs and coordinate labels, but these conventions are teachable inside the coordinate lesson. Do not make the entire FND-001 cluster a rigid gate.</t>
         </is>
       </c>
-      <c r="I46" s="74" t="inlineStr">
+      <c r="I46" s="75" t="inlineStr">
         <is>
           <t>Give a brief ordered-pair/axis primer and test plotting; compare error types before and after the local explanation.</t>
         </is>
       </c>
-      <c r="J46" s="74" t="inlineStr">
+      <c r="J46" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K46" s="74" t="inlineStr">
+      <c r="K46" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22108,27 +22148,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G47" s="74" t="inlineStr">
+      <c r="G47" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H47" s="74" t="inlineStr">
+      <c r="H47" s="75" t="inlineStr">
         <is>
           <t>Graph literacy explicitly requires plotting/interpreting coordinates and relating graphs to tables, equations, and contexts; coordinate-plane fluency is a direct dependency.</t>
         </is>
       </c>
-      <c r="I47" s="74" t="inlineStr">
+      <c r="I47" s="75" t="inlineStr">
         <is>
           <t>Before graph-construction tasks, plot table values with labelled axes and scales; assess coordinate plotting separately from trend interpretation.</t>
         </is>
       </c>
-      <c r="J47" s="74" t="inlineStr">
+      <c r="J47" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K47" s="74" t="inlineStr">
+      <c r="K47" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22165,27 +22205,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G48" s="74" t="inlineStr">
+      <c r="G48" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H48" s="74" t="inlineStr">
+      <c r="H48" s="75" t="inlineStr">
         <is>
           <t>Proportional relationships offer useful graphs through the origin, but graph literacy must cover non-proportional, nonlinear, and empirical graphs too.</t>
         </is>
       </c>
-      <c r="I48" s="74" t="inlineStr">
+      <c r="I48" s="75" t="inlineStr">
         <is>
           <t>Test graph interpretation on non-proportional lines, nonlinear curves, and empirical/categorical data as well as percentage examples.</t>
         </is>
       </c>
-      <c r="J48" s="74" t="inlineStr">
+      <c r="J48" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K48" s="74" t="inlineStr">
+      <c r="K48" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22222,27 +22262,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G49" s="74" t="inlineStr">
+      <c r="G49" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H49" s="74" t="inlineStr">
+      <c r="H49" s="75" t="inlineStr">
         <is>
           <t>The current slope/rate outcome includes graph interpretation and proportional-versus-affine comparison; graph literacy supports axis/scale reading and representation changes.</t>
         </is>
       </c>
-      <c r="I49" s="74" t="inlineStr">
+      <c r="I49" s="75" t="inlineStr">
         <is>
           <t>Infer rate from a graph with nontrivial axis scales, confirm from a table, and separate graph-reading errors from rate-reasoning errors.</t>
         </is>
       </c>
-      <c r="J49" s="74" t="inlineStr">
+      <c r="J49" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K49" s="74" t="inlineStr">
+      <c r="K49" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22279,27 +22319,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G50" s="74" t="inlineStr">
+      <c r="G50" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H50" s="74" t="inlineStr">
+      <c r="H50" s="75" t="inlineStr">
         <is>
           <t>Slope/rate of change is change-per-change; ratios and unit rates supply the conceptual basis for interpreting slope rather than memorizing rise-over-run.</t>
         </is>
       </c>
-      <c r="I50" s="74" t="inlineStr">
+      <c r="I50" s="75" t="inlineStr">
         <is>
           <t>Transfer from a unit-rate context and double number line to a table and graph; explain the ratio and its units.</t>
         </is>
       </c>
-      <c r="J50" s="74" t="inlineStr">
+      <c r="J50" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K50" s="74" t="inlineStr">
+      <c r="K50" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22336,27 +22376,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G51" s="74" t="inlineStr">
+      <c r="G51" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H51" s="74" t="inlineStr">
+      <c r="H51" s="75" t="inlineStr">
         <is>
           <t>Unit/dimensional sense improves interpretation of slope and intercept units, but an initial slope concept can be taught on a unitless graph. The full measurement cluster is broader than the minimum prerequisite.</t>
         </is>
       </c>
-      <c r="I51" s="74" t="inlineStr">
+      <c r="I51" s="75" t="inlineStr">
         <is>
           <t>Assess calculation first and unit interpretation second; teach only the missing unit subskill locally when needed.</t>
         </is>
       </c>
-      <c r="J51" s="74" t="inlineStr">
+      <c r="J51" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K51" s="74" t="inlineStr">
+      <c r="K51" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22393,27 +22433,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G52" s="74" t="inlineStr">
+      <c r="G52" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H52" s="74" t="inlineStr">
+      <c r="H52" s="75" t="inlineStr">
         <is>
           <t>A function can first be introduced through mappings, input-output tables, and uniqueness, without symbolic expressions. Expression skill is needed for formula representations.</t>
         </is>
       </c>
-      <c r="I52" s="74" t="inlineStr">
+      <c r="I52" s="75" t="inlineStr">
         <is>
           <t>Teach a mapping/table example before a formula; assess function recognition separately from interpretation of symbolic rules.</t>
         </is>
       </c>
-      <c r="J52" s="74" t="inlineStr">
+      <c r="J52" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K52" s="74" t="inlineStr">
+      <c r="K52" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22450,27 +22490,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G53" s="74" t="inlineStr">
+      <c r="G53" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H53" s="74" t="inlineStr">
+      <c r="H53" s="75" t="inlineStr">
         <is>
           <t>Coordinates are needed for graphical representations of functions, not for the input-output/mapping definition itself. Multiple representations should provide more than one entry route.</t>
         </is>
       </c>
-      <c r="I53" s="74" t="inlineStr">
+      <c r="I53" s="75" t="inlineStr">
         <is>
           <t>Assess function recognition from mappings and tables before graph tasks; keep graph interpretation as a dependent sub-outcome.</t>
         </is>
       </c>
-      <c r="J53" s="74" t="inlineStr">
+      <c r="J53" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K53" s="74" t="inlineStr">
+      <c r="K53" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22507,27 +22547,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G54" s="74" t="inlineStr">
+      <c r="G54" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H54" s="74" t="inlineStr">
+      <c r="H54" s="75" t="inlineStr">
         <is>
           <t>The mapped linear-function outcome uses slope/rate and the proportional-versus-affine distinction established in ALG-008.</t>
         </is>
       </c>
-      <c r="I54" s="74" t="inlineStr">
+      <c r="I54" s="75" t="inlineStr">
         <is>
           <t>From a table with constant first differences, build a linear rule, identify slope/intercept, and distinguish a line through the origin from one with nonzero intercept.</t>
         </is>
       </c>
-      <c r="J54" s="74" t="inlineStr">
+      <c r="J54" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K54" s="74" t="inlineStr">
+      <c r="K54" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22564,27 +22604,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G55" s="74" t="inlineStr">
+      <c r="G55" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H55" s="74" t="inlineStr">
+      <c r="H55" s="75" t="inlineStr">
         <is>
           <t>In this curriculum, a general function concept supplies input-output, domain, and range language needed to position linear functions as one function family. Motivation with a linear example can still come first.</t>
         </is>
       </c>
-      <c r="I55" s="74" t="inlineStr">
+      <c r="I55" s="75" t="inlineStr">
         <is>
           <t>Compare linear and non-linear functions and a relation that fails uniqueness; check whether learners can explain the special case and its domain.</t>
         </is>
       </c>
-      <c r="J55" s="74" t="inlineStr">
+      <c r="J55" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K55" s="74" t="inlineStr">
+      <c r="K55" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22621,27 +22661,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G56" s="74" t="inlineStr">
+      <c r="G56" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H56" s="74" t="inlineStr">
+      <c r="H56" s="75" t="inlineStr">
         <is>
           <t>Interpreting a linear function as an equation requires minimum fluency with equality as a relation and symbolic statements. Teach that minimum within the linear-function lesson if necessary.</t>
         </is>
       </c>
-      <c r="I56" s="74" t="inlineStr">
+      <c r="I56" s="75" t="inlineStr">
         <is>
           <t>Ask learners to read y = 2x + 3 as a relationship, explain what equality asserts, and interpret slope/intercept; note if a short bridge suffices.</t>
         </is>
       </c>
-      <c r="J56" s="74" t="inlineStr">
+      <c r="J56" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K56" s="74" t="inlineStr">
+      <c r="K56" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22678,27 +22718,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G57" s="74" t="inlineStr">
+      <c r="G57" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H57" s="74" t="inlineStr">
+      <c r="H57" s="75" t="inlineStr">
         <is>
           <t>Substitution and elimination extend equation-solving transformations and depend on preserving equality while isolating or eliminating variables.</t>
         </is>
       </c>
-      <c r="I57" s="74" t="inlineStr">
+      <c r="I57" s="75" t="inlineStr">
         <is>
           <t>Have learners solve/check a one-variable linear equation before a system; code errors as equation-solving, sign, or system-model issues.</t>
         </is>
       </c>
-      <c r="J57" s="74" t="inlineStr">
+      <c r="J57" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K57" s="74" t="inlineStr">
+      <c r="K57" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22735,27 +22775,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G58" s="74" t="inlineStr">
+      <c r="G58" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H58" s="74" t="inlineStr">
+      <c r="H58" s="75" t="inlineStr">
         <is>
           <t>The mapped systems outcome explicitly includes graphical solutions, which require coordinate plotting and reading intersection points. Algebraic methods may be introduced separately.</t>
         </is>
       </c>
-      <c r="I58" s="74" t="inlineStr">
+      <c r="I58" s="75" t="inlineStr">
         <is>
           <t>Solve a two-line system graphically and algebraically, then compare the intersection with the ordered-pair solution.</t>
         </is>
       </c>
-      <c r="J58" s="74" t="inlineStr">
+      <c r="J58" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K58" s="74" t="inlineStr">
+      <c r="K58" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22792,27 +22832,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G59" s="74" t="inlineStr">
+      <c r="G59" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H59" s="74" t="inlineStr">
+      <c r="H59" s="75" t="inlineStr">
         <is>
           <t>Linear-function representations supply the line equations and intersection meaning used in graphical systems. This is core to the full multi-representation outcome, though substitution/elimination can be taught separately.</t>
         </is>
       </c>
-      <c r="I59" s="74" t="inlineStr">
+      <c r="I59" s="75" t="inlineStr">
         <is>
           <t>Plot two linear functions, identify their intersection, and substitute the ordered pair into both equations; assess algebra and graph-reading separately.</t>
         </is>
       </c>
-      <c r="J59" s="74" t="inlineStr">
+      <c r="J59" s="75" t="inlineStr">
         <is>
           <t>AI-assisted preliminary desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K59" s="74" t="inlineStr">
+      <c r="K59" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22849,15 +22889,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G60" s="74" t="inlineStr">
+      <c r="G60" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H60" s="74" t="n"/>
-      <c r="I60" s="74" t="n"/>
-      <c r="J60" s="74" t="n"/>
-      <c r="K60" s="74" t="n"/>
+      <c r="H60" s="75" t="n"/>
+      <c r="I60" s="75" t="n"/>
+      <c r="J60" s="75" t="n"/>
+      <c r="K60" s="75" t="n"/>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="32" t="inlineStr">
@@ -22890,27 +22930,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G61" s="74" t="inlineStr">
+      <c r="G61" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H61" s="74" t="inlineStr">
+      <c r="H61" s="75" t="inlineStr">
         <is>
           <t>The polynomial cluster uses powers of the variable and interprets degree/coefficient structure; exponent meaning is part of reading polynomial terms, though a brief exponent refresher can be embedded in the first polynomial lesson.</t>
         </is>
       </c>
-      <c r="I61" s="74" t="inlineStr">
+      <c r="I61" s="75" t="inlineStr">
         <is>
           <t>Ask learners to read and compare x, x², and 3x² + 2x; check whether they can explain the exponent/degree meaning and carry out products without an exponent-law prerequisite gap.</t>
         </is>
       </c>
-      <c r="J61" s="74" t="inlineStr">
+      <c r="J61" s="75" t="inlineStr">
         <is>
           <t>AI-assisted desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K61" s="74" t="inlineStr">
+      <c r="K61" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -22947,15 +22987,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G62" s="74" t="inlineStr">
+      <c r="G62" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H62" s="74" t="n"/>
-      <c r="I62" s="74" t="n"/>
-      <c r="J62" s="74" t="n"/>
-      <c r="K62" s="74" t="n"/>
+      <c r="H62" s="75" t="n"/>
+      <c r="I62" s="75" t="n"/>
+      <c r="J62" s="75" t="n"/>
+      <c r="K62" s="75" t="n"/>
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="32" t="inlineStr">
@@ -22988,27 +23028,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G63" s="74" t="inlineStr">
+      <c r="G63" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H63" s="74" t="inlineStr">
+      <c r="H63" s="75" t="inlineStr">
         <is>
           <t>Integer factors and common multiples can support factor intuition, but polynomial factorization is not simply prime factorization. Treat FND-007 as a source of examples, not a gate to learning algebraic identities.</t>
         </is>
       </c>
-      <c r="I63" s="74" t="inlineStr">
+      <c r="I63" s="75" t="inlineStr">
         <is>
           <t>Test factoring simple polynomials such as x² + 5x + 6 and x² - 9 after teaching polynomial structure; compare performance with a separate numerical-factor diagnostic to see what actually blocks progress.</t>
         </is>
       </c>
-      <c r="J63" s="74" t="inlineStr">
+      <c r="J63" s="75" t="inlineStr">
         <is>
           <t>AI-assisted desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K63" s="74" t="inlineStr">
+      <c r="K63" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -23045,15 +23085,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G64" s="74" t="inlineStr">
+      <c r="G64" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H64" s="74" t="n"/>
-      <c r="I64" s="74" t="n"/>
-      <c r="J64" s="74" t="n"/>
-      <c r="K64" s="74" t="n"/>
+      <c r="H64" s="75" t="n"/>
+      <c r="I64" s="75" t="n"/>
+      <c r="J64" s="75" t="n"/>
+      <c r="K64" s="75" t="n"/>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="32" t="inlineStr">
@@ -23086,15 +23126,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G65" s="74" t="inlineStr">
+      <c r="G65" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H65" s="74" t="n"/>
-      <c r="I65" s="74" t="n"/>
-      <c r="J65" s="74" t="n"/>
-      <c r="K65" s="74" t="n"/>
+      <c r="H65" s="75" t="n"/>
+      <c r="I65" s="75" t="n"/>
+      <c r="J65" s="75" t="n"/>
+      <c r="K65" s="75" t="n"/>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="32" t="inlineStr">
@@ -23127,15 +23167,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G66" s="74" t="inlineStr">
+      <c r="G66" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H66" s="74" t="n"/>
-      <c r="I66" s="74" t="n"/>
-      <c r="J66" s="74" t="n"/>
-      <c r="K66" s="74" t="n"/>
+      <c r="H66" s="75" t="n"/>
+      <c r="I66" s="75" t="n"/>
+      <c r="J66" s="75" t="n"/>
+      <c r="K66" s="75" t="n"/>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="32" t="inlineStr">
@@ -23168,15 +23208,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G67" s="74" t="inlineStr">
+      <c r="G67" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H67" s="74" t="n"/>
-      <c r="I67" s="74" t="n"/>
-      <c r="J67" s="74" t="n"/>
-      <c r="K67" s="74" t="n"/>
+      <c r="H67" s="75" t="n"/>
+      <c r="I67" s="75" t="n"/>
+      <c r="J67" s="75" t="n"/>
+      <c r="K67" s="75" t="n"/>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="32" t="inlineStr">
@@ -23209,15 +23249,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G68" s="74" t="inlineStr">
+      <c r="G68" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H68" s="74" t="n"/>
-      <c r="I68" s="74" t="n"/>
-      <c r="J68" s="74" t="n"/>
-      <c r="K68" s="74" t="n"/>
+      <c r="H68" s="75" t="n"/>
+      <c r="I68" s="75" t="n"/>
+      <c r="J68" s="75" t="n"/>
+      <c r="K68" s="75" t="n"/>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="32" t="inlineStr">
@@ -23250,27 +23290,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G69" s="74" t="inlineStr">
+      <c r="G69" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H69" s="74" t="inlineStr">
+      <c r="H69" s="75" t="inlineStr">
         <is>
           <t>Rational expressions are quotients of expressions/polynomials and can be introduced without prior fluency with powers and integer exponents. Powers are useful for later rational-expression examples but not for the basic fraction/domain idea.</t>
         </is>
       </c>
-      <c r="I69" s="74" t="inlineStr">
+      <c r="I69" s="75" t="inlineStr">
         <is>
           <t>Assess simplification and excluded-value reasoning on (x² - 1)/(x - 1) and simple linear quotients before using exponent-heavy examples; insert an exponent refresher only when required.</t>
         </is>
       </c>
-      <c r="J69" s="74" t="inlineStr">
+      <c r="J69" s="75" t="inlineStr">
         <is>
           <t>AI-assisted desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K69" s="74" t="inlineStr">
+      <c r="K69" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -23307,27 +23347,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G70" s="74" t="inlineStr">
+      <c r="G70" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H70" s="74" t="inlineStr">
+      <c r="H70" s="75" t="inlineStr">
         <is>
           <t>The radicals/rational-exponents cluster directly relies on the meaning of powers and exponent notation. Real-domain rules and equivalence manipulations build on that base.</t>
         </is>
       </c>
-      <c r="I70" s="74" t="inlineStr">
+      <c r="I70" s="75" t="inlineStr">
         <is>
           <t>Use conversion tasks between square roots and fractional exponents, simplify simple powers, then solve a radical equation and check the result. Distinguish exponent meaning errors from domain errors.</t>
         </is>
       </c>
-      <c r="J70" s="74" t="inlineStr">
+      <c r="J70" s="75" t="inlineStr">
         <is>
           <t>AI-assisted desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K70" s="74" t="inlineStr">
+      <c r="K70" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -23364,15 +23404,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G71" s="74" t="inlineStr">
+      <c r="G71" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H71" s="74" t="n"/>
-      <c r="I71" s="74" t="n"/>
-      <c r="J71" s="74" t="n"/>
-      <c r="K71" s="74" t="n"/>
+      <c r="H71" s="75" t="n"/>
+      <c r="I71" s="75" t="n"/>
+      <c r="J71" s="75" t="n"/>
+      <c r="K71" s="75" t="n"/>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="32" t="inlineStr">
@@ -23405,27 +23445,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G72" s="74" t="inlineStr">
+      <c r="G72" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H72" s="74" t="inlineStr">
+      <c r="H72" s="75" t="inlineStr">
         <is>
           <t>For the full radicals/rational-exponents outcome, learners need to reason about real-number domains, intervals, and valid values—especially even roots and constraints introduced by transformations. Teach any missing subskill locally as a bridge.</t>
         </is>
       </c>
-      <c r="I72" s="74" t="inlineStr">
+      <c r="I72" s="75" t="inlineStr">
         <is>
           <t>Give real-domain tasks such as √(x - 2), distinguish domain from output range, and ask which values make a proposed equation meaningful; identify whether interval/number-order reasoning is a genuine blocker.</t>
         </is>
       </c>
-      <c r="J72" s="74" t="inlineStr">
+      <c r="J72" s="75" t="inlineStr">
         <is>
           <t>AI-assisted desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K72" s="74" t="inlineStr">
+      <c r="K72" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -23462,15 +23502,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G73" s="74" t="inlineStr">
+      <c r="G73" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H73" s="74" t="n"/>
-      <c r="I73" s="74" t="n"/>
-      <c r="J73" s="74" t="n"/>
-      <c r="K73" s="74" t="n"/>
+      <c r="H73" s="75" t="n"/>
+      <c r="I73" s="75" t="n"/>
+      <c r="J73" s="75" t="n"/>
+      <c r="K73" s="75" t="n"/>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="32" t="inlineStr">
@@ -23503,27 +23543,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G74" s="74" t="inlineStr">
+      <c r="G74" s="75" t="inlineStr">
         <is>
           <t>Core required</t>
         </is>
       </c>
-      <c r="H74" s="74" t="inlineStr">
+      <c r="H74" s="75" t="inlineStr">
         <is>
           <t>Integer-exponent meaning underpins exponential functions as repeated multiplicative change and supports the inverse relationship between exponentials and logarithms.</t>
         </is>
       </c>
-      <c r="I74" s="74" t="inlineStr">
+      <c r="I74" s="75" t="inlineStr">
         <is>
           <t>Translate repeated percentage growth into an exponential rule, compare it with a linear sequence, and explain the role of the exponent; check this before teaching logarithms as the inverse operation.</t>
         </is>
       </c>
-      <c r="J74" s="74" t="inlineStr">
+      <c r="J74" s="75" t="inlineStr">
         <is>
           <t>AI-assisted desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K74" s="74" t="inlineStr">
+      <c r="K74" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -23560,15 +23600,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G75" s="74" t="inlineStr">
+      <c r="G75" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H75" s="74" t="n"/>
-      <c r="I75" s="74" t="n"/>
-      <c r="J75" s="74" t="n"/>
-      <c r="K75" s="74" t="n"/>
+      <c r="H75" s="75" t="n"/>
+      <c r="I75" s="75" t="n"/>
+      <c r="J75" s="75" t="n"/>
+      <c r="K75" s="75" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="32" t="inlineStr">
@@ -23601,27 +23641,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G76" s="74" t="inlineStr">
+      <c r="G76" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H76" s="74" t="inlineStr">
+      <c r="H76" s="75" t="inlineStr">
         <is>
           <t>Real-number order and interval notation help state domains/ranges and logarithm constraints, but the essential positive-input restriction for logarithms can be taught explicitly in ALG-017. The whole FND-016 cluster is broader than the minimum needed.</t>
         </is>
       </c>
-      <c r="I76" s="74" t="inlineStr">
+      <c r="I76" s="75" t="inlineStr">
         <is>
           <t>Teach log input restrictions locally, then test domain/range statements and interval notation separately. If learners understand positive inputs but struggle only with notation, treat FND-016 as a repair path rather than a hard gate.</t>
         </is>
       </c>
-      <c r="J76" s="74" t="inlineStr">
+      <c r="J76" s="75" t="inlineStr">
         <is>
           <t>AI-assisted desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K76" s="74" t="inlineStr">
+      <c r="K76" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -23658,15 +23698,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G77" s="74" t="inlineStr">
+      <c r="G77" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H77" s="74" t="n"/>
-      <c r="I77" s="74" t="n"/>
-      <c r="J77" s="74" t="n"/>
-      <c r="K77" s="74" t="n"/>
+      <c r="H77" s="75" t="n"/>
+      <c r="I77" s="75" t="n"/>
+      <c r="J77" s="75" t="n"/>
+      <c r="K77" s="75" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="32" t="inlineStr">
@@ -23699,27 +23739,27 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G78" s="74" t="inlineStr">
+      <c r="G78" s="75" t="inlineStr">
         <is>
           <t>Helpful</t>
         </is>
       </c>
-      <c r="H78" s="74" t="inlineStr">
+      <c r="H78" s="75" t="inlineStr">
         <is>
           <t>Sequences and patterns can be introduced through finite lists, tables, and recursive rules before exponent fluency. Powers are useful for geometric sequences and exponential patterns but not for every sequence.</t>
         </is>
       </c>
-      <c r="I78" s="74" t="inlineStr">
+      <c r="I78" s="75" t="inlineStr">
         <is>
           <t>Assess arithmetic and recursive sequence rules without exponents first, then geometric sequences with powers. Separate the objectives and only require FND-014 for the latter.</t>
         </is>
       </c>
-      <c r="J78" s="74" t="inlineStr">
+      <c r="J78" s="75" t="inlineStr">
         <is>
           <t>AI-assisted desk review; educator confirmation pending</t>
         </is>
       </c>
-      <c r="K78" s="74" t="inlineStr">
+      <c r="K78" s="75" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -23756,15 +23796,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G79" s="74" t="inlineStr">
+      <c r="G79" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H79" s="74" t="n"/>
-      <c r="I79" s="74" t="n"/>
-      <c r="J79" s="74" t="n"/>
-      <c r="K79" s="74" t="n"/>
+      <c r="H79" s="75" t="n"/>
+      <c r="I79" s="75" t="n"/>
+      <c r="J79" s="75" t="n"/>
+      <c r="K79" s="75" t="n"/>
     </row>
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="32" t="inlineStr">
@@ -23797,15 +23837,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G80" s="74" t="inlineStr">
+      <c r="G80" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H80" s="74" t="n"/>
-      <c r="I80" s="74" t="n"/>
-      <c r="J80" s="74" t="n"/>
-      <c r="K80" s="74" t="n"/>
+      <c r="H80" s="75" t="n"/>
+      <c r="I80" s="75" t="n"/>
+      <c r="J80" s="75" t="n"/>
+      <c r="K80" s="75" t="n"/>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="32" t="inlineStr">
@@ -23838,15 +23878,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G81" s="74" t="inlineStr">
+      <c r="G81" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H81" s="74" t="n"/>
-      <c r="I81" s="74" t="n"/>
-      <c r="J81" s="74" t="n"/>
-      <c r="K81" s="74" t="n"/>
+      <c r="H81" s="75" t="n"/>
+      <c r="I81" s="75" t="n"/>
+      <c r="J81" s="75" t="n"/>
+      <c r="K81" s="75" t="n"/>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="32" t="inlineStr">
@@ -23879,15 +23919,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G82" s="74" t="inlineStr">
+      <c r="G82" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H82" s="74" t="n"/>
-      <c r="I82" s="74" t="n"/>
-      <c r="J82" s="74" t="n"/>
-      <c r="K82" s="74" t="n"/>
+      <c r="H82" s="75" t="n"/>
+      <c r="I82" s="75" t="n"/>
+      <c r="J82" s="75" t="n"/>
+      <c r="K82" s="75" t="n"/>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="32" t="inlineStr">
@@ -23920,15 +23960,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G83" s="74" t="inlineStr">
+      <c r="G83" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H83" s="74" t="n"/>
-      <c r="I83" s="74" t="n"/>
-      <c r="J83" s="74" t="n"/>
-      <c r="K83" s="74" t="n"/>
+      <c r="H83" s="75" t="n"/>
+      <c r="I83" s="75" t="n"/>
+      <c r="J83" s="75" t="n"/>
+      <c r="K83" s="75" t="n"/>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="32" t="inlineStr">
@@ -23961,15 +24001,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G84" s="74" t="inlineStr">
+      <c r="G84" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H84" s="74" t="n"/>
-      <c r="I84" s="74" t="n"/>
-      <c r="J84" s="74" t="n"/>
-      <c r="K84" s="74" t="n"/>
+      <c r="H84" s="75" t="n"/>
+      <c r="I84" s="75" t="n"/>
+      <c r="J84" s="75" t="n"/>
+      <c r="K84" s="75" t="n"/>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="32" t="inlineStr">
@@ -24002,15 +24042,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G85" s="74" t="inlineStr">
+      <c r="G85" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H85" s="74" t="n"/>
-      <c r="I85" s="74" t="n"/>
-      <c r="J85" s="74" t="n"/>
-      <c r="K85" s="74" t="n"/>
+      <c r="H85" s="75" t="n"/>
+      <c r="I85" s="75" t="n"/>
+      <c r="J85" s="75" t="n"/>
+      <c r="K85" s="75" t="n"/>
     </row>
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="32" t="inlineStr">
@@ -24043,15 +24083,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G86" s="74" t="inlineStr">
+      <c r="G86" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H86" s="74" t="n"/>
-      <c r="I86" s="74" t="n"/>
-      <c r="J86" s="74" t="n"/>
-      <c r="K86" s="74" t="n"/>
+      <c r="H86" s="75" t="n"/>
+      <c r="I86" s="75" t="n"/>
+      <c r="J86" s="75" t="n"/>
+      <c r="K86" s="75" t="n"/>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="32" t="inlineStr">
@@ -24084,15 +24124,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G87" s="74" t="inlineStr">
+      <c r="G87" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H87" s="74" t="n"/>
-      <c r="I87" s="74" t="n"/>
-      <c r="J87" s="74" t="n"/>
-      <c r="K87" s="74" t="n"/>
+      <c r="H87" s="75" t="n"/>
+      <c r="I87" s="75" t="n"/>
+      <c r="J87" s="75" t="n"/>
+      <c r="K87" s="75" t="n"/>
     </row>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="32" t="inlineStr">
@@ -24125,15 +24165,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G88" s="74" t="inlineStr">
+      <c r="G88" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H88" s="74" t="n"/>
-      <c r="I88" s="74" t="n"/>
-      <c r="J88" s="74" t="n"/>
-      <c r="K88" s="74" t="n"/>
+      <c r="H88" s="75" t="n"/>
+      <c r="I88" s="75" t="n"/>
+      <c r="J88" s="75" t="n"/>
+      <c r="K88" s="75" t="n"/>
     </row>
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="32" t="inlineStr">
@@ -24166,15 +24206,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G89" s="74" t="inlineStr">
+      <c r="G89" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H89" s="74" t="n"/>
-      <c r="I89" s="74" t="n"/>
-      <c r="J89" s="74" t="n"/>
-      <c r="K89" s="74" t="n"/>
+      <c r="H89" s="75" t="n"/>
+      <c r="I89" s="75" t="n"/>
+      <c r="J89" s="75" t="n"/>
+      <c r="K89" s="75" t="n"/>
     </row>
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="32" t="inlineStr">
@@ -24207,15 +24247,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G90" s="74" t="inlineStr">
+      <c r="G90" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H90" s="74" t="n"/>
-      <c r="I90" s="74" t="n"/>
-      <c r="J90" s="74" t="n"/>
-      <c r="K90" s="74" t="n"/>
+      <c r="H90" s="75" t="n"/>
+      <c r="I90" s="75" t="n"/>
+      <c r="J90" s="75" t="n"/>
+      <c r="K90" s="75" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="32" t="inlineStr">
@@ -24248,15 +24288,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G91" s="74" t="inlineStr">
+      <c r="G91" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H91" s="74" t="n"/>
-      <c r="I91" s="74" t="n"/>
-      <c r="J91" s="74" t="n"/>
-      <c r="K91" s="74" t="n"/>
+      <c r="H91" s="75" t="n"/>
+      <c r="I91" s="75" t="n"/>
+      <c r="J91" s="75" t="n"/>
+      <c r="K91" s="75" t="n"/>
     </row>
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="32" t="inlineStr">
@@ -24289,15 +24329,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G92" s="74" t="inlineStr">
+      <c r="G92" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H92" s="74" t="n"/>
-      <c r="I92" s="74" t="n"/>
-      <c r="J92" s="74" t="n"/>
-      <c r="K92" s="74" t="n"/>
+      <c r="H92" s="75" t="n"/>
+      <c r="I92" s="75" t="n"/>
+      <c r="J92" s="75" t="n"/>
+      <c r="K92" s="75" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="32" t="inlineStr">
@@ -24330,15 +24370,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G93" s="74" t="inlineStr">
+      <c r="G93" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H93" s="74" t="n"/>
-      <c r="I93" s="74" t="n"/>
-      <c r="J93" s="74" t="n"/>
-      <c r="K93" s="74" t="n"/>
+      <c r="H93" s="75" t="n"/>
+      <c r="I93" s="75" t="n"/>
+      <c r="J93" s="75" t="n"/>
+      <c r="K93" s="75" t="n"/>
     </row>
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="32" t="inlineStr">
@@ -24371,15 +24411,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G94" s="74" t="inlineStr">
+      <c r="G94" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H94" s="74" t="n"/>
-      <c r="I94" s="74" t="n"/>
-      <c r="J94" s="74" t="n"/>
-      <c r="K94" s="74" t="n"/>
+      <c r="H94" s="75" t="n"/>
+      <c r="I94" s="75" t="n"/>
+      <c r="J94" s="75" t="n"/>
+      <c r="K94" s="75" t="n"/>
     </row>
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="32" t="inlineStr">
@@ -24412,15 +24452,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G95" s="74" t="inlineStr">
+      <c r="G95" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H95" s="74" t="n"/>
-      <c r="I95" s="74" t="n"/>
-      <c r="J95" s="74" t="n"/>
-      <c r="K95" s="74" t="n"/>
+      <c r="H95" s="75" t="n"/>
+      <c r="I95" s="75" t="n"/>
+      <c r="J95" s="75" t="n"/>
+      <c r="K95" s="75" t="n"/>
     </row>
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="32" t="inlineStr">
@@ -24453,15 +24493,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G96" s="74" t="inlineStr">
+      <c r="G96" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H96" s="74" t="n"/>
-      <c r="I96" s="74" t="n"/>
-      <c r="J96" s="74" t="n"/>
-      <c r="K96" s="74" t="n"/>
+      <c r="H96" s="75" t="n"/>
+      <c r="I96" s="75" t="n"/>
+      <c r="J96" s="75" t="n"/>
+      <c r="K96" s="75" t="n"/>
     </row>
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="32" t="inlineStr">
@@ -24494,15 +24534,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G97" s="74" t="inlineStr">
+      <c r="G97" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H97" s="74" t="n"/>
-      <c r="I97" s="74" t="n"/>
-      <c r="J97" s="74" t="n"/>
-      <c r="K97" s="74" t="n"/>
+      <c r="H97" s="75" t="n"/>
+      <c r="I97" s="75" t="n"/>
+      <c r="J97" s="75" t="n"/>
+      <c r="K97" s="75" t="n"/>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="32" t="inlineStr">
@@ -24535,15 +24575,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G98" s="74" t="inlineStr">
+      <c r="G98" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H98" s="74" t="n"/>
-      <c r="I98" s="74" t="n"/>
-      <c r="J98" s="74" t="n"/>
-      <c r="K98" s="74" t="n"/>
+      <c r="H98" s="75" t="n"/>
+      <c r="I98" s="75" t="n"/>
+      <c r="J98" s="75" t="n"/>
+      <c r="K98" s="75" t="n"/>
     </row>
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="32" t="inlineStr">
@@ -24576,15 +24616,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G99" s="74" t="inlineStr">
+      <c r="G99" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H99" s="74" t="n"/>
-      <c r="I99" s="74" t="n"/>
-      <c r="J99" s="74" t="n"/>
-      <c r="K99" s="74" t="n"/>
+      <c r="H99" s="75" t="n"/>
+      <c r="I99" s="75" t="n"/>
+      <c r="J99" s="75" t="n"/>
+      <c r="K99" s="75" t="n"/>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="32" t="inlineStr">
@@ -24617,15 +24657,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G100" s="74" t="inlineStr">
+      <c r="G100" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H100" s="74" t="n"/>
-      <c r="I100" s="74" t="n"/>
-      <c r="J100" s="74" t="n"/>
-      <c r="K100" s="74" t="n"/>
+      <c r="H100" s="75" t="n"/>
+      <c r="I100" s="75" t="n"/>
+      <c r="J100" s="75" t="n"/>
+      <c r="K100" s="75" t="n"/>
     </row>
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="32" t="inlineStr">
@@ -24658,15 +24698,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G101" s="74" t="inlineStr">
+      <c r="G101" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H101" s="74" t="n"/>
-      <c r="I101" s="74" t="n"/>
-      <c r="J101" s="74" t="n"/>
-      <c r="K101" s="74" t="n"/>
+      <c r="H101" s="75" t="n"/>
+      <c r="I101" s="75" t="n"/>
+      <c r="J101" s="75" t="n"/>
+      <c r="K101" s="75" t="n"/>
     </row>
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="32" t="inlineStr">
@@ -24699,15 +24739,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G102" s="74" t="inlineStr">
+      <c r="G102" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H102" s="74" t="n"/>
-      <c r="I102" s="74" t="n"/>
-      <c r="J102" s="74" t="n"/>
-      <c r="K102" s="74" t="n"/>
+      <c r="H102" s="75" t="n"/>
+      <c r="I102" s="75" t="n"/>
+      <c r="J102" s="75" t="n"/>
+      <c r="K102" s="75" t="n"/>
     </row>
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="32" t="inlineStr">
@@ -24740,15 +24780,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G103" s="74" t="inlineStr">
+      <c r="G103" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H103" s="74" t="n"/>
-      <c r="I103" s="74" t="n"/>
-      <c r="J103" s="74" t="n"/>
-      <c r="K103" s="74" t="n"/>
+      <c r="H103" s="75" t="n"/>
+      <c r="I103" s="75" t="n"/>
+      <c r="J103" s="75" t="n"/>
+      <c r="K103" s="75" t="n"/>
     </row>
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="32" t="inlineStr">
@@ -24781,15 +24821,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G104" s="74" t="inlineStr">
+      <c r="G104" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H104" s="74" t="n"/>
-      <c r="I104" s="74" t="n"/>
-      <c r="J104" s="74" t="n"/>
-      <c r="K104" s="74" t="n"/>
+      <c r="H104" s="75" t="n"/>
+      <c r="I104" s="75" t="n"/>
+      <c r="J104" s="75" t="n"/>
+      <c r="K104" s="75" t="n"/>
     </row>
     <row r="105" ht="42" customHeight="1">
       <c r="A105" s="32" t="inlineStr">
@@ -24822,15 +24862,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G105" s="74" t="inlineStr">
+      <c r="G105" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H105" s="74" t="n"/>
-      <c r="I105" s="74" t="n"/>
-      <c r="J105" s="74" t="n"/>
-      <c r="K105" s="74" t="n"/>
+      <c r="H105" s="75" t="n"/>
+      <c r="I105" s="75" t="n"/>
+      <c r="J105" s="75" t="n"/>
+      <c r="K105" s="75" t="n"/>
     </row>
     <row r="106" ht="42" customHeight="1">
       <c r="A106" s="32" t="inlineStr">
@@ -24863,15 +24903,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G106" s="74" t="inlineStr">
+      <c r="G106" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H106" s="74" t="n"/>
-      <c r="I106" s="74" t="n"/>
-      <c r="J106" s="74" t="n"/>
-      <c r="K106" s="74" t="n"/>
+      <c r="H106" s="75" t="n"/>
+      <c r="I106" s="75" t="n"/>
+      <c r="J106" s="75" t="n"/>
+      <c r="K106" s="75" t="n"/>
     </row>
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="32" t="inlineStr">
@@ -24904,15 +24944,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G107" s="74" t="inlineStr">
+      <c r="G107" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H107" s="74" t="n"/>
-      <c r="I107" s="74" t="n"/>
-      <c r="J107" s="74" t="n"/>
-      <c r="K107" s="74" t="n"/>
+      <c r="H107" s="75" t="n"/>
+      <c r="I107" s="75" t="n"/>
+      <c r="J107" s="75" t="n"/>
+      <c r="K107" s="75" t="n"/>
     </row>
     <row r="108" ht="42" customHeight="1">
       <c r="A108" s="32" t="inlineStr">
@@ -24945,15 +24985,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G108" s="74" t="inlineStr">
+      <c r="G108" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H108" s="74" t="n"/>
-      <c r="I108" s="74" t="n"/>
-      <c r="J108" s="74" t="n"/>
-      <c r="K108" s="74" t="n"/>
+      <c r="H108" s="75" t="n"/>
+      <c r="I108" s="75" t="n"/>
+      <c r="J108" s="75" t="n"/>
+      <c r="K108" s="75" t="n"/>
     </row>
     <row r="109" ht="42" customHeight="1">
       <c r="A109" s="32" t="inlineStr">
@@ -24986,15 +25026,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G109" s="74" t="inlineStr">
+      <c r="G109" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H109" s="74" t="n"/>
-      <c r="I109" s="74" t="n"/>
-      <c r="J109" s="74" t="n"/>
-      <c r="K109" s="74" t="n"/>
+      <c r="H109" s="75" t="n"/>
+      <c r="I109" s="75" t="n"/>
+      <c r="J109" s="75" t="n"/>
+      <c r="K109" s="75" t="n"/>
     </row>
     <row r="110" ht="42" customHeight="1">
       <c r="A110" s="32" t="inlineStr">
@@ -25027,15 +25067,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G110" s="74" t="inlineStr">
+      <c r="G110" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H110" s="74" t="n"/>
-      <c r="I110" s="74" t="n"/>
-      <c r="J110" s="74" t="n"/>
-      <c r="K110" s="74" t="n"/>
+      <c r="H110" s="75" t="n"/>
+      <c r="I110" s="75" t="n"/>
+      <c r="J110" s="75" t="n"/>
+      <c r="K110" s="75" t="n"/>
     </row>
     <row r="111" ht="42" customHeight="1">
       <c r="A111" s="32" t="inlineStr">
@@ -25068,15 +25108,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G111" s="74" t="inlineStr">
+      <c r="G111" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H111" s="74" t="n"/>
-      <c r="I111" s="74" t="n"/>
-      <c r="J111" s="74" t="n"/>
-      <c r="K111" s="74" t="n"/>
+      <c r="H111" s="75" t="n"/>
+      <c r="I111" s="75" t="n"/>
+      <c r="J111" s="75" t="n"/>
+      <c r="K111" s="75" t="n"/>
     </row>
     <row r="112" ht="42" customHeight="1">
       <c r="A112" s="32" t="inlineStr">
@@ -25109,15 +25149,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G112" s="74" t="inlineStr">
+      <c r="G112" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H112" s="74" t="n"/>
-      <c r="I112" s="74" t="n"/>
-      <c r="J112" s="74" t="n"/>
-      <c r="K112" s="74" t="n"/>
+      <c r="H112" s="75" t="n"/>
+      <c r="I112" s="75" t="n"/>
+      <c r="J112" s="75" t="n"/>
+      <c r="K112" s="75" t="n"/>
     </row>
     <row r="113" ht="42" customHeight="1">
       <c r="A113" s="32" t="inlineStr">
@@ -25150,15 +25190,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G113" s="74" t="inlineStr">
+      <c r="G113" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H113" s="74" t="n"/>
-      <c r="I113" s="74" t="n"/>
-      <c r="J113" s="74" t="n"/>
-      <c r="K113" s="74" t="n"/>
+      <c r="H113" s="75" t="n"/>
+      <c r="I113" s="75" t="n"/>
+      <c r="J113" s="75" t="n"/>
+      <c r="K113" s="75" t="n"/>
     </row>
     <row r="114" ht="42" customHeight="1">
       <c r="A114" s="32" t="inlineStr">
@@ -25191,15 +25231,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G114" s="74" t="inlineStr">
+      <c r="G114" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H114" s="74" t="n"/>
-      <c r="I114" s="74" t="n"/>
-      <c r="J114" s="74" t="n"/>
-      <c r="K114" s="74" t="n"/>
+      <c r="H114" s="75" t="n"/>
+      <c r="I114" s="75" t="n"/>
+      <c r="J114" s="75" t="n"/>
+      <c r="K114" s="75" t="n"/>
     </row>
     <row r="115" ht="42" customHeight="1">
       <c r="A115" s="32" t="inlineStr">
@@ -25232,15 +25272,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G115" s="74" t="inlineStr">
+      <c r="G115" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H115" s="74" t="n"/>
-      <c r="I115" s="74" t="n"/>
-      <c r="J115" s="74" t="n"/>
-      <c r="K115" s="74" t="n"/>
+      <c r="H115" s="75" t="n"/>
+      <c r="I115" s="75" t="n"/>
+      <c r="J115" s="75" t="n"/>
+      <c r="K115" s="75" t="n"/>
     </row>
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="32" t="inlineStr">
@@ -25273,15 +25313,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G116" s="74" t="inlineStr">
+      <c r="G116" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H116" s="74" t="n"/>
-      <c r="I116" s="74" t="n"/>
-      <c r="J116" s="74" t="n"/>
-      <c r="K116" s="74" t="n"/>
+      <c r="H116" s="75" t="n"/>
+      <c r="I116" s="75" t="n"/>
+      <c r="J116" s="75" t="n"/>
+      <c r="K116" s="75" t="n"/>
     </row>
     <row r="117" ht="42" customHeight="1">
       <c r="A117" s="32" t="inlineStr">
@@ -25314,15 +25354,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G117" s="74" t="inlineStr">
+      <c r="G117" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H117" s="74" t="n"/>
-      <c r="I117" s="74" t="n"/>
-      <c r="J117" s="74" t="n"/>
-      <c r="K117" s="74" t="n"/>
+      <c r="H117" s="75" t="n"/>
+      <c r="I117" s="75" t="n"/>
+      <c r="J117" s="75" t="n"/>
+      <c r="K117" s="75" t="n"/>
     </row>
     <row r="118" ht="42" customHeight="1">
       <c r="A118" s="32" t="inlineStr">
@@ -25355,15 +25395,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G118" s="74" t="inlineStr">
+      <c r="G118" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H118" s="74" t="n"/>
-      <c r="I118" s="74" t="n"/>
-      <c r="J118" s="74" t="n"/>
-      <c r="K118" s="74" t="n"/>
+      <c r="H118" s="75" t="n"/>
+      <c r="I118" s="75" t="n"/>
+      <c r="J118" s="75" t="n"/>
+      <c r="K118" s="75" t="n"/>
     </row>
     <row r="119" ht="42" customHeight="1">
       <c r="A119" s="32" t="inlineStr">
@@ -25396,15 +25436,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G119" s="74" t="inlineStr">
+      <c r="G119" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H119" s="74" t="n"/>
-      <c r="I119" s="74" t="n"/>
-      <c r="J119" s="74" t="n"/>
-      <c r="K119" s="74" t="n"/>
+      <c r="H119" s="75" t="n"/>
+      <c r="I119" s="75" t="n"/>
+      <c r="J119" s="75" t="n"/>
+      <c r="K119" s="75" t="n"/>
     </row>
     <row r="120" ht="42" customHeight="1">
       <c r="A120" s="32" t="inlineStr">
@@ -25437,15 +25477,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G120" s="74" t="inlineStr">
+      <c r="G120" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H120" s="74" t="n"/>
-      <c r="I120" s="74" t="n"/>
-      <c r="J120" s="74" t="n"/>
-      <c r="K120" s="74" t="n"/>
+      <c r="H120" s="75" t="n"/>
+      <c r="I120" s="75" t="n"/>
+      <c r="J120" s="75" t="n"/>
+      <c r="K120" s="75" t="n"/>
     </row>
     <row r="121" ht="42" customHeight="1">
       <c r="A121" s="32" t="inlineStr">
@@ -25478,15 +25518,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G121" s="74" t="inlineStr">
+      <c r="G121" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H121" s="74" t="n"/>
-      <c r="I121" s="74" t="n"/>
-      <c r="J121" s="74" t="n"/>
-      <c r="K121" s="74" t="n"/>
+      <c r="H121" s="75" t="n"/>
+      <c r="I121" s="75" t="n"/>
+      <c r="J121" s="75" t="n"/>
+      <c r="K121" s="75" t="n"/>
     </row>
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="32" t="inlineStr">
@@ -25519,15 +25559,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G122" s="74" t="inlineStr">
+      <c r="G122" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H122" s="74" t="n"/>
-      <c r="I122" s="74" t="n"/>
-      <c r="J122" s="74" t="n"/>
-      <c r="K122" s="74" t="n"/>
+      <c r="H122" s="75" t="n"/>
+      <c r="I122" s="75" t="n"/>
+      <c r="J122" s="75" t="n"/>
+      <c r="K122" s="75" t="n"/>
     </row>
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="32" t="inlineStr">
@@ -25560,15 +25600,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G123" s="74" t="inlineStr">
+      <c r="G123" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H123" s="74" t="n"/>
-      <c r="I123" s="74" t="n"/>
-      <c r="J123" s="74" t="n"/>
-      <c r="K123" s="74" t="n"/>
+      <c r="H123" s="75" t="n"/>
+      <c r="I123" s="75" t="n"/>
+      <c r="J123" s="75" t="n"/>
+      <c r="K123" s="75" t="n"/>
     </row>
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="32" t="inlineStr">
@@ -25601,15 +25641,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G124" s="74" t="inlineStr">
+      <c r="G124" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H124" s="74" t="n"/>
-      <c r="I124" s="74" t="n"/>
-      <c r="J124" s="74" t="n"/>
-      <c r="K124" s="74" t="n"/>
+      <c r="H124" s="75" t="n"/>
+      <c r="I124" s="75" t="n"/>
+      <c r="J124" s="75" t="n"/>
+      <c r="K124" s="75" t="n"/>
     </row>
     <row r="125" ht="42" customHeight="1">
       <c r="A125" s="32" t="inlineStr">
@@ -25642,15 +25682,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G125" s="74" t="inlineStr">
+      <c r="G125" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H125" s="74" t="n"/>
-      <c r="I125" s="74" t="n"/>
-      <c r="J125" s="74" t="n"/>
-      <c r="K125" s="74" t="n"/>
+      <c r="H125" s="75" t="n"/>
+      <c r="I125" s="75" t="n"/>
+      <c r="J125" s="75" t="n"/>
+      <c r="K125" s="75" t="n"/>
     </row>
     <row r="126" ht="42" customHeight="1">
       <c r="A126" s="32" t="inlineStr">
@@ -25683,15 +25723,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G126" s="74" t="inlineStr">
+      <c r="G126" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H126" s="74" t="n"/>
-      <c r="I126" s="74" t="n"/>
-      <c r="J126" s="74" t="n"/>
-      <c r="K126" s="74" t="n"/>
+      <c r="H126" s="75" t="n"/>
+      <c r="I126" s="75" t="n"/>
+      <c r="J126" s="75" t="n"/>
+      <c r="K126" s="75" t="n"/>
     </row>
     <row r="127" ht="42" customHeight="1">
       <c r="A127" s="32" t="inlineStr">
@@ -25724,15 +25764,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G127" s="74" t="inlineStr">
+      <c r="G127" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H127" s="74" t="n"/>
-      <c r="I127" s="74" t="n"/>
-      <c r="J127" s="74" t="n"/>
-      <c r="K127" s="74" t="n"/>
+      <c r="H127" s="75" t="n"/>
+      <c r="I127" s="75" t="n"/>
+      <c r="J127" s="75" t="n"/>
+      <c r="K127" s="75" t="n"/>
     </row>
     <row r="128" ht="42" customHeight="1">
       <c r="A128" s="32" t="inlineStr">
@@ -25765,15 +25805,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G128" s="74" t="inlineStr">
+      <c r="G128" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H128" s="74" t="n"/>
-      <c r="I128" s="74" t="n"/>
-      <c r="J128" s="74" t="n"/>
-      <c r="K128" s="74" t="n"/>
+      <c r="H128" s="75" t="n"/>
+      <c r="I128" s="75" t="n"/>
+      <c r="J128" s="75" t="n"/>
+      <c r="K128" s="75" t="n"/>
     </row>
     <row r="129" ht="42" customHeight="1">
       <c r="A129" s="32" t="inlineStr">
@@ -25806,15 +25846,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G129" s="74" t="inlineStr">
+      <c r="G129" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H129" s="74" t="n"/>
-      <c r="I129" s="74" t="n"/>
-      <c r="J129" s="74" t="n"/>
-      <c r="K129" s="74" t="n"/>
+      <c r="H129" s="75" t="n"/>
+      <c r="I129" s="75" t="n"/>
+      <c r="J129" s="75" t="n"/>
+      <c r="K129" s="75" t="n"/>
     </row>
     <row r="130" ht="42" customHeight="1">
       <c r="A130" s="32" t="inlineStr">
@@ -25847,15 +25887,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G130" s="74" t="inlineStr">
+      <c r="G130" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H130" s="74" t="n"/>
-      <c r="I130" s="74" t="n"/>
-      <c r="J130" s="74" t="n"/>
-      <c r="K130" s="74" t="n"/>
+      <c r="H130" s="75" t="n"/>
+      <c r="I130" s="75" t="n"/>
+      <c r="J130" s="75" t="n"/>
+      <c r="K130" s="75" t="n"/>
     </row>
     <row r="131" ht="42" customHeight="1">
       <c r="A131" s="32" t="inlineStr">
@@ -25888,15 +25928,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G131" s="74" t="inlineStr">
+      <c r="G131" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H131" s="74" t="n"/>
-      <c r="I131" s="74" t="n"/>
-      <c r="J131" s="74" t="n"/>
-      <c r="K131" s="74" t="n"/>
+      <c r="H131" s="75" t="n"/>
+      <c r="I131" s="75" t="n"/>
+      <c r="J131" s="75" t="n"/>
+      <c r="K131" s="75" t="n"/>
     </row>
     <row r="132" ht="42" customHeight="1">
       <c r="A132" s="32" t="inlineStr">
@@ -25929,15 +25969,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G132" s="74" t="inlineStr">
+      <c r="G132" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H132" s="74" t="n"/>
-      <c r="I132" s="74" t="n"/>
-      <c r="J132" s="74" t="n"/>
-      <c r="K132" s="74" t="n"/>
+      <c r="H132" s="75" t="n"/>
+      <c r="I132" s="75" t="n"/>
+      <c r="J132" s="75" t="n"/>
+      <c r="K132" s="75" t="n"/>
     </row>
     <row r="133" ht="42" customHeight="1">
       <c r="A133" s="32" t="inlineStr">
@@ -25970,15 +26010,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G133" s="74" t="inlineStr">
+      <c r="G133" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H133" s="74" t="n"/>
-      <c r="I133" s="74" t="n"/>
-      <c r="J133" s="74" t="n"/>
-      <c r="K133" s="74" t="n"/>
+      <c r="H133" s="75" t="n"/>
+      <c r="I133" s="75" t="n"/>
+      <c r="J133" s="75" t="n"/>
+      <c r="K133" s="75" t="n"/>
     </row>
     <row r="134" ht="42" customHeight="1">
       <c r="A134" s="32" t="inlineStr">
@@ -26011,15 +26051,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G134" s="74" t="inlineStr">
+      <c r="G134" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H134" s="74" t="n"/>
-      <c r="I134" s="74" t="n"/>
-      <c r="J134" s="74" t="n"/>
-      <c r="K134" s="74" t="n"/>
+      <c r="H134" s="75" t="n"/>
+      <c r="I134" s="75" t="n"/>
+      <c r="J134" s="75" t="n"/>
+      <c r="K134" s="75" t="n"/>
     </row>
     <row r="135" ht="42" customHeight="1">
       <c r="A135" s="32" t="inlineStr">
@@ -26052,15 +26092,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G135" s="74" t="inlineStr">
+      <c r="G135" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H135" s="74" t="n"/>
-      <c r="I135" s="74" t="n"/>
-      <c r="J135" s="74" t="n"/>
-      <c r="K135" s="74" t="n"/>
+      <c r="H135" s="75" t="n"/>
+      <c r="I135" s="75" t="n"/>
+      <c r="J135" s="75" t="n"/>
+      <c r="K135" s="75" t="n"/>
     </row>
     <row r="136" ht="42" customHeight="1">
       <c r="A136" s="32" t="inlineStr">
@@ -26093,15 +26133,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G136" s="74" t="inlineStr">
+      <c r="G136" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H136" s="74" t="n"/>
-      <c r="I136" s="74" t="n"/>
-      <c r="J136" s="74" t="n"/>
-      <c r="K136" s="74" t="n"/>
+      <c r="H136" s="75" t="n"/>
+      <c r="I136" s="75" t="n"/>
+      <c r="J136" s="75" t="n"/>
+      <c r="K136" s="75" t="n"/>
     </row>
     <row r="137" ht="42" customHeight="1">
       <c r="A137" s="32" t="inlineStr">
@@ -26134,15 +26174,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G137" s="74" t="inlineStr">
+      <c r="G137" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H137" s="74" t="n"/>
-      <c r="I137" s="74" t="n"/>
-      <c r="J137" s="74" t="n"/>
-      <c r="K137" s="74" t="n"/>
+      <c r="H137" s="75" t="n"/>
+      <c r="I137" s="75" t="n"/>
+      <c r="J137" s="75" t="n"/>
+      <c r="K137" s="75" t="n"/>
     </row>
     <row r="138" ht="42" customHeight="1">
       <c r="A138" s="32" t="inlineStr">
@@ -26175,15 +26215,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G138" s="74" t="inlineStr">
+      <c r="G138" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H138" s="74" t="n"/>
-      <c r="I138" s="74" t="n"/>
-      <c r="J138" s="74" t="n"/>
-      <c r="K138" s="74" t="n"/>
+      <c r="H138" s="75" t="n"/>
+      <c r="I138" s="75" t="n"/>
+      <c r="J138" s="75" t="n"/>
+      <c r="K138" s="75" t="n"/>
     </row>
     <row r="139" ht="42" customHeight="1">
       <c r="A139" s="32" t="inlineStr">
@@ -26216,15 +26256,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G139" s="74" t="inlineStr">
+      <c r="G139" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H139" s="74" t="n"/>
-      <c r="I139" s="74" t="n"/>
-      <c r="J139" s="74" t="n"/>
-      <c r="K139" s="74" t="n"/>
+      <c r="H139" s="75" t="n"/>
+      <c r="I139" s="75" t="n"/>
+      <c r="J139" s="75" t="n"/>
+      <c r="K139" s="75" t="n"/>
     </row>
     <row r="140" ht="42" customHeight="1">
       <c r="A140" s="32" t="inlineStr">
@@ -26257,15 +26297,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G140" s="74" t="inlineStr">
+      <c r="G140" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H140" s="74" t="n"/>
-      <c r="I140" s="74" t="n"/>
-      <c r="J140" s="74" t="n"/>
-      <c r="K140" s="74" t="n"/>
+      <c r="H140" s="75" t="n"/>
+      <c r="I140" s="75" t="n"/>
+      <c r="J140" s="75" t="n"/>
+      <c r="K140" s="75" t="n"/>
     </row>
     <row r="141" ht="42" customHeight="1">
       <c r="A141" s="32" t="inlineStr">
@@ -26298,15 +26338,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G141" s="74" t="inlineStr">
+      <c r="G141" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H141" s="74" t="n"/>
-      <c r="I141" s="74" t="n"/>
-      <c r="J141" s="74" t="n"/>
-      <c r="K141" s="74" t="n"/>
+      <c r="H141" s="75" t="n"/>
+      <c r="I141" s="75" t="n"/>
+      <c r="J141" s="75" t="n"/>
+      <c r="K141" s="75" t="n"/>
     </row>
     <row r="142" ht="42" customHeight="1">
       <c r="A142" s="32" t="inlineStr">
@@ -26339,15 +26379,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G142" s="74" t="inlineStr">
+      <c r="G142" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H142" s="74" t="n"/>
-      <c r="I142" s="74" t="n"/>
-      <c r="J142" s="74" t="n"/>
-      <c r="K142" s="74" t="n"/>
+      <c r="H142" s="75" t="n"/>
+      <c r="I142" s="75" t="n"/>
+      <c r="J142" s="75" t="n"/>
+      <c r="K142" s="75" t="n"/>
     </row>
     <row r="143" ht="42" customHeight="1">
       <c r="A143" s="32" t="inlineStr">
@@ -26380,15 +26420,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G143" s="74" t="inlineStr">
+      <c r="G143" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H143" s="74" t="n"/>
-      <c r="I143" s="74" t="n"/>
-      <c r="J143" s="74" t="n"/>
-      <c r="K143" s="74" t="n"/>
+      <c r="H143" s="75" t="n"/>
+      <c r="I143" s="75" t="n"/>
+      <c r="J143" s="75" t="n"/>
+      <c r="K143" s="75" t="n"/>
     </row>
     <row r="144" ht="42" customHeight="1">
       <c r="A144" s="32" t="inlineStr">
@@ -26421,15 +26461,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G144" s="74" t="inlineStr">
+      <c r="G144" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H144" s="74" t="n"/>
-      <c r="I144" s="74" t="n"/>
-      <c r="J144" s="74" t="n"/>
-      <c r="K144" s="74" t="n"/>
+      <c r="H144" s="75" t="n"/>
+      <c r="I144" s="75" t="n"/>
+      <c r="J144" s="75" t="n"/>
+      <c r="K144" s="75" t="n"/>
     </row>
     <row r="145" ht="42" customHeight="1">
       <c r="A145" s="32" t="inlineStr">
@@ -26462,15 +26502,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G145" s="74" t="inlineStr">
+      <c r="G145" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H145" s="74" t="n"/>
-      <c r="I145" s="74" t="n"/>
-      <c r="J145" s="74" t="n"/>
-      <c r="K145" s="74" t="n"/>
+      <c r="H145" s="75" t="n"/>
+      <c r="I145" s="75" t="n"/>
+      <c r="J145" s="75" t="n"/>
+      <c r="K145" s="75" t="n"/>
     </row>
     <row r="146" ht="42" customHeight="1">
       <c r="A146" s="32" t="inlineStr">
@@ -26503,15 +26543,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G146" s="74" t="inlineStr">
+      <c r="G146" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H146" s="74" t="n"/>
-      <c r="I146" s="74" t="n"/>
-      <c r="J146" s="74" t="n"/>
-      <c r="K146" s="74" t="n"/>
+      <c r="H146" s="75" t="n"/>
+      <c r="I146" s="75" t="n"/>
+      <c r="J146" s="75" t="n"/>
+      <c r="K146" s="75" t="n"/>
     </row>
     <row r="147" ht="42" customHeight="1">
       <c r="A147" s="32" t="inlineStr">
@@ -26544,15 +26584,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G147" s="74" t="inlineStr">
+      <c r="G147" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H147" s="74" t="n"/>
-      <c r="I147" s="74" t="n"/>
-      <c r="J147" s="74" t="n"/>
-      <c r="K147" s="74" t="n"/>
+      <c r="H147" s="75" t="n"/>
+      <c r="I147" s="75" t="n"/>
+      <c r="J147" s="75" t="n"/>
+      <c r="K147" s="75" t="n"/>
     </row>
     <row r="148" ht="42" customHeight="1">
       <c r="A148" s="32" t="inlineStr">
@@ -26585,15 +26625,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G148" s="74" t="inlineStr">
+      <c r="G148" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H148" s="74" t="n"/>
-      <c r="I148" s="74" t="n"/>
-      <c r="J148" s="74" t="n"/>
-      <c r="K148" s="74" t="n"/>
+      <c r="H148" s="75" t="n"/>
+      <c r="I148" s="75" t="n"/>
+      <c r="J148" s="75" t="n"/>
+      <c r="K148" s="75" t="n"/>
     </row>
     <row r="149" ht="42" customHeight="1">
       <c r="A149" s="32" t="inlineStr">
@@ -26626,15 +26666,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G149" s="74" t="inlineStr">
+      <c r="G149" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H149" s="74" t="n"/>
-      <c r="I149" s="74" t="n"/>
-      <c r="J149" s="74" t="n"/>
-      <c r="K149" s="74" t="n"/>
+      <c r="H149" s="75" t="n"/>
+      <c r="I149" s="75" t="n"/>
+      <c r="J149" s="75" t="n"/>
+      <c r="K149" s="75" t="n"/>
     </row>
     <row r="150" ht="42" customHeight="1">
       <c r="A150" s="32" t="inlineStr">
@@ -26667,15 +26707,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G150" s="74" t="inlineStr">
+      <c r="G150" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H150" s="74" t="n"/>
-      <c r="I150" s="74" t="n"/>
-      <c r="J150" s="74" t="n"/>
-      <c r="K150" s="74" t="n"/>
+      <c r="H150" s="75" t="n"/>
+      <c r="I150" s="75" t="n"/>
+      <c r="J150" s="75" t="n"/>
+      <c r="K150" s="75" t="n"/>
     </row>
     <row r="151" ht="42" customHeight="1">
       <c r="A151" s="32" t="inlineStr">
@@ -26708,15 +26748,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G151" s="74" t="inlineStr">
+      <c r="G151" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H151" s="74" t="n"/>
-      <c r="I151" s="74" t="n"/>
-      <c r="J151" s="74" t="n"/>
-      <c r="K151" s="74" t="n"/>
+      <c r="H151" s="75" t="n"/>
+      <c r="I151" s="75" t="n"/>
+      <c r="J151" s="75" t="n"/>
+      <c r="K151" s="75" t="n"/>
     </row>
     <row r="152" ht="42" customHeight="1">
       <c r="A152" s="32" t="inlineStr">
@@ -26749,15 +26789,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G152" s="74" t="inlineStr">
+      <c r="G152" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H152" s="74" t="n"/>
-      <c r="I152" s="74" t="n"/>
-      <c r="J152" s="74" t="n"/>
-      <c r="K152" s="74" t="n"/>
+      <c r="H152" s="75" t="n"/>
+      <c r="I152" s="75" t="n"/>
+      <c r="J152" s="75" t="n"/>
+      <c r="K152" s="75" t="n"/>
     </row>
     <row r="153" ht="42" customHeight="1">
       <c r="A153" s="32" t="inlineStr">
@@ -26790,15 +26830,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G153" s="74" t="inlineStr">
+      <c r="G153" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H153" s="74" t="n"/>
-      <c r="I153" s="74" t="n"/>
-      <c r="J153" s="74" t="n"/>
-      <c r="K153" s="74" t="n"/>
+      <c r="H153" s="75" t="n"/>
+      <c r="I153" s="75" t="n"/>
+      <c r="J153" s="75" t="n"/>
+      <c r="K153" s="75" t="n"/>
     </row>
     <row r="154" ht="42" customHeight="1">
       <c r="A154" s="32" t="inlineStr">
@@ -26831,15 +26871,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G154" s="74" t="inlineStr">
+      <c r="G154" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H154" s="74" t="n"/>
-      <c r="I154" s="74" t="n"/>
-      <c r="J154" s="74" t="n"/>
-      <c r="K154" s="74" t="n"/>
+      <c r="H154" s="75" t="n"/>
+      <c r="I154" s="75" t="n"/>
+      <c r="J154" s="75" t="n"/>
+      <c r="K154" s="75" t="n"/>
     </row>
     <row r="155" ht="42" customHeight="1">
       <c r="A155" s="32" t="inlineStr">
@@ -26872,15 +26912,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G155" s="74" t="inlineStr">
+      <c r="G155" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H155" s="74" t="n"/>
-      <c r="I155" s="74" t="n"/>
-      <c r="J155" s="74" t="n"/>
-      <c r="K155" s="74" t="n"/>
+      <c r="H155" s="75" t="n"/>
+      <c r="I155" s="75" t="n"/>
+      <c r="J155" s="75" t="n"/>
+      <c r="K155" s="75" t="n"/>
     </row>
     <row r="156" ht="42" customHeight="1">
       <c r="A156" s="32" t="inlineStr">
@@ -26913,15 +26953,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G156" s="74" t="inlineStr">
+      <c r="G156" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H156" s="74" t="n"/>
-      <c r="I156" s="74" t="n"/>
-      <c r="J156" s="74" t="n"/>
-      <c r="K156" s="74" t="n"/>
+      <c r="H156" s="75" t="n"/>
+      <c r="I156" s="75" t="n"/>
+      <c r="J156" s="75" t="n"/>
+      <c r="K156" s="75" t="n"/>
     </row>
     <row r="157" ht="42" customHeight="1">
       <c r="A157" s="32" t="inlineStr">
@@ -26954,15 +26994,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G157" s="74" t="inlineStr">
+      <c r="G157" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H157" s="74" t="n"/>
-      <c r="I157" s="74" t="n"/>
-      <c r="J157" s="74" t="n"/>
-      <c r="K157" s="74" t="n"/>
+      <c r="H157" s="75" t="n"/>
+      <c r="I157" s="75" t="n"/>
+      <c r="J157" s="75" t="n"/>
+      <c r="K157" s="75" t="n"/>
     </row>
     <row r="158" ht="42" customHeight="1">
       <c r="A158" s="32" t="inlineStr">
@@ -26995,15 +27035,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G158" s="74" t="inlineStr">
+      <c r="G158" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H158" s="74" t="n"/>
-      <c r="I158" s="74" t="n"/>
-      <c r="J158" s="74" t="n"/>
-      <c r="K158" s="74" t="n"/>
+      <c r="H158" s="75" t="n"/>
+      <c r="I158" s="75" t="n"/>
+      <c r="J158" s="75" t="n"/>
+      <c r="K158" s="75" t="n"/>
     </row>
     <row r="159" ht="42" customHeight="1">
       <c r="A159" s="32" t="inlineStr">
@@ -27036,15 +27076,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G159" s="74" t="inlineStr">
+      <c r="G159" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H159" s="74" t="n"/>
-      <c r="I159" s="74" t="n"/>
-      <c r="J159" s="74" t="n"/>
-      <c r="K159" s="74" t="n"/>
+      <c r="H159" s="75" t="n"/>
+      <c r="I159" s="75" t="n"/>
+      <c r="J159" s="75" t="n"/>
+      <c r="K159" s="75" t="n"/>
     </row>
     <row r="160" ht="42" customHeight="1">
       <c r="A160" s="32" t="inlineStr">
@@ -27077,15 +27117,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G160" s="74" t="inlineStr">
+      <c r="G160" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H160" s="74" t="n"/>
-      <c r="I160" s="74" t="n"/>
-      <c r="J160" s="74" t="n"/>
-      <c r="K160" s="74" t="n"/>
+      <c r="H160" s="75" t="n"/>
+      <c r="I160" s="75" t="n"/>
+      <c r="J160" s="75" t="n"/>
+      <c r="K160" s="75" t="n"/>
     </row>
     <row r="161" ht="42" customHeight="1">
       <c r="A161" s="32" t="inlineStr">
@@ -27118,15 +27158,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G161" s="74" t="inlineStr">
+      <c r="G161" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H161" s="74" t="n"/>
-      <c r="I161" s="74" t="n"/>
-      <c r="J161" s="74" t="n"/>
-      <c r="K161" s="74" t="n"/>
+      <c r="H161" s="75" t="n"/>
+      <c r="I161" s="75" t="n"/>
+      <c r="J161" s="75" t="n"/>
+      <c r="K161" s="75" t="n"/>
     </row>
     <row r="162" ht="42" customHeight="1">
       <c r="A162" s="32" t="inlineStr">
@@ -27159,15 +27199,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G162" s="74" t="inlineStr">
+      <c r="G162" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H162" s="74" t="n"/>
-      <c r="I162" s="74" t="n"/>
-      <c r="J162" s="74" t="n"/>
-      <c r="K162" s="74" t="n"/>
+      <c r="H162" s="75" t="n"/>
+      <c r="I162" s="75" t="n"/>
+      <c r="J162" s="75" t="n"/>
+      <c r="K162" s="75" t="n"/>
     </row>
     <row r="163" ht="42" customHeight="1">
       <c r="A163" s="32" t="inlineStr">
@@ -27200,15 +27240,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G163" s="74" t="inlineStr">
+      <c r="G163" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H163" s="74" t="n"/>
-      <c r="I163" s="74" t="n"/>
-      <c r="J163" s="74" t="n"/>
-      <c r="K163" s="74" t="n"/>
+      <c r="H163" s="75" t="n"/>
+      <c r="I163" s="75" t="n"/>
+      <c r="J163" s="75" t="n"/>
+      <c r="K163" s="75" t="n"/>
     </row>
     <row r="164" ht="42" customHeight="1">
       <c r="A164" s="32" t="inlineStr">
@@ -27241,15 +27281,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G164" s="74" t="inlineStr">
+      <c r="G164" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H164" s="74" t="n"/>
-      <c r="I164" s="74" t="n"/>
-      <c r="J164" s="74" t="n"/>
-      <c r="K164" s="74" t="n"/>
+      <c r="H164" s="75" t="n"/>
+      <c r="I164" s="75" t="n"/>
+      <c r="J164" s="75" t="n"/>
+      <c r="K164" s="75" t="n"/>
     </row>
     <row r="165" ht="42" customHeight="1">
       <c r="A165" s="32" t="inlineStr">
@@ -27282,15 +27322,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G165" s="74" t="inlineStr">
+      <c r="G165" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H165" s="74" t="n"/>
-      <c r="I165" s="74" t="n"/>
-      <c r="J165" s="74" t="n"/>
-      <c r="K165" s="74" t="n"/>
+      <c r="H165" s="75" t="n"/>
+      <c r="I165" s="75" t="n"/>
+      <c r="J165" s="75" t="n"/>
+      <c r="K165" s="75" t="n"/>
     </row>
     <row r="166" ht="42" customHeight="1">
       <c r="A166" s="32" t="inlineStr">
@@ -27323,15 +27363,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G166" s="74" t="inlineStr">
+      <c r="G166" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H166" s="74" t="n"/>
-      <c r="I166" s="74" t="n"/>
-      <c r="J166" s="74" t="n"/>
-      <c r="K166" s="74" t="n"/>
+      <c r="H166" s="75" t="n"/>
+      <c r="I166" s="75" t="n"/>
+      <c r="J166" s="75" t="n"/>
+      <c r="K166" s="75" t="n"/>
     </row>
     <row r="167" ht="42" customHeight="1">
       <c r="A167" s="32" t="inlineStr">
@@ -27364,15 +27404,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G167" s="74" t="inlineStr">
+      <c r="G167" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H167" s="74" t="n"/>
-      <c r="I167" s="74" t="n"/>
-      <c r="J167" s="74" t="n"/>
-      <c r="K167" s="74" t="n"/>
+      <c r="H167" s="75" t="n"/>
+      <c r="I167" s="75" t="n"/>
+      <c r="J167" s="75" t="n"/>
+      <c r="K167" s="75" t="n"/>
     </row>
     <row r="168" ht="42" customHeight="1">
       <c r="A168" s="32" t="inlineStr">
@@ -27405,15 +27445,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G168" s="74" t="inlineStr">
+      <c r="G168" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H168" s="74" t="n"/>
-      <c r="I168" s="74" t="n"/>
-      <c r="J168" s="74" t="n"/>
-      <c r="K168" s="74" t="n"/>
+      <c r="H168" s="75" t="n"/>
+      <c r="I168" s="75" t="n"/>
+      <c r="J168" s="75" t="n"/>
+      <c r="K168" s="75" t="n"/>
     </row>
     <row r="169" ht="42" customHeight="1">
       <c r="A169" s="32" t="inlineStr">
@@ -27446,15 +27486,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G169" s="74" t="inlineStr">
+      <c r="G169" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H169" s="74" t="n"/>
-      <c r="I169" s="74" t="n"/>
-      <c r="J169" s="74" t="n"/>
-      <c r="K169" s="74" t="n"/>
+      <c r="H169" s="75" t="n"/>
+      <c r="I169" s="75" t="n"/>
+      <c r="J169" s="75" t="n"/>
+      <c r="K169" s="75" t="n"/>
     </row>
     <row r="170" ht="42" customHeight="1">
       <c r="A170" s="32" t="inlineStr">
@@ -27487,15 +27527,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G170" s="74" t="inlineStr">
+      <c r="G170" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H170" s="74" t="n"/>
-      <c r="I170" s="74" t="n"/>
-      <c r="J170" s="74" t="n"/>
-      <c r="K170" s="74" t="n"/>
+      <c r="H170" s="75" t="n"/>
+      <c r="I170" s="75" t="n"/>
+      <c r="J170" s="75" t="n"/>
+      <c r="K170" s="75" t="n"/>
     </row>
     <row r="171" ht="42" customHeight="1">
       <c r="A171" s="32" t="inlineStr">
@@ -27528,15 +27568,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G171" s="74" t="inlineStr">
+      <c r="G171" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H171" s="74" t="n"/>
-      <c r="I171" s="74" t="n"/>
-      <c r="J171" s="74" t="n"/>
-      <c r="K171" s="74" t="n"/>
+      <c r="H171" s="75" t="n"/>
+      <c r="I171" s="75" t="n"/>
+      <c r="J171" s="75" t="n"/>
+      <c r="K171" s="75" t="n"/>
     </row>
     <row r="172" ht="42" customHeight="1">
       <c r="A172" s="32" t="inlineStr">
@@ -27569,15 +27609,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G172" s="74" t="inlineStr">
+      <c r="G172" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H172" s="74" t="n"/>
-      <c r="I172" s="74" t="n"/>
-      <c r="J172" s="74" t="n"/>
-      <c r="K172" s="74" t="n"/>
+      <c r="H172" s="75" t="n"/>
+      <c r="I172" s="75" t="n"/>
+      <c r="J172" s="75" t="n"/>
+      <c r="K172" s="75" t="n"/>
     </row>
     <row r="173" ht="42" customHeight="1">
       <c r="A173" s="32" t="inlineStr">
@@ -27610,15 +27650,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G173" s="74" t="inlineStr">
+      <c r="G173" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H173" s="74" t="n"/>
-      <c r="I173" s="74" t="n"/>
-      <c r="J173" s="74" t="n"/>
-      <c r="K173" s="74" t="n"/>
+      <c r="H173" s="75" t="n"/>
+      <c r="I173" s="75" t="n"/>
+      <c r="J173" s="75" t="n"/>
+      <c r="K173" s="75" t="n"/>
     </row>
     <row r="174" ht="42" customHeight="1">
       <c r="A174" s="32" t="inlineStr">
@@ -27651,15 +27691,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G174" s="74" t="inlineStr">
+      <c r="G174" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H174" s="74" t="n"/>
-      <c r="I174" s="74" t="n"/>
-      <c r="J174" s="74" t="n"/>
-      <c r="K174" s="74" t="n"/>
+      <c r="H174" s="75" t="n"/>
+      <c r="I174" s="75" t="n"/>
+      <c r="J174" s="75" t="n"/>
+      <c r="K174" s="75" t="n"/>
     </row>
     <row r="175" ht="42" customHeight="1">
       <c r="A175" s="32" t="inlineStr">
@@ -27692,15 +27732,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G175" s="74" t="inlineStr">
+      <c r="G175" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H175" s="74" t="n"/>
-      <c r="I175" s="74" t="n"/>
-      <c r="J175" s="74" t="n"/>
-      <c r="K175" s="74" t="n"/>
+      <c r="H175" s="75" t="n"/>
+      <c r="I175" s="75" t="n"/>
+      <c r="J175" s="75" t="n"/>
+      <c r="K175" s="75" t="n"/>
     </row>
     <row r="176" ht="42" customHeight="1">
       <c r="A176" s="32" t="inlineStr">
@@ -27733,15 +27773,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G176" s="74" t="inlineStr">
+      <c r="G176" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H176" s="74" t="n"/>
-      <c r="I176" s="74" t="n"/>
-      <c r="J176" s="74" t="n"/>
-      <c r="K176" s="74" t="n"/>
+      <c r="H176" s="75" t="n"/>
+      <c r="I176" s="75" t="n"/>
+      <c r="J176" s="75" t="n"/>
+      <c r="K176" s="75" t="n"/>
     </row>
     <row r="177" ht="42" customHeight="1">
       <c r="A177" s="32" t="inlineStr">
@@ -27774,15 +27814,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G177" s="74" t="inlineStr">
+      <c r="G177" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H177" s="74" t="n"/>
-      <c r="I177" s="74" t="n"/>
-      <c r="J177" s="74" t="n"/>
-      <c r="K177" s="74" t="n"/>
+      <c r="H177" s="75" t="n"/>
+      <c r="I177" s="75" t="n"/>
+      <c r="J177" s="75" t="n"/>
+      <c r="K177" s="75" t="n"/>
     </row>
     <row r="178" ht="42" customHeight="1">
       <c r="A178" s="32" t="inlineStr">
@@ -27815,15 +27855,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G178" s="74" t="inlineStr">
+      <c r="G178" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H178" s="74" t="n"/>
-      <c r="I178" s="74" t="n"/>
-      <c r="J178" s="74" t="n"/>
-      <c r="K178" s="74" t="n"/>
+      <c r="H178" s="75" t="n"/>
+      <c r="I178" s="75" t="n"/>
+      <c r="J178" s="75" t="n"/>
+      <c r="K178" s="75" t="n"/>
     </row>
     <row r="179" ht="42" customHeight="1">
       <c r="A179" s="32" t="inlineStr">
@@ -27856,15 +27896,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G179" s="74" t="inlineStr">
+      <c r="G179" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H179" s="74" t="n"/>
-      <c r="I179" s="74" t="n"/>
-      <c r="J179" s="74" t="n"/>
-      <c r="K179" s="74" t="n"/>
+      <c r="H179" s="75" t="n"/>
+      <c r="I179" s="75" t="n"/>
+      <c r="J179" s="75" t="n"/>
+      <c r="K179" s="75" t="n"/>
     </row>
     <row r="180" ht="42" customHeight="1">
       <c r="A180" s="32" t="inlineStr">
@@ -27897,15 +27937,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G180" s="74" t="inlineStr">
+      <c r="G180" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H180" s="74" t="n"/>
-      <c r="I180" s="74" t="n"/>
-      <c r="J180" s="74" t="n"/>
-      <c r="K180" s="74" t="n"/>
+      <c r="H180" s="75" t="n"/>
+      <c r="I180" s="75" t="n"/>
+      <c r="J180" s="75" t="n"/>
+      <c r="K180" s="75" t="n"/>
     </row>
     <row r="181" ht="42" customHeight="1">
       <c r="A181" s="32" t="inlineStr">
@@ -27938,15 +27978,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G181" s="74" t="inlineStr">
+      <c r="G181" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H181" s="74" t="n"/>
-      <c r="I181" s="74" t="n"/>
-      <c r="J181" s="74" t="n"/>
-      <c r="K181" s="74" t="n"/>
+      <c r="H181" s="75" t="n"/>
+      <c r="I181" s="75" t="n"/>
+      <c r="J181" s="75" t="n"/>
+      <c r="K181" s="75" t="n"/>
     </row>
     <row r="182" ht="42" customHeight="1">
       <c r="A182" s="32" t="inlineStr">
@@ -27979,15 +28019,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G182" s="74" t="inlineStr">
+      <c r="G182" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H182" s="74" t="n"/>
-      <c r="I182" s="74" t="n"/>
-      <c r="J182" s="74" t="n"/>
-      <c r="K182" s="74" t="n"/>
+      <c r="H182" s="75" t="n"/>
+      <c r="I182" s="75" t="n"/>
+      <c r="J182" s="75" t="n"/>
+      <c r="K182" s="75" t="n"/>
     </row>
     <row r="183" ht="42" customHeight="1">
       <c r="A183" s="32" t="inlineStr">
@@ -28020,15 +28060,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G183" s="74" t="inlineStr">
+      <c r="G183" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H183" s="74" t="n"/>
-      <c r="I183" s="74" t="n"/>
-      <c r="J183" s="74" t="n"/>
-      <c r="K183" s="74" t="n"/>
+      <c r="H183" s="75" t="n"/>
+      <c r="I183" s="75" t="n"/>
+      <c r="J183" s="75" t="n"/>
+      <c r="K183" s="75" t="n"/>
     </row>
     <row r="184" ht="42" customHeight="1">
       <c r="A184" s="32" t="inlineStr">
@@ -28061,15 +28101,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G184" s="74" t="inlineStr">
+      <c r="G184" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H184" s="74" t="n"/>
-      <c r="I184" s="74" t="n"/>
-      <c r="J184" s="74" t="n"/>
-      <c r="K184" s="74" t="n"/>
+      <c r="H184" s="75" t="n"/>
+      <c r="I184" s="75" t="n"/>
+      <c r="J184" s="75" t="n"/>
+      <c r="K184" s="75" t="n"/>
     </row>
     <row r="185" ht="42" customHeight="1">
       <c r="A185" s="32" t="inlineStr">
@@ -28102,15 +28142,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G185" s="74" t="inlineStr">
+      <c r="G185" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H185" s="74" t="n"/>
-      <c r="I185" s="74" t="n"/>
-      <c r="J185" s="74" t="n"/>
-      <c r="K185" s="74" t="n"/>
+      <c r="H185" s="75" t="n"/>
+      <c r="I185" s="75" t="n"/>
+      <c r="J185" s="75" t="n"/>
+      <c r="K185" s="75" t="n"/>
     </row>
     <row r="186" ht="42" customHeight="1">
       <c r="A186" s="32" t="inlineStr">
@@ -28143,15 +28183,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G186" s="74" t="inlineStr">
+      <c r="G186" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H186" s="74" t="n"/>
-      <c r="I186" s="74" t="n"/>
-      <c r="J186" s="74" t="n"/>
-      <c r="K186" s="74" t="n"/>
+      <c r="H186" s="75" t="n"/>
+      <c r="I186" s="75" t="n"/>
+      <c r="J186" s="75" t="n"/>
+      <c r="K186" s="75" t="n"/>
     </row>
     <row r="187" ht="42" customHeight="1">
       <c r="A187" s="32" t="inlineStr">
@@ -28184,15 +28224,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G187" s="74" t="inlineStr">
+      <c r="G187" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H187" s="74" t="n"/>
-      <c r="I187" s="74" t="n"/>
-      <c r="J187" s="74" t="n"/>
-      <c r="K187" s="74" t="n"/>
+      <c r="H187" s="75" t="n"/>
+      <c r="I187" s="75" t="n"/>
+      <c r="J187" s="75" t="n"/>
+      <c r="K187" s="75" t="n"/>
     </row>
     <row r="188" ht="42" customHeight="1">
       <c r="A188" s="32" t="inlineStr">
@@ -28225,15 +28265,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G188" s="74" t="inlineStr">
+      <c r="G188" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H188" s="74" t="n"/>
-      <c r="I188" s="74" t="n"/>
-      <c r="J188" s="74" t="n"/>
-      <c r="K188" s="74" t="n"/>
+      <c r="H188" s="75" t="n"/>
+      <c r="I188" s="75" t="n"/>
+      <c r="J188" s="75" t="n"/>
+      <c r="K188" s="75" t="n"/>
     </row>
     <row r="189" ht="42" customHeight="1">
       <c r="A189" s="32" t="inlineStr">
@@ -28266,15 +28306,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G189" s="74" t="inlineStr">
+      <c r="G189" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H189" s="74" t="n"/>
-      <c r="I189" s="74" t="n"/>
-      <c r="J189" s="74" t="n"/>
-      <c r="K189" s="74" t="n"/>
+      <c r="H189" s="75" t="n"/>
+      <c r="I189" s="75" t="n"/>
+      <c r="J189" s="75" t="n"/>
+      <c r="K189" s="75" t="n"/>
     </row>
     <row r="190" ht="42" customHeight="1">
       <c r="A190" s="32" t="inlineStr">
@@ -28307,15 +28347,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G190" s="74" t="inlineStr">
+      <c r="G190" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H190" s="74" t="n"/>
-      <c r="I190" s="74" t="n"/>
-      <c r="J190" s="74" t="n"/>
-      <c r="K190" s="74" t="n"/>
+      <c r="H190" s="75" t="n"/>
+      <c r="I190" s="75" t="n"/>
+      <c r="J190" s="75" t="n"/>
+      <c r="K190" s="75" t="n"/>
     </row>
     <row r="191" ht="42" customHeight="1">
       <c r="A191" s="32" t="inlineStr">
@@ -28348,15 +28388,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G191" s="74" t="inlineStr">
+      <c r="G191" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H191" s="74" t="n"/>
-      <c r="I191" s="74" t="n"/>
-      <c r="J191" s="74" t="n"/>
-      <c r="K191" s="74" t="n"/>
+      <c r="H191" s="75" t="n"/>
+      <c r="I191" s="75" t="n"/>
+      <c r="J191" s="75" t="n"/>
+      <c r="K191" s="75" t="n"/>
     </row>
     <row r="192" ht="42" customHeight="1">
       <c r="A192" s="32" t="inlineStr">
@@ -28389,15 +28429,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G192" s="74" t="inlineStr">
+      <c r="G192" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H192" s="74" t="n"/>
-      <c r="I192" s="74" t="n"/>
-      <c r="J192" s="74" t="n"/>
-      <c r="K192" s="74" t="n"/>
+      <c r="H192" s="75" t="n"/>
+      <c r="I192" s="75" t="n"/>
+      <c r="J192" s="75" t="n"/>
+      <c r="K192" s="75" t="n"/>
     </row>
     <row r="193" ht="42" customHeight="1">
       <c r="A193" s="32" t="inlineStr">
@@ -28430,15 +28470,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G193" s="74" t="inlineStr">
+      <c r="G193" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H193" s="74" t="n"/>
-      <c r="I193" s="74" t="n"/>
-      <c r="J193" s="74" t="n"/>
-      <c r="K193" s="74" t="n"/>
+      <c r="H193" s="75" t="n"/>
+      <c r="I193" s="75" t="n"/>
+      <c r="J193" s="75" t="n"/>
+      <c r="K193" s="75" t="n"/>
     </row>
     <row r="194" ht="42" customHeight="1">
       <c r="A194" s="32" t="inlineStr">
@@ -28471,15 +28511,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G194" s="74" t="inlineStr">
+      <c r="G194" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H194" s="74" t="n"/>
-      <c r="I194" s="74" t="n"/>
-      <c r="J194" s="74" t="n"/>
-      <c r="K194" s="74" t="n"/>
+      <c r="H194" s="75" t="n"/>
+      <c r="I194" s="75" t="n"/>
+      <c r="J194" s="75" t="n"/>
+      <c r="K194" s="75" t="n"/>
     </row>
     <row r="195" ht="42" customHeight="1">
       <c r="A195" s="32" t="inlineStr">
@@ -28512,15 +28552,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G195" s="74" t="inlineStr">
+      <c r="G195" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H195" s="74" t="n"/>
-      <c r="I195" s="74" t="n"/>
-      <c r="J195" s="74" t="n"/>
-      <c r="K195" s="74" t="n"/>
+      <c r="H195" s="75" t="n"/>
+      <c r="I195" s="75" t="n"/>
+      <c r="J195" s="75" t="n"/>
+      <c r="K195" s="75" t="n"/>
     </row>
     <row r="196" ht="42" customHeight="1">
       <c r="A196" s="32" t="inlineStr">
@@ -28553,15 +28593,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G196" s="74" t="inlineStr">
+      <c r="G196" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H196" s="74" t="n"/>
-      <c r="I196" s="74" t="n"/>
-      <c r="J196" s="74" t="n"/>
-      <c r="K196" s="74" t="n"/>
+      <c r="H196" s="75" t="n"/>
+      <c r="I196" s="75" t="n"/>
+      <c r="J196" s="75" t="n"/>
+      <c r="K196" s="75" t="n"/>
     </row>
     <row r="197" ht="42" customHeight="1">
       <c r="A197" s="32" t="inlineStr">
@@ -28594,15 +28634,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G197" s="74" t="inlineStr">
+      <c r="G197" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H197" s="74" t="n"/>
-      <c r="I197" s="74" t="n"/>
-      <c r="J197" s="74" t="n"/>
-      <c r="K197" s="74" t="n"/>
+      <c r="H197" s="75" t="n"/>
+      <c r="I197" s="75" t="n"/>
+      <c r="J197" s="75" t="n"/>
+      <c r="K197" s="75" t="n"/>
     </row>
     <row r="198" ht="42" customHeight="1">
       <c r="A198" s="32" t="inlineStr">
@@ -28635,15 +28675,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G198" s="74" t="inlineStr">
+      <c r="G198" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H198" s="74" t="n"/>
-      <c r="I198" s="74" t="n"/>
-      <c r="J198" s="74" t="n"/>
-      <c r="K198" s="74" t="n"/>
+      <c r="H198" s="75" t="n"/>
+      <c r="I198" s="75" t="n"/>
+      <c r="J198" s="75" t="n"/>
+      <c r="K198" s="75" t="n"/>
     </row>
     <row r="199" ht="42" customHeight="1">
       <c r="A199" s="32" t="inlineStr">
@@ -28676,15 +28716,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G199" s="74" t="inlineStr">
+      <c r="G199" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H199" s="74" t="n"/>
-      <c r="I199" s="74" t="n"/>
-      <c r="J199" s="74" t="n"/>
-      <c r="K199" s="74" t="n"/>
+      <c r="H199" s="75" t="n"/>
+      <c r="I199" s="75" t="n"/>
+      <c r="J199" s="75" t="n"/>
+      <c r="K199" s="75" t="n"/>
     </row>
     <row r="200" ht="42" customHeight="1">
       <c r="A200" s="32" t="inlineStr">
@@ -28717,15 +28757,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G200" s="74" t="inlineStr">
+      <c r="G200" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H200" s="74" t="n"/>
-      <c r="I200" s="74" t="n"/>
-      <c r="J200" s="74" t="n"/>
-      <c r="K200" s="74" t="n"/>
+      <c r="H200" s="75" t="n"/>
+      <c r="I200" s="75" t="n"/>
+      <c r="J200" s="75" t="n"/>
+      <c r="K200" s="75" t="n"/>
     </row>
     <row r="201" ht="42" customHeight="1">
       <c r="A201" s="32" t="inlineStr">
@@ -28758,15 +28798,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G201" s="74" t="inlineStr">
+      <c r="G201" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H201" s="74" t="n"/>
-      <c r="I201" s="74" t="n"/>
-      <c r="J201" s="74" t="n"/>
-      <c r="K201" s="74" t="n"/>
+      <c r="H201" s="75" t="n"/>
+      <c r="I201" s="75" t="n"/>
+      <c r="J201" s="75" t="n"/>
+      <c r="K201" s="75" t="n"/>
     </row>
     <row r="202" ht="42" customHeight="1">
       <c r="A202" s="32" t="inlineStr">
@@ -28799,15 +28839,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G202" s="74" t="inlineStr">
+      <c r="G202" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H202" s="74" t="n"/>
-      <c r="I202" s="74" t="n"/>
-      <c r="J202" s="74" t="n"/>
-      <c r="K202" s="74" t="n"/>
+      <c r="H202" s="75" t="n"/>
+      <c r="I202" s="75" t="n"/>
+      <c r="J202" s="75" t="n"/>
+      <c r="K202" s="75" t="n"/>
     </row>
     <row r="203" ht="42" customHeight="1">
       <c r="A203" s="32" t="inlineStr">
@@ -28840,15 +28880,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G203" s="74" t="inlineStr">
+      <c r="G203" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H203" s="74" t="n"/>
-      <c r="I203" s="74" t="n"/>
-      <c r="J203" s="74" t="n"/>
-      <c r="K203" s="74" t="n"/>
+      <c r="H203" s="75" t="n"/>
+      <c r="I203" s="75" t="n"/>
+      <c r="J203" s="75" t="n"/>
+      <c r="K203" s="75" t="n"/>
     </row>
     <row r="204" ht="42" customHeight="1">
       <c r="A204" s="32" t="inlineStr">
@@ -28881,15 +28921,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G204" s="74" t="inlineStr">
+      <c r="G204" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H204" s="74" t="n"/>
-      <c r="I204" s="74" t="n"/>
-      <c r="J204" s="74" t="n"/>
-      <c r="K204" s="74" t="n"/>
+      <c r="H204" s="75" t="n"/>
+      <c r="I204" s="75" t="n"/>
+      <c r="J204" s="75" t="n"/>
+      <c r="K204" s="75" t="n"/>
     </row>
     <row r="205" ht="42" customHeight="1">
       <c r="A205" s="32" t="inlineStr">
@@ -28922,15 +28962,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G205" s="74" t="inlineStr">
+      <c r="G205" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H205" s="74" t="n"/>
-      <c r="I205" s="74" t="n"/>
-      <c r="J205" s="74" t="n"/>
-      <c r="K205" s="74" t="n"/>
+      <c r="H205" s="75" t="n"/>
+      <c r="I205" s="75" t="n"/>
+      <c r="J205" s="75" t="n"/>
+      <c r="K205" s="75" t="n"/>
     </row>
     <row r="206" ht="42" customHeight="1">
       <c r="A206" s="32" t="inlineStr">
@@ -28963,15 +29003,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G206" s="74" t="inlineStr">
+      <c r="G206" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H206" s="74" t="n"/>
-      <c r="I206" s="74" t="n"/>
-      <c r="J206" s="74" t="n"/>
-      <c r="K206" s="74" t="n"/>
+      <c r="H206" s="75" t="n"/>
+      <c r="I206" s="75" t="n"/>
+      <c r="J206" s="75" t="n"/>
+      <c r="K206" s="75" t="n"/>
     </row>
     <row r="207" ht="42" customHeight="1">
       <c r="A207" s="32" t="inlineStr">
@@ -29004,15 +29044,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G207" s="74" t="inlineStr">
+      <c r="G207" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H207" s="74" t="n"/>
-      <c r="I207" s="74" t="n"/>
-      <c r="J207" s="74" t="n"/>
-      <c r="K207" s="74" t="n"/>
+      <c r="H207" s="75" t="n"/>
+      <c r="I207" s="75" t="n"/>
+      <c r="J207" s="75" t="n"/>
+      <c r="K207" s="75" t="n"/>
     </row>
     <row r="208" ht="42" customHeight="1">
       <c r="A208" s="32" t="inlineStr">
@@ -29045,15 +29085,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G208" s="74" t="inlineStr">
+      <c r="G208" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H208" s="74" t="n"/>
-      <c r="I208" s="74" t="n"/>
-      <c r="J208" s="74" t="n"/>
-      <c r="K208" s="74" t="n"/>
+      <c r="H208" s="75" t="n"/>
+      <c r="I208" s="75" t="n"/>
+      <c r="J208" s="75" t="n"/>
+      <c r="K208" s="75" t="n"/>
     </row>
     <row r="209" ht="42" customHeight="1">
       <c r="A209" s="32" t="inlineStr">
@@ -29086,15 +29126,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G209" s="74" t="inlineStr">
+      <c r="G209" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H209" s="74" t="n"/>
-      <c r="I209" s="74" t="n"/>
-      <c r="J209" s="74" t="n"/>
-      <c r="K209" s="74" t="n"/>
+      <c r="H209" s="75" t="n"/>
+      <c r="I209" s="75" t="n"/>
+      <c r="J209" s="75" t="n"/>
+      <c r="K209" s="75" t="n"/>
     </row>
     <row r="210" ht="42" customHeight="1">
       <c r="A210" s="32" t="inlineStr">
@@ -29127,15 +29167,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G210" s="74" t="inlineStr">
+      <c r="G210" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H210" s="74" t="n"/>
-      <c r="I210" s="74" t="n"/>
-      <c r="J210" s="74" t="n"/>
-      <c r="K210" s="74" t="n"/>
+      <c r="H210" s="75" t="n"/>
+      <c r="I210" s="75" t="n"/>
+      <c r="J210" s="75" t="n"/>
+      <c r="K210" s="75" t="n"/>
     </row>
     <row r="211" ht="42" customHeight="1">
       <c r="A211" s="32" t="inlineStr">
@@ -29168,15 +29208,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G211" s="74" t="inlineStr">
+      <c r="G211" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H211" s="74" t="n"/>
-      <c r="I211" s="74" t="n"/>
-      <c r="J211" s="74" t="n"/>
-      <c r="K211" s="74" t="n"/>
+      <c r="H211" s="75" t="n"/>
+      <c r="I211" s="75" t="n"/>
+      <c r="J211" s="75" t="n"/>
+      <c r="K211" s="75" t="n"/>
     </row>
     <row r="212" ht="42" customHeight="1">
       <c r="A212" s="32" t="inlineStr">
@@ -29209,15 +29249,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G212" s="74" t="inlineStr">
+      <c r="G212" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H212" s="74" t="n"/>
-      <c r="I212" s="74" t="n"/>
-      <c r="J212" s="74" t="n"/>
-      <c r="K212" s="74" t="n"/>
+      <c r="H212" s="75" t="n"/>
+      <c r="I212" s="75" t="n"/>
+      <c r="J212" s="75" t="n"/>
+      <c r="K212" s="75" t="n"/>
     </row>
     <row r="213" ht="42" customHeight="1">
       <c r="A213" s="32" t="inlineStr">
@@ -29250,15 +29290,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G213" s="74" t="inlineStr">
+      <c r="G213" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H213" s="74" t="n"/>
-      <c r="I213" s="74" t="n"/>
-      <c r="J213" s="74" t="n"/>
-      <c r="K213" s="74" t="n"/>
+      <c r="H213" s="75" t="n"/>
+      <c r="I213" s="75" t="n"/>
+      <c r="J213" s="75" t="n"/>
+      <c r="K213" s="75" t="n"/>
     </row>
     <row r="214" ht="42" customHeight="1">
       <c r="A214" s="32" t="inlineStr">
@@ -29291,15 +29331,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G214" s="74" t="inlineStr">
+      <c r="G214" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H214" s="74" t="n"/>
-      <c r="I214" s="74" t="n"/>
-      <c r="J214" s="74" t="n"/>
-      <c r="K214" s="74" t="n"/>
+      <c r="H214" s="75" t="n"/>
+      <c r="I214" s="75" t="n"/>
+      <c r="J214" s="75" t="n"/>
+      <c r="K214" s="75" t="n"/>
     </row>
     <row r="215" ht="42" customHeight="1">
       <c r="A215" s="32" t="inlineStr">
@@ -29332,15 +29372,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G215" s="74" t="inlineStr">
+      <c r="G215" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H215" s="74" t="n"/>
-      <c r="I215" s="74" t="n"/>
-      <c r="J215" s="74" t="n"/>
-      <c r="K215" s="74" t="n"/>
+      <c r="H215" s="75" t="n"/>
+      <c r="I215" s="75" t="n"/>
+      <c r="J215" s="75" t="n"/>
+      <c r="K215" s="75" t="n"/>
     </row>
     <row r="216" ht="42" customHeight="1">
       <c r="A216" s="32" t="inlineStr">
@@ -29373,15 +29413,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G216" s="74" t="inlineStr">
+      <c r="G216" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H216" s="74" t="n"/>
-      <c r="I216" s="74" t="n"/>
-      <c r="J216" s="74" t="n"/>
-      <c r="K216" s="74" t="n"/>
+      <c r="H216" s="75" t="n"/>
+      <c r="I216" s="75" t="n"/>
+      <c r="J216" s="75" t="n"/>
+      <c r="K216" s="75" t="n"/>
     </row>
     <row r="217" ht="42" customHeight="1">
       <c r="A217" s="32" t="inlineStr">
@@ -29414,15 +29454,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G217" s="74" t="inlineStr">
+      <c r="G217" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H217" s="74" t="n"/>
-      <c r="I217" s="74" t="n"/>
-      <c r="J217" s="74" t="n"/>
-      <c r="K217" s="74" t="n"/>
+      <c r="H217" s="75" t="n"/>
+      <c r="I217" s="75" t="n"/>
+      <c r="J217" s="75" t="n"/>
+      <c r="K217" s="75" t="n"/>
     </row>
     <row r="218" ht="42" customHeight="1">
       <c r="A218" s="32" t="inlineStr">
@@ -29455,15 +29495,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G218" s="74" t="inlineStr">
+      <c r="G218" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H218" s="74" t="n"/>
-      <c r="I218" s="74" t="n"/>
-      <c r="J218" s="74" t="n"/>
-      <c r="K218" s="74" t="n"/>
+      <c r="H218" s="75" t="n"/>
+      <c r="I218" s="75" t="n"/>
+      <c r="J218" s="75" t="n"/>
+      <c r="K218" s="75" t="n"/>
     </row>
     <row r="219" ht="42" customHeight="1">
       <c r="A219" s="32" t="inlineStr">
@@ -29496,15 +29536,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G219" s="74" t="inlineStr">
+      <c r="G219" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H219" s="74" t="n"/>
-      <c r="I219" s="74" t="n"/>
-      <c r="J219" s="74" t="n"/>
-      <c r="K219" s="74" t="n"/>
+      <c r="H219" s="75" t="n"/>
+      <c r="I219" s="75" t="n"/>
+      <c r="J219" s="75" t="n"/>
+      <c r="K219" s="75" t="n"/>
     </row>
     <row r="220" ht="42" customHeight="1">
       <c r="A220" s="32" t="inlineStr">
@@ -29537,15 +29577,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G220" s="74" t="inlineStr">
+      <c r="G220" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H220" s="74" t="n"/>
-      <c r="I220" s="74" t="n"/>
-      <c r="J220" s="74" t="n"/>
-      <c r="K220" s="74" t="n"/>
+      <c r="H220" s="75" t="n"/>
+      <c r="I220" s="75" t="n"/>
+      <c r="J220" s="75" t="n"/>
+      <c r="K220" s="75" t="n"/>
     </row>
     <row r="221" ht="42" customHeight="1">
       <c r="A221" s="32" t="inlineStr">
@@ -29578,15 +29618,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G221" s="74" t="inlineStr">
+      <c r="G221" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H221" s="74" t="n"/>
-      <c r="I221" s="74" t="n"/>
-      <c r="J221" s="74" t="n"/>
-      <c r="K221" s="74" t="n"/>
+      <c r="H221" s="75" t="n"/>
+      <c r="I221" s="75" t="n"/>
+      <c r="J221" s="75" t="n"/>
+      <c r="K221" s="75" t="n"/>
     </row>
     <row r="222" ht="42" customHeight="1">
       <c r="A222" s="32" t="inlineStr">
@@ -29619,15 +29659,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G222" s="74" t="inlineStr">
+      <c r="G222" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H222" s="74" t="n"/>
-      <c r="I222" s="74" t="n"/>
-      <c r="J222" s="74" t="n"/>
-      <c r="K222" s="74" t="n"/>
+      <c r="H222" s="75" t="n"/>
+      <c r="I222" s="75" t="n"/>
+      <c r="J222" s="75" t="n"/>
+      <c r="K222" s="75" t="n"/>
     </row>
     <row r="223" ht="42" customHeight="1">
       <c r="A223" s="32" t="inlineStr">
@@ -29660,15 +29700,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G223" s="74" t="inlineStr">
+      <c r="G223" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H223" s="74" t="n"/>
-      <c r="I223" s="74" t="n"/>
-      <c r="J223" s="74" t="n"/>
-      <c r="K223" s="74" t="n"/>
+      <c r="H223" s="75" t="n"/>
+      <c r="I223" s="75" t="n"/>
+      <c r="J223" s="75" t="n"/>
+      <c r="K223" s="75" t="n"/>
     </row>
     <row r="224" ht="42" customHeight="1">
       <c r="A224" s="32" t="inlineStr">
@@ -29701,15 +29741,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G224" s="74" t="inlineStr">
+      <c r="G224" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H224" s="74" t="n"/>
-      <c r="I224" s="74" t="n"/>
-      <c r="J224" s="74" t="n"/>
-      <c r="K224" s="74" t="n"/>
+      <c r="H224" s="75" t="n"/>
+      <c r="I224" s="75" t="n"/>
+      <c r="J224" s="75" t="n"/>
+      <c r="K224" s="75" t="n"/>
     </row>
     <row r="225" ht="42" customHeight="1">
       <c r="A225" s="32" t="inlineStr">
@@ -29742,15 +29782,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G225" s="74" t="inlineStr">
+      <c r="G225" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H225" s="74" t="n"/>
-      <c r="I225" s="74" t="n"/>
-      <c r="J225" s="74" t="n"/>
-      <c r="K225" s="74" t="n"/>
+      <c r="H225" s="75" t="n"/>
+      <c r="I225" s="75" t="n"/>
+      <c r="J225" s="75" t="n"/>
+      <c r="K225" s="75" t="n"/>
     </row>
     <row r="226" ht="42" customHeight="1">
       <c r="A226" s="32" t="inlineStr">
@@ -29783,15 +29823,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G226" s="74" t="inlineStr">
+      <c r="G226" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H226" s="74" t="n"/>
-      <c r="I226" s="74" t="n"/>
-      <c r="J226" s="74" t="n"/>
-      <c r="K226" s="74" t="n"/>
+      <c r="H226" s="75" t="n"/>
+      <c r="I226" s="75" t="n"/>
+      <c r="J226" s="75" t="n"/>
+      <c r="K226" s="75" t="n"/>
     </row>
     <row r="227" ht="42" customHeight="1">
       <c r="A227" s="32" t="inlineStr">
@@ -29824,15 +29864,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G227" s="74" t="inlineStr">
+      <c r="G227" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H227" s="74" t="n"/>
-      <c r="I227" s="74" t="n"/>
-      <c r="J227" s="74" t="n"/>
-      <c r="K227" s="74" t="n"/>
+      <c r="H227" s="75" t="n"/>
+      <c r="I227" s="75" t="n"/>
+      <c r="J227" s="75" t="n"/>
+      <c r="K227" s="75" t="n"/>
     </row>
     <row r="228" ht="42" customHeight="1">
       <c r="A228" s="32" t="inlineStr">
@@ -29865,15 +29905,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G228" s="74" t="inlineStr">
+      <c r="G228" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H228" s="74" t="n"/>
-      <c r="I228" s="74" t="n"/>
-      <c r="J228" s="74" t="n"/>
-      <c r="K228" s="74" t="n"/>
+      <c r="H228" s="75" t="n"/>
+      <c r="I228" s="75" t="n"/>
+      <c r="J228" s="75" t="n"/>
+      <c r="K228" s="75" t="n"/>
     </row>
     <row r="229" ht="42" customHeight="1">
       <c r="A229" s="32" t="inlineStr">
@@ -29906,15 +29946,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G229" s="74" t="inlineStr">
+      <c r="G229" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H229" s="74" t="n"/>
-      <c r="I229" s="74" t="n"/>
-      <c r="J229" s="74" t="n"/>
-      <c r="K229" s="74" t="n"/>
+      <c r="H229" s="75" t="n"/>
+      <c r="I229" s="75" t="n"/>
+      <c r="J229" s="75" t="n"/>
+      <c r="K229" s="75" t="n"/>
     </row>
     <row r="230" ht="42" customHeight="1">
       <c r="A230" s="32" t="inlineStr">
@@ -29947,15 +29987,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G230" s="74" t="inlineStr">
+      <c r="G230" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H230" s="74" t="n"/>
-      <c r="I230" s="74" t="n"/>
-      <c r="J230" s="74" t="n"/>
-      <c r="K230" s="74" t="n"/>
+      <c r="H230" s="75" t="n"/>
+      <c r="I230" s="75" t="n"/>
+      <c r="J230" s="75" t="n"/>
+      <c r="K230" s="75" t="n"/>
     </row>
     <row r="231" ht="42" customHeight="1">
       <c r="A231" s="32" t="inlineStr">
@@ -29988,15 +30028,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G231" s="74" t="inlineStr">
+      <c r="G231" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H231" s="74" t="n"/>
-      <c r="I231" s="74" t="n"/>
-      <c r="J231" s="74" t="n"/>
-      <c r="K231" s="74" t="n"/>
+      <c r="H231" s="75" t="n"/>
+      <c r="I231" s="75" t="n"/>
+      <c r="J231" s="75" t="n"/>
+      <c r="K231" s="75" t="n"/>
     </row>
     <row r="232" ht="42" customHeight="1">
       <c r="A232" s="32" t="inlineStr">
@@ -30029,15 +30069,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G232" s="74" t="inlineStr">
+      <c r="G232" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H232" s="74" t="n"/>
-      <c r="I232" s="74" t="n"/>
-      <c r="J232" s="74" t="n"/>
-      <c r="K232" s="74" t="n"/>
+      <c r="H232" s="75" t="n"/>
+      <c r="I232" s="75" t="n"/>
+      <c r="J232" s="75" t="n"/>
+      <c r="K232" s="75" t="n"/>
     </row>
     <row r="233" ht="42" customHeight="1">
       <c r="A233" s="32" t="inlineStr">
@@ -30070,15 +30110,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G233" s="74" t="inlineStr">
+      <c r="G233" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H233" s="74" t="n"/>
-      <c r="I233" s="74" t="n"/>
-      <c r="J233" s="74" t="n"/>
-      <c r="K233" s="74" t="n"/>
+      <c r="H233" s="75" t="n"/>
+      <c r="I233" s="75" t="n"/>
+      <c r="J233" s="75" t="n"/>
+      <c r="K233" s="75" t="n"/>
     </row>
     <row r="234" ht="42" customHeight="1">
       <c r="A234" s="32" t="inlineStr">
@@ -30111,15 +30151,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G234" s="74" t="inlineStr">
+      <c r="G234" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H234" s="74" t="n"/>
-      <c r="I234" s="74" t="n"/>
-      <c r="J234" s="74" t="n"/>
-      <c r="K234" s="74" t="n"/>
+      <c r="H234" s="75" t="n"/>
+      <c r="I234" s="75" t="n"/>
+      <c r="J234" s="75" t="n"/>
+      <c r="K234" s="75" t="n"/>
     </row>
     <row r="235" ht="42" customHeight="1">
       <c r="A235" s="32" t="inlineStr">
@@ -30152,15 +30192,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G235" s="74" t="inlineStr">
+      <c r="G235" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H235" s="74" t="n"/>
-      <c r="I235" s="74" t="n"/>
-      <c r="J235" s="74" t="n"/>
-      <c r="K235" s="74" t="n"/>
+      <c r="H235" s="75" t="n"/>
+      <c r="I235" s="75" t="n"/>
+      <c r="J235" s="75" t="n"/>
+      <c r="K235" s="75" t="n"/>
     </row>
     <row r="236" ht="42" customHeight="1">
       <c r="A236" s="32" t="inlineStr">
@@ -30193,15 +30233,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G236" s="74" t="inlineStr">
+      <c r="G236" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H236" s="74" t="n"/>
-      <c r="I236" s="74" t="n"/>
-      <c r="J236" s="74" t="n"/>
-      <c r="K236" s="74" t="n"/>
+      <c r="H236" s="75" t="n"/>
+      <c r="I236" s="75" t="n"/>
+      <c r="J236" s="75" t="n"/>
+      <c r="K236" s="75" t="n"/>
     </row>
     <row r="237" ht="42" customHeight="1">
       <c r="A237" s="32" t="inlineStr">
@@ -30234,15 +30274,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G237" s="74" t="inlineStr">
+      <c r="G237" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H237" s="74" t="n"/>
-      <c r="I237" s="74" t="n"/>
-      <c r="J237" s="74" t="n"/>
-      <c r="K237" s="74" t="n"/>
+      <c r="H237" s="75" t="n"/>
+      <c r="I237" s="75" t="n"/>
+      <c r="J237" s="75" t="n"/>
+      <c r="K237" s="75" t="n"/>
     </row>
     <row r="238" ht="42" customHeight="1">
       <c r="A238" s="32" t="inlineStr">
@@ -30275,15 +30315,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G238" s="74" t="inlineStr">
+      <c r="G238" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H238" s="74" t="n"/>
-      <c r="I238" s="74" t="n"/>
-      <c r="J238" s="74" t="n"/>
-      <c r="K238" s="74" t="n"/>
+      <c r="H238" s="75" t="n"/>
+      <c r="I238" s="75" t="n"/>
+      <c r="J238" s="75" t="n"/>
+      <c r="K238" s="75" t="n"/>
     </row>
     <row r="239" ht="42" customHeight="1">
       <c r="A239" s="32" t="inlineStr">
@@ -30316,15 +30356,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G239" s="74" t="inlineStr">
+      <c r="G239" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H239" s="74" t="n"/>
-      <c r="I239" s="74" t="n"/>
-      <c r="J239" s="74" t="n"/>
-      <c r="K239" s="74" t="n"/>
+      <c r="H239" s="75" t="n"/>
+      <c r="I239" s="75" t="n"/>
+      <c r="J239" s="75" t="n"/>
+      <c r="K239" s="75" t="n"/>
     </row>
     <row r="240" ht="42" customHeight="1">
       <c r="A240" s="32" t="inlineStr">
@@ -30357,15 +30397,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G240" s="74" t="inlineStr">
+      <c r="G240" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H240" s="74" t="n"/>
-      <c r="I240" s="74" t="n"/>
-      <c r="J240" s="74" t="n"/>
-      <c r="K240" s="74" t="n"/>
+      <c r="H240" s="75" t="n"/>
+      <c r="I240" s="75" t="n"/>
+      <c r="J240" s="75" t="n"/>
+      <c r="K240" s="75" t="n"/>
     </row>
     <row r="241" ht="42" customHeight="1">
       <c r="A241" s="32" t="inlineStr">
@@ -30398,15 +30438,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G241" s="74" t="inlineStr">
+      <c r="G241" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H241" s="74" t="n"/>
-      <c r="I241" s="74" t="n"/>
-      <c r="J241" s="74" t="n"/>
-      <c r="K241" s="74" t="n"/>
+      <c r="H241" s="75" t="n"/>
+      <c r="I241" s="75" t="n"/>
+      <c r="J241" s="75" t="n"/>
+      <c r="K241" s="75" t="n"/>
     </row>
     <row r="242" ht="42" customHeight="1">
       <c r="A242" s="32" t="inlineStr">
@@ -30439,15 +30479,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G242" s="74" t="inlineStr">
+      <c r="G242" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H242" s="74" t="n"/>
-      <c r="I242" s="74" t="n"/>
-      <c r="J242" s="74" t="n"/>
-      <c r="K242" s="74" t="n"/>
+      <c r="H242" s="75" t="n"/>
+      <c r="I242" s="75" t="n"/>
+      <c r="J242" s="75" t="n"/>
+      <c r="K242" s="75" t="n"/>
     </row>
     <row r="243" ht="42" customHeight="1">
       <c r="A243" s="32" t="inlineStr">
@@ -30480,15 +30520,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G243" s="74" t="inlineStr">
+      <c r="G243" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H243" s="74" t="n"/>
-      <c r="I243" s="74" t="n"/>
-      <c r="J243" s="74" t="n"/>
-      <c r="K243" s="74" t="n"/>
+      <c r="H243" s="75" t="n"/>
+      <c r="I243" s="75" t="n"/>
+      <c r="J243" s="75" t="n"/>
+      <c r="K243" s="75" t="n"/>
     </row>
     <row r="244" ht="42" customHeight="1">
       <c r="A244" s="32" t="inlineStr">
@@ -30521,15 +30561,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G244" s="74" t="inlineStr">
+      <c r="G244" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H244" s="74" t="n"/>
-      <c r="I244" s="74" t="n"/>
-      <c r="J244" s="74" t="n"/>
-      <c r="K244" s="74" t="n"/>
+      <c r="H244" s="75" t="n"/>
+      <c r="I244" s="75" t="n"/>
+      <c r="J244" s="75" t="n"/>
+      <c r="K244" s="75" t="n"/>
     </row>
     <row r="245" ht="42" customHeight="1">
       <c r="A245" s="32" t="inlineStr">
@@ -30562,15 +30602,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G245" s="74" t="inlineStr">
+      <c r="G245" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H245" s="74" t="n"/>
-      <c r="I245" s="74" t="n"/>
-      <c r="J245" s="74" t="n"/>
-      <c r="K245" s="74" t="n"/>
+      <c r="H245" s="75" t="n"/>
+      <c r="I245" s="75" t="n"/>
+      <c r="J245" s="75" t="n"/>
+      <c r="K245" s="75" t="n"/>
     </row>
     <row r="246" ht="42" customHeight="1">
       <c r="A246" s="32" t="inlineStr">
@@ -30603,15 +30643,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G246" s="74" t="inlineStr">
+      <c r="G246" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H246" s="74" t="n"/>
-      <c r="I246" s="74" t="n"/>
-      <c r="J246" s="74" t="n"/>
-      <c r="K246" s="74" t="n"/>
+      <c r="H246" s="75" t="n"/>
+      <c r="I246" s="75" t="n"/>
+      <c r="J246" s="75" t="n"/>
+      <c r="K246" s="75" t="n"/>
     </row>
     <row r="247" ht="42" customHeight="1">
       <c r="A247" s="32" t="inlineStr">
@@ -30644,15 +30684,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G247" s="74" t="inlineStr">
+      <c r="G247" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H247" s="74" t="n"/>
-      <c r="I247" s="74" t="n"/>
-      <c r="J247" s="74" t="n"/>
-      <c r="K247" s="74" t="n"/>
+      <c r="H247" s="75" t="n"/>
+      <c r="I247" s="75" t="n"/>
+      <c r="J247" s="75" t="n"/>
+      <c r="K247" s="75" t="n"/>
     </row>
     <row r="248" ht="42" customHeight="1">
       <c r="A248" s="32" t="inlineStr">
@@ -30685,15 +30725,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G248" s="74" t="inlineStr">
+      <c r="G248" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H248" s="74" t="n"/>
-      <c r="I248" s="74" t="n"/>
-      <c r="J248" s="74" t="n"/>
-      <c r="K248" s="74" t="n"/>
+      <c r="H248" s="75" t="n"/>
+      <c r="I248" s="75" t="n"/>
+      <c r="J248" s="75" t="n"/>
+      <c r="K248" s="75" t="n"/>
     </row>
     <row r="249" ht="42" customHeight="1">
       <c r="A249" s="32" t="inlineStr">
@@ -30726,15 +30766,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G249" s="74" t="inlineStr">
+      <c r="G249" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H249" s="74" t="n"/>
-      <c r="I249" s="74" t="n"/>
-      <c r="J249" s="74" t="n"/>
-      <c r="K249" s="74" t="n"/>
+      <c r="H249" s="75" t="n"/>
+      <c r="I249" s="75" t="n"/>
+      <c r="J249" s="75" t="n"/>
+      <c r="K249" s="75" t="n"/>
     </row>
     <row r="250" ht="42" customHeight="1">
       <c r="A250" s="32" t="inlineStr">
@@ -30767,15 +30807,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G250" s="74" t="inlineStr">
+      <c r="G250" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H250" s="74" t="n"/>
-      <c r="I250" s="74" t="n"/>
-      <c r="J250" s="74" t="n"/>
-      <c r="K250" s="74" t="n"/>
+      <c r="H250" s="75" t="n"/>
+      <c r="I250" s="75" t="n"/>
+      <c r="J250" s="75" t="n"/>
+      <c r="K250" s="75" t="n"/>
     </row>
     <row r="251" ht="42" customHeight="1">
       <c r="A251" s="32" t="inlineStr">
@@ -30808,15 +30848,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G251" s="74" t="inlineStr">
+      <c r="G251" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H251" s="74" t="n"/>
-      <c r="I251" s="74" t="n"/>
-      <c r="J251" s="74" t="n"/>
-      <c r="K251" s="74" t="n"/>
+      <c r="H251" s="75" t="n"/>
+      <c r="I251" s="75" t="n"/>
+      <c r="J251" s="75" t="n"/>
+      <c r="K251" s="75" t="n"/>
     </row>
     <row r="252" ht="42" customHeight="1">
       <c r="A252" s="32" t="inlineStr">
@@ -30849,15 +30889,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G252" s="74" t="inlineStr">
+      <c r="G252" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H252" s="74" t="n"/>
-      <c r="I252" s="74" t="n"/>
-      <c r="J252" s="74" t="n"/>
-      <c r="K252" s="74" t="n"/>
+      <c r="H252" s="75" t="n"/>
+      <c r="I252" s="75" t="n"/>
+      <c r="J252" s="75" t="n"/>
+      <c r="K252" s="75" t="n"/>
     </row>
     <row r="253" ht="42" customHeight="1">
       <c r="A253" s="32" t="inlineStr">
@@ -30890,15 +30930,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G253" s="74" t="inlineStr">
+      <c r="G253" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H253" s="74" t="n"/>
-      <c r="I253" s="74" t="n"/>
-      <c r="J253" s="74" t="n"/>
-      <c r="K253" s="74" t="n"/>
+      <c r="H253" s="75" t="n"/>
+      <c r="I253" s="75" t="n"/>
+      <c r="J253" s="75" t="n"/>
+      <c r="K253" s="75" t="n"/>
     </row>
     <row r="254" ht="42" customHeight="1">
       <c r="A254" s="32" t="inlineStr">
@@ -30931,15 +30971,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G254" s="74" t="inlineStr">
+      <c r="G254" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H254" s="74" t="n"/>
-      <c r="I254" s="74" t="n"/>
-      <c r="J254" s="74" t="n"/>
-      <c r="K254" s="74" t="n"/>
+      <c r="H254" s="75" t="n"/>
+      <c r="I254" s="75" t="n"/>
+      <c r="J254" s="75" t="n"/>
+      <c r="K254" s="75" t="n"/>
     </row>
     <row r="255" ht="42" customHeight="1">
       <c r="A255" s="32" t="inlineStr">
@@ -30972,15 +31012,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G255" s="74" t="inlineStr">
+      <c r="G255" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H255" s="74" t="n"/>
-      <c r="I255" s="74" t="n"/>
-      <c r="J255" s="74" t="n"/>
-      <c r="K255" s="74" t="n"/>
+      <c r="H255" s="75" t="n"/>
+      <c r="I255" s="75" t="n"/>
+      <c r="J255" s="75" t="n"/>
+      <c r="K255" s="75" t="n"/>
     </row>
     <row r="256" ht="42" customHeight="1">
       <c r="A256" s="32" t="inlineStr">
@@ -31013,15 +31053,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G256" s="74" t="inlineStr">
+      <c r="G256" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H256" s="74" t="n"/>
-      <c r="I256" s="74" t="n"/>
-      <c r="J256" s="74" t="n"/>
-      <c r="K256" s="74" t="n"/>
+      <c r="H256" s="75" t="n"/>
+      <c r="I256" s="75" t="n"/>
+      <c r="J256" s="75" t="n"/>
+      <c r="K256" s="75" t="n"/>
     </row>
     <row r="257" ht="42" customHeight="1">
       <c r="A257" s="32" t="inlineStr">
@@ -31054,15 +31094,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G257" s="74" t="inlineStr">
+      <c r="G257" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H257" s="74" t="n"/>
-      <c r="I257" s="74" t="n"/>
-      <c r="J257" s="74" t="n"/>
-      <c r="K257" s="74" t="n"/>
+      <c r="H257" s="75" t="n"/>
+      <c r="I257" s="75" t="n"/>
+      <c r="J257" s="75" t="n"/>
+      <c r="K257" s="75" t="n"/>
     </row>
     <row r="258" ht="42" customHeight="1">
       <c r="A258" s="32" t="inlineStr">
@@ -31095,15 +31135,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G258" s="74" t="inlineStr">
+      <c r="G258" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H258" s="74" t="n"/>
-      <c r="I258" s="74" t="n"/>
-      <c r="J258" s="74" t="n"/>
-      <c r="K258" s="74" t="n"/>
+      <c r="H258" s="75" t="n"/>
+      <c r="I258" s="75" t="n"/>
+      <c r="J258" s="75" t="n"/>
+      <c r="K258" s="75" t="n"/>
     </row>
     <row r="259" ht="42" customHeight="1">
       <c r="A259" s="32" t="inlineStr">
@@ -31136,15 +31176,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G259" s="74" t="inlineStr">
+      <c r="G259" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H259" s="74" t="n"/>
-      <c r="I259" s="74" t="n"/>
-      <c r="J259" s="74" t="n"/>
-      <c r="K259" s="74" t="n"/>
+      <c r="H259" s="75" t="n"/>
+      <c r="I259" s="75" t="n"/>
+      <c r="J259" s="75" t="n"/>
+      <c r="K259" s="75" t="n"/>
     </row>
     <row r="260" ht="42" customHeight="1">
       <c r="A260" s="32" t="inlineStr">
@@ -31177,15 +31217,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G260" s="74" t="inlineStr">
+      <c r="G260" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H260" s="74" t="n"/>
-      <c r="I260" s="74" t="n"/>
-      <c r="J260" s="74" t="n"/>
-      <c r="K260" s="74" t="n"/>
+      <c r="H260" s="75" t="n"/>
+      <c r="I260" s="75" t="n"/>
+      <c r="J260" s="75" t="n"/>
+      <c r="K260" s="75" t="n"/>
     </row>
     <row r="261" ht="42" customHeight="1">
       <c r="A261" s="32" t="inlineStr">
@@ -31218,15 +31258,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G261" s="74" t="inlineStr">
+      <c r="G261" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H261" s="74" t="n"/>
-      <c r="I261" s="74" t="n"/>
-      <c r="J261" s="74" t="n"/>
-      <c r="K261" s="74" t="n"/>
+      <c r="H261" s="75" t="n"/>
+      <c r="I261" s="75" t="n"/>
+      <c r="J261" s="75" t="n"/>
+      <c r="K261" s="75" t="n"/>
     </row>
     <row r="262" ht="42" customHeight="1">
       <c r="A262" s="32" t="inlineStr">
@@ -31259,15 +31299,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G262" s="74" t="inlineStr">
+      <c r="G262" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H262" s="74" t="n"/>
-      <c r="I262" s="74" t="n"/>
-      <c r="J262" s="74" t="n"/>
-      <c r="K262" s="74" t="n"/>
+      <c r="H262" s="75" t="n"/>
+      <c r="I262" s="75" t="n"/>
+      <c r="J262" s="75" t="n"/>
+      <c r="K262" s="75" t="n"/>
     </row>
     <row r="263" ht="42" customHeight="1">
       <c r="A263" s="32" t="inlineStr">
@@ -31300,15 +31340,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G263" s="74" t="inlineStr">
+      <c r="G263" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H263" s="74" t="n"/>
-      <c r="I263" s="74" t="n"/>
-      <c r="J263" s="74" t="n"/>
-      <c r="K263" s="74" t="n"/>
+      <c r="H263" s="75" t="n"/>
+      <c r="I263" s="75" t="n"/>
+      <c r="J263" s="75" t="n"/>
+      <c r="K263" s="75" t="n"/>
     </row>
     <row r="264" ht="42" customHeight="1">
       <c r="A264" s="32" t="inlineStr">
@@ -31341,15 +31381,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G264" s="74" t="inlineStr">
+      <c r="G264" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H264" s="74" t="n"/>
-      <c r="I264" s="74" t="n"/>
-      <c r="J264" s="74" t="n"/>
-      <c r="K264" s="74" t="n"/>
+      <c r="H264" s="75" t="n"/>
+      <c r="I264" s="75" t="n"/>
+      <c r="J264" s="75" t="n"/>
+      <c r="K264" s="75" t="n"/>
     </row>
     <row r="265" ht="42" customHeight="1">
       <c r="A265" s="32" t="inlineStr">
@@ -31382,15 +31422,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G265" s="74" t="inlineStr">
+      <c r="G265" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H265" s="74" t="n"/>
-      <c r="I265" s="74" t="n"/>
-      <c r="J265" s="74" t="n"/>
-      <c r="K265" s="74" t="n"/>
+      <c r="H265" s="75" t="n"/>
+      <c r="I265" s="75" t="n"/>
+      <c r="J265" s="75" t="n"/>
+      <c r="K265" s="75" t="n"/>
     </row>
     <row r="266" ht="42" customHeight="1">
       <c r="A266" s="32" t="inlineStr">
@@ -31423,15 +31463,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G266" s="74" t="inlineStr">
+      <c r="G266" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H266" s="74" t="n"/>
-      <c r="I266" s="74" t="n"/>
-      <c r="J266" s="74" t="n"/>
-      <c r="K266" s="74" t="n"/>
+      <c r="H266" s="75" t="n"/>
+      <c r="I266" s="75" t="n"/>
+      <c r="J266" s="75" t="n"/>
+      <c r="K266" s="75" t="n"/>
     </row>
     <row r="267" ht="42" customHeight="1">
       <c r="A267" s="32" t="inlineStr">
@@ -31464,15 +31504,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G267" s="74" t="inlineStr">
+      <c r="G267" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H267" s="74" t="n"/>
-      <c r="I267" s="74" t="n"/>
-      <c r="J267" s="74" t="n"/>
-      <c r="K267" s="74" t="n"/>
+      <c r="H267" s="75" t="n"/>
+      <c r="I267" s="75" t="n"/>
+      <c r="J267" s="75" t="n"/>
+      <c r="K267" s="75" t="n"/>
     </row>
     <row r="268" ht="42" customHeight="1">
       <c r="A268" s="32" t="inlineStr">
@@ -31505,15 +31545,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G268" s="74" t="inlineStr">
+      <c r="G268" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H268" s="74" t="n"/>
-      <c r="I268" s="74" t="n"/>
-      <c r="J268" s="74" t="n"/>
-      <c r="K268" s="74" t="n"/>
+      <c r="H268" s="75" t="n"/>
+      <c r="I268" s="75" t="n"/>
+      <c r="J268" s="75" t="n"/>
+      <c r="K268" s="75" t="n"/>
     </row>
     <row r="269" ht="42" customHeight="1">
       <c r="A269" s="32" t="inlineStr">
@@ -31546,15 +31586,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G269" s="74" t="inlineStr">
+      <c r="G269" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H269" s="74" t="n"/>
-      <c r="I269" s="74" t="n"/>
-      <c r="J269" s="74" t="n"/>
-      <c r="K269" s="74" t="n"/>
+      <c r="H269" s="75" t="n"/>
+      <c r="I269" s="75" t="n"/>
+      <c r="J269" s="75" t="n"/>
+      <c r="K269" s="75" t="n"/>
     </row>
     <row r="270" ht="42" customHeight="1">
       <c r="A270" s="32" t="inlineStr">
@@ -31587,15 +31627,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G270" s="74" t="inlineStr">
+      <c r="G270" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H270" s="74" t="n"/>
-      <c r="I270" s="74" t="n"/>
-      <c r="J270" s="74" t="n"/>
-      <c r="K270" s="74" t="n"/>
+      <c r="H270" s="75" t="n"/>
+      <c r="I270" s="75" t="n"/>
+      <c r="J270" s="75" t="n"/>
+      <c r="K270" s="75" t="n"/>
     </row>
     <row r="271" ht="42" customHeight="1">
       <c r="A271" s="32" t="inlineStr">
@@ -31628,15 +31668,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G271" s="74" t="inlineStr">
+      <c r="G271" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H271" s="74" t="n"/>
-      <c r="I271" s="74" t="n"/>
-      <c r="J271" s="74" t="n"/>
-      <c r="K271" s="74" t="n"/>
+      <c r="H271" s="75" t="n"/>
+      <c r="I271" s="75" t="n"/>
+      <c r="J271" s="75" t="n"/>
+      <c r="K271" s="75" t="n"/>
     </row>
     <row r="272" ht="42" customHeight="1">
       <c r="A272" s="32" t="inlineStr">
@@ -31669,15 +31709,15 @@
           <t>Provisional</t>
         </is>
       </c>
-      <c r="G272" s="74" t="inlineStr">
+      <c r="G272" s="75" t="inlineStr">
         <is>
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="H272" s="74" t="n"/>
-      <c r="I272" s="74" t="n"/>
-      <c r="J272" s="74" t="n"/>
-      <c r="K272" s="74" t="n"/>
+      <c r="H272" s="75" t="n"/>
+      <c r="I272" s="75" t="n"/>
+      <c r="J272" s="75" t="n"/>
+      <c r="K272" s="75" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/curriculum/master-map/Mathematics_Understood_Master_Curriculum_Map_v0.2.xlsx
+++ b/curriculum/master-map/Mathematics_Understood_Master_Curriculum_Map_v0.2.xlsx
@@ -732,7 +732,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="OpenDecisionsTable" displayName="OpenDecisionsTable" ref="A4:G14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="OpenDecisionsTable" displayName="OpenDecisionsTable" ref="A4:G15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Decision ID"/>
     <tableColumn id="2" name="Open question"/>
